--- a/literature/literature_review.xlsx
+++ b/literature/literature_review.xlsx
@@ -12,8 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Gaps" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Selection and Exclusions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exclusion Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Literature Review'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Literature Analysis'!$A$1:$AC$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Research Gaps'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Selection and Exclusions'!$A$1:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Exclusion Log'!$A$1:$C$6</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +41,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,10 +89,11 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,9 +104,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -453,7 +477,7 @@
   <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -466,7 +490,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Sr No</t>
         </is>
@@ -523,47 +547,47 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Gaboitaolelwe et al. (2023)</t>
+          <t>Niu et al. (2020)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Jwaone Gaboitaolelwe; Adamu Murtala Zungeru; Abid Yahya; Caspar K. Lebekwe; Dasari Naga Vinod; Ayodeji Olalekan Salau</t>
+          <t>Dongxiao Niu; Keke Wang; Lijie Sun; Jing Wu; Xiaomin Xu</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020-8</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Institute of Electrical and Electronics Engineers (IEEE) / IEEE Access</t>
+          <t>Elsevier BV / Applied Soft Computing</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Based Solar Photovoltaic Power Forecasting: A Review and Comparison</t>
+          <t>Short-term photovoltaic power generation forecasting based on random forest feature selection and CEEMD: A case study</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Summary: The growing interest in renewable energy and the falling prices of solar panels place solar electricity in a favourable position for adoption. However, the high-rate adoption of intermittent renewable energy introduces challenges and the potential to create power instability between the available power generation and the load demand. Hence, accurate solar Photovoltaic (PV) power forecasting is essential to maintain system reliability and maximize renewable energy integration. The current solar PV power forecasting approaches are an essential tool to maintain system reliability and maximize renewable energy integration. This paper presents a comprehensive and comparative review of existing Machine Learning (ML) based approaches used in PV power forecasting, focusing on short-term horizons. We provide an overview of factors affecting solar PV power forecasting and an overview of existing PV power forecasting methods in the literature, with a specific focus on ML-based models. To further enhance the comparison and provide more insights into the advancement in the area, we simulate the performance of different ML methods used in solar PV power forecasting and, finally, a discussion on the results of the work.</t>
+          <t>Summary: To mitigate solar curtailment caused by large-scale development of photovoltaic (PV) power generation, accurate forecasting of PV power generation is important. A hybrid forecasting model was constructed that combines random forest (RF), improved grey ideal value approximation (IGIVA), complementary ensemble empirical mode decomposition (CEEMD), the particle swarm optimization algorithm based on dynamic inertia factor (DIFPSO), and backpropagation neural network (BPNN), called RF-CEEMD-DIFPSO-BPNN. PV power generation is affected by many factors. The RF method is used to calculate the importance degree and rank the factors, then eliminate the less important factors. Then, the importance degree calculated by RF is transferred as the weight values to the IGIVA model to screen the similar days of different weather types to improve the data quality of the training sets. Then, the original power sequence is decomposed into intrinsic mode functions (IMFs) at different frequencies and a residual component by CEEMD to weaken the fluctuation of the original sequence. We empirically analyzed a PV power plant to verify the effectiveness of the hybrid model, which proved that the RF-CEEMD-DIFPSO-BPNN is a promising approach in terms of PV power generation forecasting.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Summary: To further enhance the comparison and provide more insights into the advancement in the area, we simulate the performance of different ML methods used in solar PV power forecasting and, finally, a discussion on the results of the work.</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: End-to-end hybrid pipeline coupling RF-based factor ranking, weather-type similar-day screening, CEEMD decomposition and PSO-tuned BPNN.)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>solar power forecasting review; machine learning; deep learning; survey; state of the art; Photovoltaic system; Renewable energy; Computer science; Solar power; Solar energy</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2023.3270041</t>
+          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Photovoltaic system; Computer science; Random forest; Particle swarm optimization; Backpropagation</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.asoc.2020.106389</t>
         </is>
       </c>
     </row>
@@ -573,47 +597,47 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Khouili et al. (2025)</t>
+          <t>Fonseca et al. (2011)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Oussama Khouili; Mohamed Hanine; Mohamed Louzazni; Miguel Angel López Flores; Eduardo García Villena; Imran Ashraf</t>
+          <t>Joao Gari da Silva Fonseca; Takashi Oozeki; Takumi Takashima; Gentarou Koshimizu; Yoshihisa Uchida; Kazuhiko Ogimoto</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-5</t>
+          <t>2011-07-22 (online); 2012-11 (issue)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy Strategy Reviews</t>
+          <t>Wiley / Progress in Photovoltaics: Research and Applications</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Evaluating the impact of deep learning approaches on solar and photovoltaic power forecasting: A systematic review</t>
+          <t>Use of support vector regression and numerically predicted cloudiness to forecast power output of a photovoltaic power plant in Kitakyushu, Japan</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Summary: Accurate solar and photovoltaic (PV) power forecasting is essential for optimizing grid integration, managing energy storage, and maximizing the efficiency of solar power systems. Deep learning (DL) models have shown promise in this area due to their ability to learn complex, non-linear relationships within large datasets. This study presents a systematic literature review (SLR) of deep learning applications for solar PV forecasting, addressing a gap in the existing literature, which often focuses on traditional ML or broader renewable energy applications. This review specifically aims to identify the DL architectures employed, preprocessing and feature engineering techniques used, the input features leveraged, evaluation metrics applied, and the persistent challenges in this field. Through a rigorous analysis of 26 selected papers from an initial set of 155 articles retrieved from the Web of Science database, we found that Long Short-Term Memory (LSTM) networks were the most frequently used algorithm (appearing in 32.69% of the papers), closely followed by Convolutional Neural Networks (CNNs) at 28.85%. Furthermore, Wavelet Transform (WT) was found to be the most prominent data decomposition technique, while Pearson Correlation was the most used for feature selection. We also found that ambient temperature, pressure, and humidity are the most common input features. Our systematic evaluation provides critical insights into state-of-the-art DL-based solar forecasting and identifies key areas for upcoming research. Future research should prioritize the development of more robust and interpretable models, as well as explore the integration of multi-source data to further enhance forecasting accuracy. Such advancements are crucial for the effective integration of solar energy into future power grids. • Review of DL approaches on solar and photovoltaic power forecasting. • Data preprocessing techniques and feature engineering approach for DL algorithms. • Prominent features employed for DL-based solar forecasting. • Obstacles in DL-based solar forecasting.</t>
+          <t>Summary: The development of a methodology to forecast accurately the power produced by photovoltaic systems can be an important tool for the dissemination and integration of such systems on the public electricity grids. Thus, the objective of this study was to forecast the power production of a 1‐MW photovoltaic power plant in Kitakyushu, Japan, using a new methodology based on support vector machines and on the use of several numerically predicted weather variables, including cloudiness. Hourly forecasts of the power produced for 1 year were carried out. Moreover, the effect of the use of numerically predicted cloudiness on the quality of the forecasts was also investigated. The forecasts of power production obtained with the proposed methodology had a root mean square error of 0.0948 MW h and a mean absolute error of 0.058 MW h. It was also found that the forecast and measured values of power production had a good level of correlation varying from 0.8 to 0.88 according to the season of the year. Finally, the use of numerically predicted cloudiness had an important role in the accuracy of the forecasts, and when cloudiness was not used, the root mean square error of the forecasts increased more than 32%, and the mean absolute error increased more than 42%. Copyright © 2011 John Wiley &amp; Sons, Ltd.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Summary: Through a rigorous analysis of 26 selected papers from an initial set of 155 articles retrieved from the Web of Science database, we found that Long Short-Term Memory (LSTM) networks were the most frequently used algorithm (appearing in 32.69% of the papers), closely followed by Convolutional Neural Networks (CNNs) at 28.85%.</t>
+          <t>Summary: It was also found that the forecast and measured values of power production had a good level of correlation varying from 0.8 to 0.88 according to the season of the year.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>solar power forecasting review; machine learning; deep learning; survey; state of the art; Photovoltaic system; Computer science; Engineering; Electrical engineering</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.esr.2025.101735</t>
+          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Mean squared error; Photovoltaic system; Environmental science; Meteorology; Cloud cover</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/pip.1152</t>
         </is>
       </c>
     </row>
@@ -623,47 +647,47 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Kumari &amp; Toshniwal (2021)</t>
+          <t>Massaoudi et al. (2021)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Pratima Kumari; Durga Toshniwal</t>
+          <t>Mohamed Massaoudi; Ines Chihi; Lilia Sidhom; Mohamed Trabelsi; Shady S. Refaat; Fakhreddine S. Oueslati</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2021-10</t>
+          <t>2021-07-02 (online)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Journal of Cleaner Production</t>
+          <t>MDPI AG / Energies</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Deep learning models for solar irradiance forecasting: A comprehensive review</t>
+          <t>Enhanced Random Forest Model for Robust Short-Term Photovoltaic Power Forecasting Using Weather Measurements</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Summary: NOT AVAILABLE - the source abstract is paywalled and was not retrievable from Crossref, OpenAlex, Semantic Scholar, the publisher landing page or any RePEc mirror. Bibliographic metadata for this record is fully verified, but no methodological or numerical claim is asserted here. Full-text consultation is required before citing this work.</t>
+          <t>Summary: Short-term Photovoltaic (PV) Power Forecasting (STPF) is considered a topic of utmost importance in smart grids. The deployment of STPF techniques provides fast dispatching in the case of sudden variations due to stochastic weather conditions. This paper presents an efficient data-driven method based on enhanced Random Forest (RF) model. The proposed method employs an ensemble of attribute selection techniques to manage bias/variance optimization for STPF application and enhance the forecasting quality results. The overall architecture strategy gathers the relevant information to constitute a voted feature-weighting vector of weather inputs. The main emphasis in this paper is laid on the knowledge expertise obtained from weather measurements. The feature selection techniques are based on local Interpretable Model-Agnostic Explanations, Extreme Boosting Model, and Elastic Net. A comparative performance investigation using an actual database, collected from the weather sensors, demonstrates the superiority of the proposed technique versus several data-driven machine learning models when applied to a typical distributed PV system.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Comprehensive review of deep learning models for solar irradiance forecasting (title and venue verified; 394 citations per Semantic Scholar).)</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Uses interpretability methods as a functional component of model construction (voted feature weighting) rather than as post-hoc commentary.)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>solar power forecasting review; machine learning; deep learning; survey; state of the art; Solar irradiance; Irradiance; Environmental science; Meteorology; Computer science</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jclepro.2021.128566</t>
+          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Random forest; Photovoltaic system; Computer science; Weighting; Boosting (machine learning)</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/en14133992</t>
         </is>
       </c>
     </row>
@@ -673,47 +697,47 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Markovics &amp; Mayer (2022)</t>
+          <t>Rohini et al. (2026)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Dávid Markovics; Martin János Mayer</t>
+          <t>G. Rohini; T. Mariprasth; Seif Al Bustanji; Ievgen Zaitsev</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2022-6</t>
+          <t>2026-04-10 (online)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Renewable and Sustainable Energy Reviews</t>
+          <t>Springer Science and Business Media LLC / Scientific Reports</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Comparison of machine learning methods for photovoltaic power forecasting based on numerical weather prediction</t>
+          <t>A stacked Gradient Boosting–XGBoost ensemble with ridge meta-learner for accurate short-term solar PV power forecasting in smart grids</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Summary: The increase of the worldwide installed photovoltaic (PV) capacity and the intermittent nature of the solar resource highlights the importance of power forecasting for the grid integration of the technology. This study compares 24 machine learning models for deterministic day-ahead power forecasting based on numerical weather predictions (NWP), tested for two-year-long 15-min resolution datasets of 16 PV plants in Hungary. The effects of the predictor selection and the benefits of the hyperparameter tuning are also evaluated. The results show that the two most accurate models are kernel ridge regression and multilayer perceptron with an up to 44.6% forecast skill score over persistence. Supplementing the basic NWP data with Sun position angles and statistically processed irradiance values as the inputs of the learning models results in a 13.1% decrease of the root mean square error (RMSE), which underlines the importance of the predictor selection. The hyperparameter tuning is essential to exploit the full potential of the models, especially for the less robust models, which are prone to under or overfitting without proper tuning. The overall best forecasts have a 13.9% lower RMSE compared to the baseline scenario of using linear regression. Moreover, the power forecasts based on only daily average irradiance forecasts and the Sun position angles have only a 1.5% higher RMSE than the best scenario, which demonstrates the effectiveness of machine learning even for limited data availability. The results of this paper can support both researchers and practitioners in constructing the best data-driven techniques for NWP-based PV power forecasting.</t>
+          <t>Summary: As the solar photovoltaic (PV) penetration level increases in smart grids, precise and computationally efficient short-term forecasting becomes essential to aid operational planning and real-time energy management. However, the power produced by PV is highly nonlinear and stochastic due to variations in weather factors, which weakens the performance of single forecasting models. The aim of this work is to propose a stacked ensemble regression model that combines Gradient Boosting and XGBoost (Extreme Gradient Boosting) as base learners, with Ridge Regression as the meta-learner, for very short-term PV power prediction. The model operates using meteorological and operational parameters, such as temperature, humidity, wind profile, cloudiness distribution, and solar situation. Standard preprocessing steps (missing value imputation, feature selection, and normalization) are adopted to facilitate stable model training. An empirical study is carried out using real-world PV generation data, and the results are compared with popular gradient boosting algorithms such as Gradient Boosting, XGBoost, LightGBM (Light Gradient Boosting Machine), and CatBoost (Categorical Boosting), and machine learning models such as multilayer perceptron (MLP) and LSTM, using k-fold cross-validation. The boosted ensemble improves predictive accuracy, achieving MAE = 0.042 ± 0.002, MSE = 0.0031 ± 0.0002, and R² = 94% ± 1% under the experimental conditions used in this work. Nonparametric tests (i.e., the Wilcoxon signed-rank test and the Friedman test) show that such improvements are statistically significant (p &lt; 0.05). Moreover, the inference latency of the proposed model is quite low, which demonstrates its suitability for near-real-time deployment in real-world smart grid scenarios. According to experimental results, lightweight ensemble learning can stand as a competitive and practical alternative to complicated deep learning methods for short-term PV power forecasting when data availability and computational budget are taken into account.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Summary: The results show that the two most accurate models are kernel ridge regression and multilayer perceptron with an up to 44.6% forecast skill score over persistence.</t>
+          <t>Summary: An empirical study is carried out using real-world PV generation data, and the results are compared with popular gradient boosting algorithms such as Gradient Boosting, XGBoost, LightGBM (Light Gradient Boosting Machine), and CatBoost (Categorical Boosting), and machine learning models such as multilayer perceptron (MLP) and LSTM, using k-fold cross-validation.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Numerical weather prediction; Mean squared error; Overfitting; Forecast skill; Machine learning</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.rser.2022.112364</t>
+          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Ridge; Photovoltaic system; Power (physics); Smart grid; Solar energy</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41598-026-47042-3</t>
         </is>
       </c>
     </row>
@@ -723,47 +747,47 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Niu et al. (2020)</t>
+          <t>Markovics &amp; Mayer (2022)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Dongxiao Niu; Keke Wang; Lijie Sun; Jing Wu; Xiaomin Xu</t>
+          <t>Dávid Markovics; Martin János Mayer</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2020-8</t>
+          <t>2022-6</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Applied Soft Computing</t>
+          <t>Elsevier BV / Renewable and Sustainable Energy Reviews</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Short-term photovoltaic power generation forecasting based on random forest feature selection and CEEMD: A case study</t>
+          <t>Comparison of machine learning methods for photovoltaic power forecasting based on numerical weather prediction</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Summary: To mitigate solar curtailment caused by large-scale development of photovoltaic (PV) power generation, accurate forecasting of PV power generation is important. A hybrid forecasting model was constructed that combines random forest (RF), improved grey ideal value approximation (IGIVA), complementary ensemble empirical mode decomposition (CEEMD), the particle swarm optimization algorithm based on dynamic inertia factor (DIFPSO), and backpropagation neural network (BPNN), called RF-CEEMD-DIFPSO-BPNN. PV power generation is affected by many factors. The RF method is used to calculate the importance degree and rank the factors, then eliminate the less important factors. Then, the importance degree calculated by RF is transferred as the weight values to the IGIVA model to screen the similar days of different weather types to improve the data quality of the training sets. Then, the original power sequence is decomposed into intrinsic mode functions (IMFs) at different frequencies and a residual component by CEEMD to weaken the fluctuation of the original sequence. We empirically analyzed a PV power plant to verify the effectiveness of the hybrid model, which proved that the RF-CEEMD-DIFPSO-BPNN is a promising approach in terms of PV power generation forecasting.</t>
+          <t>Summary: The increase of the worldwide installed photovoltaic (PV) capacity and the intermittent nature of the solar resource highlights the importance of power forecasting for the grid integration of the technology. This study compares 24 machine learning models for deterministic day-ahead power forecasting based on numerical weather predictions (NWP), tested for two-year-long 15-min resolution datasets of 16 PV plants in Hungary. The effects of the predictor selection and the benefits of the hyperparameter tuning are also evaluated. The results show that the two most accurate models are kernel ridge regression and multilayer perceptron with an up to 44.6% forecast skill score over persistence. Supplementing the basic NWP data with Sun position angles and statistically processed irradiance values as the inputs of the learning models results in a 13.1% decrease of the root mean square error (RMSE), which underlines the importance of the predictor selection. The hyperparameter tuning is essential to exploit the full potential of the models, especially for the less robust models, which are prone to under or overfitting without proper tuning. The overall best forecasts have a 13.9% lower RMSE compared to the baseline scenario of using linear regression. Moreover, the power forecasts based on only daily average irradiance forecasts and the Sun position angles have only a 1.5% higher RMSE than the best scenario, which demonstrates the effectiveness of machine learning even for limited data availability. The results of this paper can support both researchers and practitioners in constructing the best data-driven techniques for NWP-based PV power forecasting.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: End-to-end hybrid pipeline coupling RF-based factor ranking, weather-type similar-day screening, CEEMD decomposition and PSO-tuned BPNN.)</t>
+          <t>Summary: The results show that the two most accurate models are kernel ridge regression and multilayer perceptron with an up to 44.6% forecast skill score over persistence.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Photovoltaic system; Computer science; Random forest; Particle swarm optimization; Backpropagation</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.asoc.2020.106389</t>
+          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Numerical weather prediction; Mean squared error; Overfitting; Forecast skill; Machine learning</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.rser.2022.112364</t>
         </is>
       </c>
     </row>
@@ -773,47 +797,47 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fonseca et al. (2011)</t>
+          <t>Wang et al. (2019)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Joao Gari da Silva Fonseca; Takashi Oozeki; Takumi Takashima; Gentarou Koshimizu; Yoshihisa Uchida; Kazuhiko Ogimoto</t>
+          <t>Kejun Wang; Xiaoxia Qi; Hongda Liu</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2011-07-22 (online); 2012-11 (issue)</t>
+          <t>2019-12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Wiley / Progress in Photovoltaics: Research and Applications</t>
+          <t>Elsevier BV / Energy</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Use of support vector regression and numerically predicted cloudiness to forecast power output of a photovoltaic power plant in Kitakyushu, Japan</t>
+          <t>Photovoltaic power forecasting based LSTM-Convolutional Network</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Summary: The development of a methodology to forecast accurately the power produced by photovoltaic systems can be an important tool for the dissemination and integration of such systems on the public electricity grids. Thus, the objective of this study was to forecast the power production of a 1‐MW photovoltaic power plant in Kitakyushu, Japan, using a new methodology based on support vector machines and on the use of several numerically predicted weather variables, including cloudiness. Hourly forecasts of the power produced for 1 year were carried out. Moreover, the effect of the use of numerically predicted cloudiness on the quality of the forecasts was also investigated. The forecasts of power production obtained with the proposed methodology had a root mean square error of 0.0948 MW h and a mean absolute error of 0.058 MW h. It was also found that the forecast and measured values of power production had a good level of correlation varying from 0.8 to 0.88 according to the season of the year. Finally, the use of numerically predicted cloudiness had an important role in the accuracy of the forecasts, and when cloudiness was not used, the root mean square error of the forecasts increased more than 32%, and the mean absolute error increased more than 42%. Copyright © 2011 John Wiley &amp; Sons, Ltd.</t>
+          <t>Summary: The volatile and intermittent nature of solar energy itself presents a significant challenge in integrating it into existing energy systems. Accurate photovoltaic power prediction plays an important role in solving this problem. With the development of deep learning, more and more scholars have applied the deep learning model to time series prediction and achieved very good results. In this paper, a hybrid deep learning model (LSTM-Convolutional Network) is proposed and applied to photovoltaic power prediction. In the proposed hybrid prediction model, the temporal features of the data are extracted first by the long-short term memory network, and then the spatial features of the data are extracted by the convolutional neural network model. In order to show the superior performance of the proposed hybrid prediction model, the prediction results of the hybrid model are compared with those of the single model (long-short term memory network, convolutional neural network) and the hybrid network (Convolutional-LSTM Network) model, and the results of eight error evaluation indexes are given. The results show that the hybrid prediction model has better prediction effect than the single prediction model, and the proposed hybrid model (extract the temporal characteristics of data first, and then extract the spatial characteristics of data) is better than Convolutional-LSTM Network (extract the spatial characteristics of data first, and then extract the temporal characteristics of data).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Summary: It was also found that the forecast and measured values of power production had a good level of correlation varying from 0.8 to 0.88 according to the season of the year.</t>
+          <t>Summary: In order to show the superior performance of the proposed hybrid prediction model, the prediction results of the hybrid model are compared with those of the single model (long-short term memory network, convolutional neural network) and the hybrid network (Convolutional-LSTM Network) model, and the results of eight error evaluation indexes are given.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Mean squared error; Photovoltaic system; Environmental science; Meteorology; Cloud cover</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/pip.1152</t>
+          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Computer science; Convolutional neural network; Photovoltaic system; Artificial intelligence; Deep learning</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.energy.2019.116225</t>
         </is>
       </c>
     </row>
@@ -823,47 +847,47 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Massaoudi et al. (2021)</t>
+          <t>Gupta &amp; Singh (2023)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Massaoudi; Ines Chihi; Lilia Sidhom; Mohamed Trabelsi; Shady S. Refaat; Fakhreddine S. Oueslati</t>
+          <t>Priya Gupta; Rhythm Singh</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2021-07-02 (online)</t>
+          <t>2023-9</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>MDPI AG / Energies</t>
+          <t>Elsevier BV / Sustainable Energy, Grids and Networks</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Enhanced Random Forest Model for Robust Short-Term Photovoltaic Power Forecasting Using Weather Measurements</t>
+          <t>Forecasting hourly day-ahead solar photovoltaic power generation by assembling a new adaptive multivariate data analysis with a long short-term memory network</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Summary: Short-term Photovoltaic (PV) Power Forecasting (STPF) is considered a topic of utmost importance in smart grids. The deployment of STPF techniques provides fast dispatching in the case of sudden variations due to stochastic weather conditions. This paper presents an efficient data-driven method based on enhanced Random Forest (RF) model. The proposed method employs an ensemble of attribute selection techniques to manage bias/variance optimization for STPF application and enhance the forecasting quality results. The overall architecture strategy gathers the relevant information to constitute a voted feature-weighting vector of weather inputs. The main emphasis in this paper is laid on the knowledge expertise obtained from weather measurements. The feature selection techniques are based on local Interpretable Model-Agnostic Explanations, Extreme Boosting Model, and Elastic Net. A comparative performance investigation using an actual database, collected from the weather sensors, demonstrates the superiority of the proposed technique versus several data-driven machine learning models when applied to a typical distributed PV system.</t>
+          <t>Summary: Accurate multi-step PV power forecasting is a challenging task because of complex time series and error buildup in muti-step forecasts. This work is based on developing a decomposition-based hybrid model for hourly day-ahead PV power forecasting. Noise-assisted multivariate empirical mode decomposition (NA-MEMD) is an updated version of a popular MEMD technique that breaks the original series into several subseries termed as intrinsic mode functions (IMFs). Due to IMFs' statistically independent behavior, a separate long short-term memory (LSTM) network is designed for each set of multivariate IMFs. A single LSTM model is trained to simultaneously predict the IMF of the target variable for the sunshine hours of a day. Incorporating NA-MEMD with LSTM showed an average % RMSE (% MAE) reduction of 47.65 (50.99) and 11.11 (15.76) compared to the standalone LSTM and MEMD-based LSTM model, respectively, across three locations. The proposed model reported an average RMSE of 65.08 W/m2 across three locations. This investigation indicates that decomposition-based hybrid models can potentially reduce the error of multi-step forecasts. This study also recommends using NA-MEMD instead of MEMD because it improves forecast accuracy and requires less time for data demarcation (MEMD: 251 sec, NA-MEMD: 195 sec).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Uses interpretability methods as a functional component of model construction (voted feature weighting) rather than as post-hoc commentary.)</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Decomposition-based day-ahead multi-step forecasting with a per-IMF LSTM design, plus a decomposition-cost comparison (NA-MEMD 195 s vs MEMD 251 s).)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Random forest; Photovoltaic system; Computer science; Weighting; Boosting (machine learning)</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/en14133992</t>
+          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Computer science; Multivariate statistics; Photovoltaic system; Mean squared error; Mode (computer interface)</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.segan.2023.101133</t>
         </is>
       </c>
     </row>
@@ -873,47 +897,47 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Rohini et al. (2026)</t>
+          <t>Yu et al. (2019)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>G. Rohini; T. Mariprasth; Seif Al Bustanji; Ievgen Zaitsev</t>
+          <t>Yunjun Yu; Junfei Cao; Jianyong Zhu</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10 (online)</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Springer Science and Business Media LLC / Scientific Reports</t>
+          <t>Institute of Electrical and Electronics Engineers (IEEE) / IEEE Access</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>A stacked Gradient Boosting–XGBoost ensemble with ridge meta-learner for accurate short-term solar PV power forecasting in smart grids</t>
+          <t>An LSTM Short-Term Solar Irradiance Forecasting Under Complicated Weather Conditions</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Summary: As the solar photovoltaic (PV) penetration level increases in smart grids, precise and computationally efficient short-term forecasting becomes essential to aid operational planning and real-time energy management. However, the power produced by PV is highly nonlinear and stochastic due to variations in weather factors, which weakens the performance of single forecasting models. The aim of this work is to propose a stacked ensemble regression model that combines Gradient Boosting and XGBoost (Extreme Gradient Boosting) as base learners, with Ridge Regression as the meta-learner, for very short-term PV power prediction. The model operates using meteorological and operational parameters, such as temperature, humidity, wind profile, cloudiness distribution, and solar situation. Standard preprocessing steps (missing value imputation, feature selection, and normalization) are adopted to facilitate stable model training. An empirical study is carried out using real-world PV generation data, and the results are compared with popular gradient boosting algorithms such as Gradient Boosting, XGBoost, LightGBM (Light Gradient Boosting Machine), and CatBoost (Categorical Boosting), and machine learning models such as multilayer perceptron (MLP) and LSTM, using k-fold cross-validation. The boosted ensemble improves predictive accuracy, achieving MAE = 0.042 ± 0.002, MSE = 0.0031 ± 0.0002, and R² = 94% ± 1% under the experimental conditions used in this work. Nonparametric tests (i.e., the Wilcoxon signed-rank test and the Friedman test) show that such improvements are statistically significant (p &lt; 0.05). Moreover, the inference latency of the proposed model is quite low, which demonstrates its suitability for near-real-time deployment in real-world smart grid scenarios. According to experimental results, lightweight ensemble learning can stand as a competitive and practical alternative to complicated deep learning methods for short-term PV power forecasting when data availability and computational budget are taken into account.</t>
+          <t>Summary: Complicated weather conditions lead to intermittent, random and volatility in photovoltaic (PV) systems, which makes PV predictions difficult. A recurrent neural network (RNN) is considered to be an effective tool for time-series data prediction. However, when the weather changes intensely, the long-term sequence of multivariate may cause gradient vanishing (exploding) during the training of RNN, leading the prediction results to local optimum. Long short-term memory (LSTM) network is the deep structure of RNN. Due to its special hidden layer unit structure, it can preserve the trend information contained in the long-term sequence, which is allowed to solve the problems of RNN and improve performance. An LSTM-based approach is applied for short-term predictions in this study based on a timescale that encompasses global horizontal irradiance (GHI) one hour in advance and one day in advance. Inaccurate forecasts usually occur on cloudy days, and the results of ANN and SVR in the literature prove this. To improve prediction accuracy on cloudy days, the clearness-index was introduced as an input data for the LSTM model and to classify the type of weather by k-means during the data processing, where cloudy days are classified as the cloudy and the mixed(partially cloudy). NN models are established to compare the accuracy of different approaches and the cross-regional study is to prove whether the method can be generalizable. From the results of hourly forecast, the R2 coefficient of LSTM on cloudy days and mixed days is exceeding 0.9, while the R2 of RNN is only 0.70 and 0.79 in Atlanta and Hawaii. From the results of daily forecast, All R2 on cloudy days is about 0.85. However, the LSTM is still very effective in improving of RNN and more accurate than other models.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Summary: An empirical study is carried out using real-world PV generation data, and the results are compared with popular gradient boosting algorithms such as Gradient Boosting, XGBoost, LightGBM (Light Gradient Boosting Machine), and CatBoost (Categorical Boosting), and machine learning models such as multilayer perceptron (MLP) and LSTM, using k-fold cross-validation.</t>
+          <t>Summary: Inaccurate forecasts usually occur on cloudy days, and the results of ANN and SVR in the literature prove this.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>photovoltaic power forecasting; machine learning; XGBoost; random forest; support vector regression; gradient boosting; NWP; Ridge; Photovoltaic system; Power (physics); Smart grid; Solar energy</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-026-47042-3</t>
+          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Term (time); Irradiance; Solar irradiance; Meteorology; Weather forecasting</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/access.2019.2946057</t>
         </is>
       </c>
     </row>
@@ -923,47 +947,47 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Wang et al. (2019)</t>
+          <t>Sun et al. (2019)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Kejun Wang; Xiaoxia Qi; Hongda Liu</t>
+          <t>Yuchi Sun; Vignesh Venugopal; Adam R. Brandt</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2019-12</t>
+          <t>2019-8</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy</t>
+          <t>Elsevier BV / Solar Energy</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Photovoltaic power forecasting based LSTM-Convolutional Network</t>
+          <t>Short-term solar power forecast with deep learning: Exploring optimal input and output configuration</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Summary: The volatile and intermittent nature of solar energy itself presents a significant challenge in integrating it into existing energy systems. Accurate photovoltaic power prediction plays an important role in solving this problem. With the development of deep learning, more and more scholars have applied the deep learning model to time series prediction and achieved very good results. In this paper, a hybrid deep learning model (LSTM-Convolutional Network) is proposed and applied to photovoltaic power prediction. In the proposed hybrid prediction model, the temporal features of the data are extracted first by the long-short term memory network, and then the spatial features of the data are extracted by the convolutional neural network model. In order to show the superior performance of the proposed hybrid prediction model, the prediction results of the hybrid model are compared with those of the single model (long-short term memory network, convolutional neural network) and the hybrid network (Convolutional-LSTM Network) model, and the results of eight error evaluation indexes are given. The results show that the hybrid prediction model has better prediction effect than the single prediction model, and the proposed hybrid model (extract the temporal characteristics of data first, and then extract the spatial characteristics of data) is better than Convolutional-LSTM Network (extract the spatial characteristics of data first, and then extract the temporal characteristics of data).</t>
+          <t>Summary: The volatility of cloud movement introduces significant uncertainty in short-term solar power forecasting, which can complicate the operation of modern power systems. This work proposes a specialized convolutional neural network (CNN) “SUNSET” to predict 15-min ahead minutely-averaged PV output. The model is characterized by its usage of hybrid input, temporal history and strong regularization. On a 1-year database, the “baseline” model achieves 16.3% forecast skill in cloudy conditions and 15.7% in all weather conditions, relative to a smart persistence forecast. Optimal input and output configurations are explored and suggestions are given. In terms of input, both sky images and PV output history are found to be crucial. Output-wise, training against PV output significantly outperforms using clear sky index (CSI). Careful down-sampling can reduce the training time by as much as 83% without affecting accuracy. For lag term configurations, using the same length of history as the forecast horizon is a good heuristic, while using slightly shorter history yielded a modest 0.5–0.9% improvement in this case. To ensure reproducibility and facilitate future works, the code base of this work is available at Github/YuchiSun/SUNSET.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Summary: In order to show the superior performance of the proposed hybrid prediction model, the prediction results of the hybrid model are compared with those of the single model (long-short term memory network, convolutional neural network) and the hybrid network (Convolutional-LSTM Network) model, and the results of eight error evaluation indexes are given.</t>
+          <t>Summary: Output-wise, training against PV output significantly outperforms using clear sky index (CSI).</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Computer science; Convolutional neural network; Photovoltaic system; Artificial intelligence; Deep learning</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.energy.2019.116225</t>
+          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Computer science; Term (time); Sky; Deep learning; Forecast skill</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.solener.2019.06.041</t>
         </is>
       </c>
     </row>
@@ -973,47 +997,47 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Gupta &amp; Singh (2023)</t>
+          <t>Mishra et al. (2020)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Priya Gupta; Rhythm Singh</t>
+          <t>Manohar Mishra; Pandit Byomakesha Dash; Janmenjoy Nayak; Bighnaraj Naik; Subrat Kumar Swain</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2023-9</t>
+          <t>2020-12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Sustainable Energy, Grids and Networks</t>
+          <t>Elsevier BV / Measurement</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Forecasting hourly day-ahead solar photovoltaic power generation by assembling a new adaptive multivariate data analysis with a long short-term memory network</t>
+          <t>Deep learning and wavelet transform integrated approach for short-term solar PV power prediction</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Summary: Accurate multi-step PV power forecasting is a challenging task because of complex time series and error buildup in muti-step forecasts. This work is based on developing a decomposition-based hybrid model for hourly day-ahead PV power forecasting. Noise-assisted multivariate empirical mode decomposition (NA-MEMD) is an updated version of a popular MEMD technique that breaks the original series into several subseries termed as intrinsic mode functions (IMFs). Due to IMFs' statistically independent behavior, a separate long short-term memory (LSTM) network is designed for each set of multivariate IMFs. A single LSTM model is trained to simultaneously predict the IMF of the target variable for the sunshine hours of a day. Incorporating NA-MEMD with LSTM showed an average % RMSE (% MAE) reduction of 47.65 (50.99) and 11.11 (15.76) compared to the standalone LSTM and MEMD-based LSTM model, respectively, across three locations. The proposed model reported an average RMSE of 65.08 W/m2 across three locations. This investigation indicates that decomposition-based hybrid models can potentially reduce the error of multi-step forecasts. This study also recommends using NA-MEMD instead of MEMD because it improves forecast accuracy and requires less time for data demarcation (MEMD: 251 sec, NA-MEMD: 195 sec).</t>
+          <t>Summary: A novel short-term solar power prediction model is presented in this work, by utilizing the learning ability of Long-Shot-Term-Memory network (LSTM) based deep learning (DL) technique and the concept of wavelet transform (WT). In this proposed WT-LSTM model, the WT is used to decompose the recorded solar energy time-series data into different frequency series followed by the statistical feature extraction process. The LSTM with dropout based DL model is proposed to predict the futuristic value of solar energy generation in different time-horizon (hourly and day basis), where the statistical WT based features combined with several other meteorological factors such as temperature, wind speed, pressure, cloudy-index, humidity and altimeter index are modelled as input to the LSTM model. The efficiency of the suggested WT-LSTM model has been proved by comparing statistical performance measures in terms of RMSE, MAPE, MAE and R2 score, with other contemporary machine learning and deep-learning based models.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Decomposition-based day-ahead multi-step forecasting with a per-IMF LSTM design, plus a decomposition-cost comparison (NA-MEMD 195 s vs MEMD 251 s).)</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Couples wavelet-domain feature extraction with an LSTM and evaluates at two horizons (hourly and daily).)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Computer science; Multivariate statistics; Photovoltaic system; Mean squared error; Mode (computer interface)</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.segan.2023.101133</t>
+          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Mean squared error; Wavelet transform; Artificial intelligence; Computer science; Deep learning</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.measurement.2020.108250</t>
         </is>
       </c>
     </row>
@@ -1023,47 +1047,47 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Yu et al. (2019)</t>
+          <t>Yao et al. (2022)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Yunjun Yu; Junfei Cao; Jianyong Zhu</t>
+          <t>Tiechui Yao; Jue Wang; Haoyan Wu; Pei Zhang; Shigang Li; Ke Xu; Xiaoyan Liu; Xuebin Chi</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022-1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Institute of Electrical and Electronics Engineers (IEEE) / IEEE Access</t>
+          <t>Institute of Electrical and Electronics Engineers (IEEE) / IEEE Transactions on Sustainable Energy</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>An LSTM Short-Term Solar Irradiance Forecasting Under Complicated Weather Conditions</t>
+          <t>Intra-Hour Photovoltaic Generation Forecasting Based on Multi-Source Data and Deep Learning Methods</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Summary: Complicated weather conditions lead to intermittent, random and volatility in photovoltaic (PV) systems, which makes PV predictions difficult. A recurrent neural network (RNN) is considered to be an effective tool for time-series data prediction. However, when the weather changes intensely, the long-term sequence of multivariate may cause gradient vanishing (exploding) during the training of RNN, leading the prediction results to local optimum. Long short-term memory (LSTM) network is the deep structure of RNN. Due to its special hidden layer unit structure, it can preserve the trend information contained in the long-term sequence, which is allowed to solve the problems of RNN and improve performance. An LSTM-based approach is applied for short-term predictions in this study based on a timescale that encompasses global horizontal irradiance (GHI) one hour in advance and one day in advance. Inaccurate forecasts usually occur on cloudy days, and the results of ANN and SVR in the literature prove this. To improve prediction accuracy on cloudy days, the clearness-index was introduced as an input data for the LSTM model and to classify the type of weather by k-means during the data processing, where cloudy days are classified as the cloudy and the mixed(partially cloudy). NN models are established to compare the accuracy of different approaches and the cross-regional study is to prove whether the method can be generalizable. From the results of hourly forecast, the R2 coefficient of LSTM on cloudy days and mixed days is exceeding 0.9, while the R2 of RNN is only 0.70 and 0.79 in Atlanta and Hawaii. From the results of daily forecast, All R2 on cloudy days is about 0.85. However, the LSTM is still very effective in improving of RNN and more accurate than other models.</t>
+          <t>Summary: Global issues pertaining to climate change have necessitated the rapid deployment of new energy sources, such as photovoltaic (PV) generation. In smart grids, accurate forecasting is essential to ensure the reliability and economy of the power system. However, PV generation is severely affected by meteorological factors, which hinders accurate forecasting. Various types of data, such as local measurement data, numerical weather prediction, and satellite images, can reflect meteorological dynamics over different time scales. This paper proposes a novel data-driven forecasting framework based on deep learning, which integrates an advanced U-net and an encoder-decoder architecture to cooperatively process multi-source (time series recording and satellite image) data. The adaption of the neural networks to the data sources and the collaborative learning of both spatial and temporal features boost the model accuracy. The experimental results for 50 real-world PV power stations indicate that the proposed framework features a higher accuracy than that of other baseline models.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Summary: Inaccurate forecasts usually occur on cloudy days, and the results of ANN and SVR in the literature prove this.</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Demonstrates that fusing satellite imagery with local time series via U-Net plus encoder-decoder improves intra-hour forecasting, validated at unusual scale (50 stations).)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Term (time); Irradiance; Solar irradiance; Meteorology; Weather forecasting</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2019.2946057</t>
+          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Computer science; Software deployment; Deep learning; Data modeling</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/tste.2021.3123337</t>
         </is>
       </c>
     </row>
@@ -1073,47 +1097,47 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Sun et al. (2019)</t>
+          <t>Liu &amp; Mao (2024)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Yuchi Sun; Vignesh Venugopal; Adam R. Brandt</t>
+          <t>Wencheng Liu; Zhizhong Mao</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2019-8</t>
+          <t>2024-5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Solar Energy</t>
+          <t>Elsevier BV / Renewable Energy</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Short-term solar power forecast with deep learning: Exploring optimal input and output configuration</t>
+          <t>Short-term photovoltaic power forecasting with feature extraction and attention mechanisms</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Summary: The volatility of cloud movement introduces significant uncertainty in short-term solar power forecasting, which can complicate the operation of modern power systems. This work proposes a specialized convolutional neural network (CNN) “SUNSET” to predict 15-min ahead minutely-averaged PV output. The model is characterized by its usage of hybrid input, temporal history and strong regularization. On a 1-year database, the “baseline” model achieves 16.3% forecast skill in cloudy conditions and 15.7% in all weather conditions, relative to a smart persistence forecast. Optimal input and output configurations are explored and suggestions are given. In terms of input, both sky images and PV output history are found to be crucial. Output-wise, training against PV output significantly outperforms using clear sky index (CSI). Careful down-sampling can reduce the training time by as much as 83% without affecting accuracy. For lag term configurations, using the same length of history as the forecast horizon is a good heuristic, while using slightly shorter history yielded a modest 0.5–0.9% improvement in this case. To ensure reproducibility and facilitate future works, the code base of this work is available at Github/YuchiSun/SUNSET.</t>
+          <t>Summary: The uncertainty of weather conditions has always been a major challenge limiting the performance of photovoltaic (PV) power prediction. Enhancing the accuracy and stability of PV power prediction is crucial for optimizing grid operation. In response to this challenge, this study introduces a hybrid model that integrates an attention mechanism with the Convolutional Neural Network (CNN) and Bidirectional Long Short-Term Memory Network (BiLSTM). This model aims to mitigate the adverse impact of weather variability on the accuracy of PV power prediction by effectively extracting key features from multidimensional time series data. Additionally, through ablation experiments, this research further assesses the contribution of each model component to performance. Validated with actual data collected from a 1 MW PV power station in China, our proposed model demonstrates significant performance advantages compared to eight advanced prediction models. Ablation study results reveal that removing the CNN component led to a 58.2% increase in MAE and a 53.9% increase in RMSE, while the removal of the attention mechanism resulted in an 83.8% increase in maximum error. These findings underscore the substantial enhancement in prediction accuracy achieved through the integration of CNN and BiLSTM, and the introduction of the attention mechanism significantly boosts the model's prediction stability.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Summary: Output-wise, training against PV output significantly outperforms using clear sky index (CSI).</t>
+          <t>Summary: Ablation study results reveal that removing the CNN component led to a 58.2% increase in MAE and a 53.9% increase in RMSE, while the removal of the attention mechanism resulted in an 83.8% increase in maximum error.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>LSTM; GRU; recurrent neural network; short-term solar power forecasting; time-series regression; Computer science; Term (time); Sky; Deep learning; Forecast skill</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.solener.2019.06.041</t>
+          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Computer science; Stability (learning theory); Component (thermodynamics); Convolutional neural network</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.renene.2024.120437</t>
         </is>
       </c>
     </row>
@@ -1123,47 +1147,47 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mishra et al. (2020)</t>
+          <t>Hu et al. (2024)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Manohar Mishra; Pandit Byomakesha Dash; Janmenjoy Nayak; Bighnaraj Naik; Subrat Kumar Swain</t>
+          <t>Feng Hu; Linghua Zhang; Jiaqi Wang</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2020-12</t>
+          <t>2024-06-14 (online)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Measurement</t>
+          <t>MDPI AG / Applied Sciences</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Deep learning and wavelet transform integrated approach for short-term solar PV power prediction</t>
+          <t>A Hybrid Convolutional–Long Short-Term Memory–Attention Framework for Short-Term Photovoltaic Power Forecasting, Incorporating Data from Neighboring Stations</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Summary: A novel short-term solar power prediction model is presented in this work, by utilizing the learning ability of Long-Shot-Term-Memory network (LSTM) based deep learning (DL) technique and the concept of wavelet transform (WT). In this proposed WT-LSTM model, the WT is used to decompose the recorded solar energy time-series data into different frequency series followed by the statistical feature extraction process. The LSTM with dropout based DL model is proposed to predict the futuristic value of solar energy generation in different time-horizon (hourly and day basis), where the statistical WT based features combined with several other meteorological factors such as temperature, wind speed, pressure, cloudy-index, humidity and altimeter index are modelled as input to the LSTM model. The efficiency of the suggested WT-LSTM model has been proved by comparing statistical performance measures in terms of RMSE, MAPE, MAE and R2 score, with other contemporary machine learning and deep-learning based models.</t>
+          <t>Summary: To enhance the safety of grid operations, this paper proposes a high-precision short-term photovoltaic (PV) power forecasting method that integrates information from surrounding PV stations and deep learning prediction models. The proposed method utilizes numerical weather prediction (NWP) data of the target PV station and highly correlated features from nearby stations as inputs. This study first analyzes the correlation between irradiance and power sequences and calculates a comprehensive similarity index based on distance factors. Stations with high-similarity indices are selected as data sources. Subsequently, Bayesian optimization is employed to determine the optimal data fusion ratio. The selected data are then used to model power predictions through the convolutional long short-term memory with attention (Conv-LSTM-ATT) deep neural network. Experimental results show that the proposed model significantly outperforms three classical models in terms of forecasting accuracy. The data fusion strategy determined by Bayesian optimization reduces the root mean square error (RMSE) of the test set by 20.04%, 28.24%, and 30.94% under sunny, cloudy, and rainy conditions, respectively.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Couples wavelet-domain feature extraction with an LSTM and evaluates at two horizons (hourly and daily).)</t>
+          <t>Summary: Experimental results show that the proposed model significantly outperforms three classical models in terms of forecasting accuracy.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Mean squared error; Wavelet transform; Artificial intelligence; Computer science; Deep learning</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.measurement.2020.108250</t>
+          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Computer science; Mean squared error; Term (time); Convolutional neural network</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/app14125189</t>
         </is>
       </c>
     </row>
@@ -1173,47 +1197,47 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Yao et al. (2022)</t>
+          <t>Dai et al. (2022)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tiechui Yao; Jue Wang; Haoyan Wu; Pei Zhang; Shigang Li; Ke Xu; Xiaoyan Liu; Xuebin Chi</t>
+          <t>Yeming Dai; Yanxin Wang; Mingming Leng; Xinyu Yang; Qiong Zhou</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2022-1</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Institute of Electrical and Electronics Engineers (IEEE) / IEEE Transactions on Sustainable Energy</t>
+          <t>Elsevier BV / Energy</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Intra-Hour Photovoltaic Generation Forecasting Based on Multi-Source Data and Deep Learning Methods</t>
+          <t>LOWESS smoothing and Random Forest based GRU model: A short-term photovoltaic power generation forecasting method</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Summary: Global issues pertaining to climate change have necessitated the rapid deployment of new energy sources, such as photovoltaic (PV) generation. In smart grids, accurate forecasting is essential to ensure the reliability and economy of the power system. However, PV generation is severely affected by meteorological factors, which hinders accurate forecasting. Various types of data, such as local measurement data, numerical weather prediction, and satellite images, can reflect meteorological dynamics over different time scales. This paper proposes a novel data-driven forecasting framework based on deep learning, which integrates an advanced U-net and an encoder-decoder architecture to cooperatively process multi-source (time series recording and satellite image) data. The adaption of the neural networks to the data sources and the collaborative learning of both spatial and temporal features boost the model accuracy. The experimental results for 50 real-world PV power stations indicate that the proposed framework features a higher accuracy than that of other baseline models.</t>
+          <t>Summary: Photovoltaic (PV) power generation forecasting mainly includes data processing and model prediction, in which data processing is a necessary prerequisite. Existing studies generally overlook the effect of data fluctuation on prediction performance. To address this, this paper compares five data smoothing techniques for daily PV power generation - locally weighted scatterplot smoothing (LOWESS), locally estimated scatterplot smoothing (LOESS), percentile filtering (PF), Savitzky-Golay smoothing (SG) and adjacent average (AAv) - and retains the one with the lowest prediction error. Random Forest is then used for feature selection to identify the natural factors that most affect daily PV power generation. Finally, the GRU prediction model is optimised by adding RepeatVector and TimeDistributed layers, which the authors argue differentiates it from other optimised GRU models in terms of model hierarchy and multidimensional input handling. The method is validated on daily PV power generation data from Xuhui District, Shanghai, China, and additionally on DKASC (Alice Springs, Australia) data to compare short-term forecasting against medium- and long-term forecasting horizons. The authors position the contribution as the combination of smoothing-based data processing, Random Forest feature selection and an improved GRU architecture, which none of the compared reference models jointly provide.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Demonstrates that fusing satellite imagery with local time series via U-Net plus encoder-decoder improves intra-hour forecasting, validated at unusual scale (50 stations).)</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Compares five smoothing techniques head-to-head, adds RF feature selection, and augments GRU with RepeatVector/TimeDistributed layers; tests the method on a second, climatically distinct dataset.)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Computer science; Software deployment; Deep learning; Data modeling</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tste.2021.3123337</t>
+          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Term (time); Random forest; Smoothing; Econometrics</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.energy.2022.124661</t>
         </is>
       </c>
     </row>
@@ -1223,47 +1247,47 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Liu &amp; Mao (2024)</t>
+          <t>Lei et al. (2026)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Wencheng Liu; Zhizhong Mao</t>
+          <t>Mingze Lei; Tao Chen; Yao Xiao; Caixia Yang; Worawat Sa-Ngiamvibool; Supannika Wattana; Buncha Wattana</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2024-5</t>
+          <t>2026-04-02 (online)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Renewable Energy</t>
+          <t>MDPI AG / Energies</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Short-term photovoltaic power forecasting with feature extraction and attention mechanisms</t>
+          <t>Short-Term Photovoltaic Power Forecasting Based on CNN–LSTM–Attention Mechanism</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Summary: The uncertainty of weather conditions has always been a major challenge limiting the performance of photovoltaic (PV) power prediction. Enhancing the accuracy and stability of PV power prediction is crucial for optimizing grid operation. In response to this challenge, this study introduces a hybrid model that integrates an attention mechanism with the Convolutional Neural Network (CNN) and Bidirectional Long Short-Term Memory Network (BiLSTM). This model aims to mitigate the adverse impact of weather variability on the accuracy of PV power prediction by effectively extracting key features from multidimensional time series data. Additionally, through ablation experiments, this research further assesses the contribution of each model component to performance. Validated with actual data collected from a 1 MW PV power station in China, our proposed model demonstrates significant performance advantages compared to eight advanced prediction models. Ablation study results reveal that removing the CNN component led to a 58.2% increase in MAE and a 53.9% increase in RMSE, while the removal of the attention mechanism resulted in an 83.8% increase in maximum error. These findings underscore the substantial enhancement in prediction accuracy achieved through the integration of CNN and BiLSTM, and the introduction of the attention mechanism significantly boosts the model's prediction stability.</t>
+          <t>Summary: Accurate short-term photovoltaic (PV) power forecasting is crucial for maintaining grid stability. However, existing hybrid deep learning models suffer from inherent limitations owing to static feature-weighting mechanisms, often displaying significant phase lag and peak clipping under severe meteorological fluctuations. To address this, in this study, we adopt a hybrid CNN–LSTM–Attention forecasting framework incorporating an SE-based attention strategy. Field validation at a 150 kW PV power plant in Ningxia, China, demonstrated that the adopted model achieved a Root Mean Square Error (RMSE) convergence of 2.157 kW. Notably, this represented a 41.92% reduction in error compared to the standard LSTM benchmark and a further 16.46% improvement over the suboptimal CNN-LSTM baseline, explicitly confirming the specific contribution of the SE-based attention mechanism. Moreover, multi-weather evaluations and ablation studies confirm the framework’s robustness. Dynamic Time Warping (DTW) and Diebold–Mariano (DM) tests establish its statistical superiority and the reduction in phase lag against baselines. Residual analysis reveals a leptokurtic distribution with white noise properties, confirming the reduction in systematic bias. Consequently, this high-fidelity tracking allows precise minute-level ramping detection and decreases spinning reserve demands in practical power dispatch.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Summary: Ablation study results reveal that removing the CNN component led to a 58.2% increase in MAE and a 53.9% increase in RMSE, while the removal of the attention mechanism resulted in an 83.8% increase in maximum error.</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: One of very few papers in this corpus that applies a Diebold-Mariano test and analyses residual distributions to support a superiority claim, and quantifies the attention module's marginal contribution.)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Computer science; Stability (learning theory); Component (thermodynamics); Convolutional neural network</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.renene.2024.120437</t>
+          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Benchmark (surveying); Residual; Photovoltaic system; Reduction (mathematics); Power (physics)</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/en19071747</t>
         </is>
       </c>
     </row>
@@ -1273,47 +1297,47 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hu et al. (2024)</t>
+          <t>Kim et al. (2024)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Feng Hu; Linghua Zhang; Jiaqi Wang</t>
+          <t>Jimin Kim; Josue Obregon; Hoonseok Park; Jae-Yoon Jung</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2024-06-14 (online)</t>
+          <t>2024-8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>MDPI AG / Applied Sciences</t>
+          <t>Elsevier BV / Renewable and Sustainable Energy Reviews</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>A Hybrid Convolutional–Long Short-Term Memory–Attention Framework for Short-Term Photovoltaic Power Forecasting, Incorporating Data from Neighboring Stations</t>
+          <t>Multi-step photovoltaic power forecasting using transformer and recurrent neural networks</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Summary: To enhance the safety of grid operations, this paper proposes a high-precision short-term photovoltaic (PV) power forecasting method that integrates information from surrounding PV stations and deep learning prediction models. The proposed method utilizes numerical weather prediction (NWP) data of the target PV station and highly correlated features from nearby stations as inputs. This study first analyzes the correlation between irradiance and power sequences and calculates a comprehensive similarity index based on distance factors. Stations with high-similarity indices are selected as data sources. Subsequently, Bayesian optimization is employed to determine the optimal data fusion ratio. The selected data are then used to model power predictions through the convolutional long short-term memory with attention (Conv-LSTM-ATT) deep neural network. Experimental results show that the proposed model significantly outperforms three classical models in terms of forecasting accuracy. The data fusion strategy determined by Bayesian optimization reduces the root mean square error (RMSE) of the test set by 20.04%, 28.24%, and 30.94% under sunny, cloudy, and rainy conditions, respectively.</t>
+          <t>Summary: Affordable and clean energy is an important UN sustainable development goal. Solar energy is more difficult to control than fossil fuels, highlighting the need for accurate solar power forecasts. This study develops three variants of the transformer networks, called PVTransNet, for a multi-step day-ahead photovoltaic power forecasting. The transformer networks use historical solar power generation, weather observation, weather forecast and solar geometry data as input to effectively predict next-day hourly power generation. In particular, the third variant model combines long short-term memory (LSTM) to transformer networks to supplement weather forecasts from the weather station. The combined model, PVTransNet-EDR, outperformed individual LSTM and other transformer models in the experiments conducted on data from two photovoltaic power plants. The model performed 48.3 % better, in mean absolute error, than simple LSTM in the power forecasting. Accurate solar power forecasting model is expected to be utilized for efficient energy storage and microgrid management, effective energy supply policy, and optimal plant location selection.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Summary: Experimental results show that the proposed model significantly outperforms three classical models in terms of forecasting accuracy.</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Shows that combining an LSTM encoder with a transformer, and adding solar geometry alongside weather data, yields large day-ahead gains over plain LSTM on two plants.)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Computer science; Mean squared error; Term (time); Convolutional neural network</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/app14125189</t>
+          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Photovoltaic system; Artificial neural network; Transformer; Computer science; Engineering</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.rser.2024.114479</t>
         </is>
       </c>
     </row>
@@ -1323,47 +1347,47 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dai et al. (2022)</t>
+          <t>Piantadosi et al. (2024)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Yeming Dai; Yanxin Wang; Mingming Leng; Xinyu Yang; Qiong Zhou</t>
+          <t>Gabriele Piantadosi; Sofia Dutto; Antonio Galli; Saverio De Vito; Carlo Sansone; Girolamo Di Francia</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2022-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy</t>
+          <t>Elsevier BV / Energy and AI</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>LOWESS smoothing and Random Forest based GRU model: A short-term photovoltaic power generation forecasting method</t>
+          <t>Photovoltaic power forecasting: A Transformer based framework</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Summary: Photovoltaic (PV) power generation forecasting mainly includes data processing and model prediction, in which data processing is a necessary prerequisite. Existing studies generally overlook the effect of data fluctuation on prediction performance. To address this, this paper compares five data smoothing techniques for daily PV power generation - locally weighted scatterplot smoothing (LOWESS), locally estimated scatterplot smoothing (LOESS), percentile filtering (PF), Savitzky-Golay smoothing (SG) and adjacent average (AAv) - and retains the one with the lowest prediction error. Random Forest is then used for feature selection to identify the natural factors that most affect daily PV power generation. Finally, the GRU prediction model is optimised by adding RepeatVector and TimeDistributed layers, which the authors argue differentiates it from other optimised GRU models in terms of model hierarchy and multidimensional input handling. The method is validated on daily PV power generation data from Xuhui District, Shanghai, China, and additionally on DKASC (Alice Springs, Australia) data to compare short-term forecasting against medium- and long-term forecasting horizons. The authors position the contribution as the combination of smoothing-based data processing, Random Forest feature selection and an improved GRU architecture, which none of the compared reference models jointly provide.</t>
+          <t>Summary: The accurate prediction of photovoltaic (PV) energy production is a crucial task to optimise the integration of solar energy into the power grid and maximise the benefit of renewable source trading in the energy market. This paper systematically and quantitatively analyses the literature by comparing different machine learning techniques and the impact of different meteorological forecast providers. The methodology consists of an irradiance model coupled with a meteorological provider; this combination removes the constraint of a local irradiance measurement. The result is a Transformer Neural Network architecture, trained and tested using OpenMeteo data, whose performance is superior to other combinations, providing a MAE of 1.22 kW (0.95%), and a MAPE of 2.21%. The implications of our study suggest that adopting a comprehensive approach, integrating local weather data, modelled irradiance, and PV plant configuration data, can significantly improve the accuracy of PV power forecasting, thus contributing to more effective technological and economic integration. • This work focuses on PV power output forecasting with ML. • PV power forecasting with ML models on various datasets to evaluate their efficacy. • Transformer model shows the lowest errors when forecasting PV power production.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Compares five smoothing techniques head-to-head, adds RF feature selection, and augments GRU with RepeatVector/TimeDistributed layers; tests the method on a second, climatically distinct dataset.)</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Systematically quantifies the effect of the meteorological forecast provider on PV forecasting accuracy, decoupling accuracy from model architecture.)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Photovoltaic system; Term (time); Random forest; Smoothing; Econometrics</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.energy.2022.124661</t>
+          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Photovoltaic system; Transformer; Computer science; Electrical engineering; Reliability engineering</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.egyai.2024.100444</t>
         </is>
       </c>
     </row>
@@ -1373,47 +1397,47 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Lei et al. (2026)</t>
+          <t>Sima et al. (2025)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Mingze Lei; Tao Chen; Yao Xiao; Caixia Yang; Worawat Sa-Ngiamvibool; Supannika Wattana; Buncha Wattana</t>
+          <t>Qi Sima; Xinze Zhang; Siyue Yang; Liang Shen; Yukun Bao</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2026-04-02 (online)</t>
+          <t>2025-6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MDPI AG / Energies</t>
+          <t>Elsevier BV / Energy Conversion and Management</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Short-Term Photovoltaic Power Forecasting Based on CNN–LSTM–Attention Mechanism</t>
+          <t>Multi-scale fused Graph Convolutional Network for multi-site photovoltaic power forecasting</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Summary: Accurate short-term photovoltaic (PV) power forecasting is crucial for maintaining grid stability. However, existing hybrid deep learning models suffer from inherent limitations owing to static feature-weighting mechanisms, often displaying significant phase lag and peak clipping under severe meteorological fluctuations. To address this, in this study, we adopt a hybrid CNN–LSTM–Attention forecasting framework incorporating an SE-based attention strategy. Field validation at a 150 kW PV power plant in Ningxia, China, demonstrated that the adopted model achieved a Root Mean Square Error (RMSE) convergence of 2.157 kW. Notably, this represented a 41.92% reduction in error compared to the standard LSTM benchmark and a further 16.46% improvement over the suboptimal CNN-LSTM baseline, explicitly confirming the specific contribution of the SE-based attention mechanism. Moreover, multi-weather evaluations and ablation studies confirm the framework’s robustness. Dynamic Time Warping (DTW) and Diebold–Mariano (DM) tests establish its statistical superiority and the reduction in phase lag against baselines. Residual analysis reveals a leptokurtic distribution with white noise properties, confirming the reduction in systematic bias. Consequently, this high-fidelity tracking allows precise minute-level ramping detection and decreases spinning reserve demands in practical power dispatch.</t>
+          <t>Summary: In the context of the large-scale development of photovoltaic systems, the demand for multi-site PV power prediction is on the rise. Unlike site-by-site modeling, multi-site PV power prediction not only helps to reduce modeling costs but also has significant potential to enhance the prediction accuracy of individual sites. The diverse variations and fluctuations in inter-site correlations at different time scales present challenges for effective spatiotemporal mining among multiple sites. As solar azimuth and altitude evolve cyclically on hourly scales, sites of similar latitude show similar fluctuations, whereas sudden changes in irradiance due to cloud movement on minute scales lead to a decrease in the power correlation between sites. This study proposes the Multi-Scale Fused Graph Convolutional Neural Network (MSF-GCN), comprising multi-scale construction, a Multi-Graph Convolution block (MGCN), a Decomposed-Bidirectional-Fusion block (DBF) and multiple independent predictors. Raw data are processed by average downsampling to construct multi-scale observations. The MGCN block extracts spatial features from diverse graphs derived from geographic topology and from self-learning graphs with learnable adjacency matrices oriented to information at different time scales. The MLP-based DBF block decomposes data into seasonal and trend components along the time dimension and integrates them across scales through bottom-up and top-down MLPs, propagating fine-grained patterns from smaller to larger scales and distilling coarse context back to refine finer representations. Multiple independent predictors with identical structure but unshared weights project and combine the extracted features. Ablation experiments are used to elucidate the role of each block, and the authors report consistent accuracy improvements over existing methods with favourable run-time efficiency.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: One of very few papers in this corpus that applies a Diebold-Mariano test and analyses residual distributions to support a superiority claim, and quantifies the attention module's marginal contribution.)</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Formalises the observation that inter-site correlation strength is time-scale dependent (geographic at hourly scales, decorrelated at minute scales) and builds a multi-scale graph architecture around it, with per-block ablation.)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>CNN-LSTM; hybrid deep learning; attention mechanism; wavelet transform; multi-source data fusion; Benchmark (surveying); Residual; Photovoltaic system; Reduction (mathematics); Power (physics)</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/en19071747</t>
+          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Photovoltaic system; Graph; Scale (ratio); Computer science; Environmental science</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.enconman.2025.119773</t>
         </is>
       </c>
     </row>
@@ -1423,47 +1447,47 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Kim et al. (2024)</t>
+          <t>Cantillo-Luna et al. (2023)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Jimin Kim; Josue Obregon; Hoonseok Park; Jae-Yoon Jung</t>
+          <t>Sergio Cantillo-Luna; Ricardo Moreno-Chuquen; David Celeita; George Anders</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2024-8</t>
+          <t>2023-05-15 (online)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Renewable and Sustainable Energy Reviews</t>
+          <t>MDPI AG / Energies</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Multi-step photovoltaic power forecasting using transformer and recurrent neural networks</t>
+          <t>Deep and Machine Learning Models to Forecast Photovoltaic Power Generation</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Summary: Affordable and clean energy is an important UN sustainable development goal. Solar energy is more difficult to control than fossil fuels, highlighting the need for accurate solar power forecasts. This study develops three variants of the transformer networks, called PVTransNet, for a multi-step day-ahead photovoltaic power forecasting. The transformer networks use historical solar power generation, weather observation, weather forecast and solar geometry data as input to effectively predict next-day hourly power generation. In particular, the third variant model combines long short-term memory (LSTM) to transformer networks to supplement weather forecasts from the weather station. The combined model, PVTransNet-EDR, outperformed individual LSTM and other transformer models in the experiments conducted on data from two photovoltaic power plants. The model performed 48.3 % better, in mean absolute error, than simple LSTM in the power forecasting. Accurate solar power forecasting model is expected to be utilized for efficient energy storage and microgrid management, effective energy supply policy, and optimal plant location selection.</t>
+          <t>Summary: The integration and management of distributed energy resources (DERs), including residential photovoltaic (PV) production, coupled with the widespread use of enabling technologies such as artificial intelligence, have led to the emergence of new tools, market models, and business opportunities. The accurate forecasting of these resources has become crucial to decision making, despite data availability and reliability issues in some parts of the world. To address these challenges, this paper proposes a deep and machine learning-based methodology for PV power forecasting, which includes XGBoost, random forest, support vector regressor, multi-layer perceptron, and LSTM-based tuned models, and introduces the ConvLSTM1D approach for this task. These models were evaluated on the univariate time-series prediction of low-volume residential PV production data across various forecast horizons. The proposed benchmarking and analysis approach considers technical and economic impacts, which can provide valuable insights for decision-making tools with these resources. The results indicate that the random forest and ConvLSTM1D model approaches yielded the most accurate forecasting performance, as demonstrated by the lowest RMSE, MAPE, and MAE across the different scenarios proposed.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Shows that combining an LSTM encoder with a transformer, and adding solar geometry alongside weather data, yields large day-ahead gains over plain LSTM on two plants.)</t>
+          <t>Summary: The results indicate that the random forest and ConvLSTM1D model approaches yielded the most accurate forecasting performance, as demonstrated by the lowest RMSE, MAPE, and MAE across the different scenarios proposed.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Photovoltaic system; Artificial neural network; Transformer; Computer science; Engineering</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.rser.2024.114479</t>
+          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Random forest; Computer science; Benchmarking; Photovoltaic system; Perceptron</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/en16104097</t>
         </is>
       </c>
     </row>
@@ -1473,47 +1497,47 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Piantadosi et al. (2024)</t>
+          <t>Radzi et al. (2026)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Gabriele Piantadosi; Sofia Dutto; Antonio Galli; Saverio De Vito; Carlo Sansone; Girolamo Di Francia</t>
+          <t>Putri Nor Liyana Mohamad Radzi; Saad Mekhilef; Noraisyah Mohamed Shah; Muhammad Naveed Akhter; Mehdi Seyedmahmoudian; Yasser Almalaq; Addy Wahyudie</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2026-1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy and AI</t>
+          <t>Elsevier BV / Energy Conversion and Management: X</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Photovoltaic power forecasting: A Transformer based framework</t>
+          <t>Enhancing short-term solar power forecasting using a hybrid deep learning approach and a comparative analysis of machine learning models</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Summary: The accurate prediction of photovoltaic (PV) energy production is a crucial task to optimise the integration of solar energy into the power grid and maximise the benefit of renewable source trading in the energy market. This paper systematically and quantitatively analyses the literature by comparing different machine learning techniques and the impact of different meteorological forecast providers. The methodology consists of an irradiance model coupled with a meteorological provider; this combination removes the constraint of a local irradiance measurement. The result is a Transformer Neural Network architecture, trained and tested using OpenMeteo data, whose performance is superior to other combinations, providing a MAE of 1.22 kW (0.95%), and a MAPE of 2.21%. The implications of our study suggest that adopting a comprehensive approach, integrating local weather data, modelled irradiance, and PV plant configuration data, can significantly improve the accuracy of PV power forecasting, thus contributing to more effective technological and economic integration. • This work focuses on PV power output forecasting with ML. • PV power forecasting with ML models on various datasets to evaluate their efficacy. • Transformer model shows the lowest errors when forecasting PV power production.</t>
+          <t>Summary: • Develop a GRU–LSTM hybrid model for hour-ahead solar power forecasting. • Introduce a sequential hybrid framework with recursive temporal forecasting. • Consider two PV types: Poly-crystalline (Array 1) and Mono-crystalline (Array 2) • Compare standalone and hybrid ML models using GRU as the core connection. • Array 1 achieves best results with RMSE 28.55 W, MAE 19.43 W, and R 2 0.9961. Photovoltaic (PV) energy is essential for sustainable urban infrastructure but remains constrained by weather-induced variability, particularly under tropical climatic conditions. Accurate solar power forecasting is critical for grid stability and resilient energy systems. This study proposes a hybrid deep learning model that integrates Gated Recurrent Unit (GRU) and Long Short-Term Memory (LSTM) architectures within a sequential configuration designed to enhance temporal feature learning. In the proposed model, the GRU functions as the primary connector, extracting short-term temporal dependencies and transferring them to the LSTM layer for long-term contextual representation. The model employs a recursive forecasting strategy using time-indexed data to effectively capture the nonlinear dynamics of PV power generation. Two PV technologies, Poly-crystalline (Array 1) and Mono-crystalline (Array 2), are evaluated. Model accuracy is assessed using statistical metrics supported by residual analyses to examine correlations between observed and predicted outputs. The proposed hybrid demonstrates superior predictive capability, achieving root mean square error (RMSE), mean absolute error (MAE), and coefficient of determination (R 2 ) values of 18.55 W, 19.43 W, and 0.9961 for Array 1, and 14.82 W, 11.85 W, and 0.9952 for Array 2, respectively. Incorporating GRU as the primary hybrid component yields performance improvements of 13.97% (RMSE) and 16.03% (MAE) for Array 1, and 16.41% (RMSE) and 12.44% (MAE) for Array 2. Beyond these quantitative enhancements, the study explores the functional advantages and limitations of employing GRU as the dominant connection module. Overall, the findings confirm that the proposed model, supported by recursive forecasting, provides a scalable solution for improving PV power prediction in variable tropical environments.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Systematically quantifies the effect of the meteorological forecast provider on PV forecasting accuracy, decoupling accuracy from model architecture.)</t>
+          <t>Summary: Overall, the findings confirm that the proposed model, supported by recursive forecasting, provides a scalable solution for improving PV power prediction in variable tropical environments.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Photovoltaic system; Transformer; Computer science; Electrical engineering; Reliability engineering</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.egyai.2024.100444</t>
+          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Mean squared error; Photovoltaic system; Residual; Deep learning; Hybrid system</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.ecmx.2025.101431</t>
         </is>
       </c>
     </row>
@@ -1523,47 +1547,47 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sima et al. (2025)</t>
+          <t>Luo et al. (2021)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Qi Sima; Xinze Zhang; Siyue Yang; Liang Shen; Yukun Bao</t>
+          <t>Xing Luo; Dongxiao Zhang; Xu Zhu</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2025-6</t>
+          <t>2021-6</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy Conversion and Management</t>
+          <t>Elsevier BV / Energy</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Multi-scale fused Graph Convolutional Network for multi-site photovoltaic power forecasting</t>
+          <t>Deep learning based forecasting of photovoltaic power generation by incorporating domain knowledge</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Summary: In the context of the large-scale development of photovoltaic systems, the demand for multi-site PV power prediction is on the rise. Unlike site-by-site modeling, multi-site PV power prediction not only helps to reduce modeling costs but also has significant potential to enhance the prediction accuracy of individual sites. The diverse variations and fluctuations in inter-site correlations at different time scales present challenges for effective spatiotemporal mining among multiple sites. As solar azimuth and altitude evolve cyclically on hourly scales, sites of similar latitude show similar fluctuations, whereas sudden changes in irradiance due to cloud movement on minute scales lead to a decrease in the power correlation between sites. This study proposes the Multi-Scale Fused Graph Convolutional Neural Network (MSF-GCN), comprising multi-scale construction, a Multi-Graph Convolution block (MGCN), a Decomposed-Bidirectional-Fusion block (DBF) and multiple independent predictors. Raw data are processed by average downsampling to construct multi-scale observations. The MGCN block extracts spatial features from diverse graphs derived from geographic topology and from self-learning graphs with learnable adjacency matrices oriented to information at different time scales. The MLP-based DBF block decomposes data into seasonal and trend components along the time dimension and integrates them across scales through bottom-up and top-down MLPs, propagating fine-grained patterns from smaller to larger scales and distilling coarse context back to refine finer representations. Multiple independent predictors with identical structure but unshared weights project and combine the extracted features. Ablation experiments are used to elucidate the role of each block, and the authors report consistent accuracy improvements over existing methods with favourable run-time efficiency.</t>
+          <t>Summary: Solar energy constitutes an effective supplement to traditional energy sources. However, photovoltaic power generation (PVPG) is strongly weather-dependent, and thus highly intermittent. High-precision forecasting of PVPG forms the basis of the production, transmission, and distribution of electricity, ensuring the stability and reliability of power systems. In this work, we propose a deep learning based framework for accurate PVPG forecasting. In particular, taking advantage of the long short-term memory (LSTM) network in solving sequential-data based regression problems, this paper considers the specific domain knowledge of PV and proposes a physics-constrained LSTM (PC-LSTM) to forecast the hourly day-ahead PVPG. It aims to overcome the shortcoming of recent machine learning algorithms that are applied based only on massive data, and thus easily producing unreasonable forecasts. Real-life PV datasets are adopted to evaluate the feasibility and effectiveness of the models. Sensitivity analysis is conducted for the selection of input feature variables based on a two-stage hybrid method. The results indicate that the proposed PC-LSTM model possesses stronger forecasting capability than the standard LSTM model. It is more robust against PVPG forecasting, and more suitable for PVPG forecasting with sparse data in practice. The PC-LSTM model also demonstrates superior performance with higher accuracy of PVPG forecasting compared to conventional machine learning and statistical methods.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Formalises the observation that inter-site correlation strength is time-scale dependent (geographic at hourly scales, decorrelated at minute scales) and builds a multi-scale graph architecture around it, with per-block ablation.)</t>
+          <t>Summary: The results indicate that the proposed PC-LSTM model possesses stronger forecasting capability than the standard LSTM model.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Photovoltaic system; Graph; Scale (ratio); Computer science; Environmental science</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.enconman.2025.119773</t>
+          <t>physics-informed; domain knowledge; solar position; physically constrained forecasting; Computer science; Photovoltaic system; Artificial intelligence; Reliability (semiconductor); Machine learning</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.energy.2021.120240</t>
         </is>
       </c>
     </row>
@@ -1573,47 +1597,47 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Cantillo-Luna et al. (2023)</t>
+          <t>Mondal et al. (2024)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Sergio Cantillo-Luna; Ricardo Moreno-Chuquen; David Celeita; George Anders</t>
+          <t>Rakesh Mondal; Surajit Kr Roy; Chandan Giri</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2023-05-15 (online)</t>
+          <t>2024-9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>MDPI AG / Energies</t>
+          <t>Elsevier BV / Energy</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Deep and Machine Learning Models to Forecast Photovoltaic Power Generation</t>
+          <t>Solar power forecasting using domain knowledge</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Summary: The integration and management of distributed energy resources (DERs), including residential photovoltaic (PV) production, coupled with the widespread use of enabling technologies such as artificial intelligence, have led to the emergence of new tools, market models, and business opportunities. The accurate forecasting of these resources has become crucial to decision making, despite data availability and reliability issues in some parts of the world. To address these challenges, this paper proposes a deep and machine learning-based methodology for PV power forecasting, which includes XGBoost, random forest, support vector regressor, multi-layer perceptron, and LSTM-based tuned models, and introduces the ConvLSTM1D approach for this task. These models were evaluated on the univariate time-series prediction of low-volume residential PV production data across various forecast horizons. The proposed benchmarking and analysis approach considers technical and economic impacts, which can provide valuable insights for decision-making tools with these resources. The results indicate that the random forest and ConvLSTM1D model approaches yielded the most accurate forecasting performance, as demonstrated by the lowest RMSE, MAPE, and MAE across the different scenarios proposed.</t>
+          <t>Summary: Integrating renewable energy into the existing energy market is crucial. Solar power forecasting is essential since it depends on weather parameters and must integrate with the central grid to use the produced solar power effectively. Contemporary studies indicate that machine learning has the potential to predict the future generation of solar energy based on past data. This research demonstrates a broad range of solar power forecasting, combining one-year time series solar power generation data, solar panel physical features, and weather information with the help of machine learning and deep learning tools with domain knowledge. The dataset is curated and preprocessed. The authors propose a deep learning ensemble model based on Bi-LSTM. The proposed model can forecast well regardless of geographical position and is able to predict both short-term and long-term time horizons. The results are compared with the existing dataset and multiple standard deep learning models, and the proposed model is found to produce better performance than traditional models. The model is also validated using different solar plants in Durgapur, India, and for long-term forecasting it outperforms the base model.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Summary: The results indicate that the random forest and ConvLSTM1D model approaches yielded the most accurate forecasting performance, as demonstrated by the lowest RMSE, MAPE, and MAE across the different scenarios proposed.</t>
+          <t>Summary: The results are compared with the existing dataset and multiple standard deep learning models, and the proposed model is found to produce better performance than traditional models.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Random forest; Computer science; Benchmarking; Photovoltaic system; Perceptron</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/en16104097</t>
+          <t>physics-informed; domain knowledge; solar position; physically constrained forecasting; Domain (mathematical analysis); Power (physics); Solar power; Computer science; Environmental science</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.energy.2024.131709</t>
         </is>
       </c>
     </row>
@@ -1623,47 +1647,47 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Radzi et al. (2026)</t>
+          <t>Singh et al. (2026)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Putri Nor Liyana Mohamad Radzi; Saad Mekhilef; Noraisyah Mohamed Shah; Muhammad Naveed Akhter; Mehdi Seyedmahmoudian; Yasser Almalaq; Addy Wahyudie</t>
+          <t>Praveen Kumar Singh; Amit Saraswat; Yogesh Gupta</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2026-1</t>
+          <t>2026-4</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy Conversion and Management: X</t>
+          <t>Elsevier BV / Next Energy</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Enhancing short-term solar power forecasting using a hybrid deep learning approach and a comparative analysis of machine learning models</t>
+          <t>Deep learning prediction models for short-term solar photovoltaic power generation forecasting</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Summary: • Develop a GRU–LSTM hybrid model for hour-ahead solar power forecasting. • Introduce a sequential hybrid framework with recursive temporal forecasting. • Consider two PV types: Poly-crystalline (Array 1) and Mono-crystalline (Array 2) • Compare standalone and hybrid ML models using GRU as the core connection. • Array 1 achieves best results with RMSE 28.55 W, MAE 19.43 W, and R 2 0.9961. Photovoltaic (PV) energy is essential for sustainable urban infrastructure but remains constrained by weather-induced variability, particularly under tropical climatic conditions. Accurate solar power forecasting is critical for grid stability and resilient energy systems. This study proposes a hybrid deep learning model that integrates Gated Recurrent Unit (GRU) and Long Short-Term Memory (LSTM) architectures within a sequential configuration designed to enhance temporal feature learning. In the proposed model, the GRU functions as the primary connector, extracting short-term temporal dependencies and transferring them to the LSTM layer for long-term contextual representation. The model employs a recursive forecasting strategy using time-indexed data to effectively capture the nonlinear dynamics of PV power generation. Two PV technologies, Poly-crystalline (Array 1) and Mono-crystalline (Array 2), are evaluated. Model accuracy is assessed using statistical metrics supported by residual analyses to examine correlations between observed and predicted outputs. The proposed hybrid demonstrates superior predictive capability, achieving root mean square error (RMSE), mean absolute error (MAE), and coefficient of determination (R 2 ) values of 18.55 W, 19.43 W, and 0.9961 for Array 1, and 14.82 W, 11.85 W, and 0.9952 for Array 2, respectively. Incorporating GRU as the primary hybrid component yields performance improvements of 13.97% (RMSE) and 16.03% (MAE) for Array 1, and 16.41% (RMSE) and 12.44% (MAE) for Array 2. Beyond these quantitative enhancements, the study explores the functional advantages and limitations of employing GRU as the dominant connection module. Overall, the findings confirm that the proposed model, supported by recursive forecasting, provides a scalable solution for improving PV power prediction in variable tropical environments.</t>
+          <t>Summary: The increasing concerns about the environmental impact of fossil fuels have emphasized the importance of clean solar energy, which offers a pollution-free alternative for meeting growing energy needs. However, the accurate prediction of solar photovoltaic (SPV) based power generation is a very challenging task because of its inherent variability and uncertainty. To address this challenging problem, this paper applies several machine-learning, deep-learning, and their hybrid models such as: One-Dimensional Convolutional Neural Network (1D CNN), Bi-Directional Long Short-Term Memory (Bi-LSTM), Stacked LSTM, Artificial Neural Network (ANN), Linear Regression (LR), Support Vector Regression (SVR), XGBoost, and a hybrid CNN-LSTM model. These models are examined and compared on four different data sequences of DKASC Alice Springs dataset. The prediction performances of all these models are evaluated based on various error metrics: MAE (mean absolute error), explained variance, RMSE (root mean square error), R², and sMAPE (symmetric mean absolute percentage error). The simulation results demonstrates that Stacked LSTM model outperforms all other benchmark forecasting models and able to obtains average values of performance metrics i.e. MAE of 1.1157, RMSE of 2.3408, an Explained Variance of 0.8998, R² of 0.9004, and sMAPE of 1.1795 as evaluated across all four different data sequences. Moreover, a comprehensive statistical analysis, using Diebold Mariano Test and boxplots, confirms the further superiority of Stacked-LSTM model to efficiently address inherent uncertainty of solar power generation.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Summary: Overall, the findings confirm that the proposed model, supported by recursive forecasting, provides a scalable solution for improving PV power prediction in variable tropical environments.</t>
+          <t>Summary: The simulation results demonstrates that Stacked LSTM model outperforms all other benchmark forecasting models and able to obtains average values of performance metrics i.e.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>transformer; iTransformer; graph convolutional network; encoder-decoder; advanced time-series architecture; Mean squared error; Photovoltaic system; Residual; Deep learning; Hybrid system</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ecmx.2025.101431</t>
+          <t>physics-informed; domain knowledge; solar position; physically constrained forecasting; Mean squared error; Artificial neural network; Benchmark (surveying); Photovoltaic system; Linear regression</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.nxener.2026.100531</t>
         </is>
       </c>
     </row>
@@ -1673,47 +1697,47 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Luo et al. (2021)</t>
+          <t>Li et al. (2026)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Xing Luo; Dongxiao Zhang; Xu Zhu</t>
+          <t>Dan Li; Yawen Zhen; Qihong Pan; Senzhe Lei; Xiangyang Liang; Minghan Qu; Zhaoxi Lin; Liu Chao; Bin Yao</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2021-6</t>
+          <t>2026-4-14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy</t>
+          <t>Bentham Science Publishers Ltd. / Recent Advances in Electrical &amp;amp; Electronic Engineering (Formerly Recent Patents on Electrical &amp;amp; Electronic Engineering)</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Deep learning based forecasting of photovoltaic power generation by incorporating domain knowledge</t>
+          <t>Day-Ahead Probabilistic Photovoltaic Power Forecasting based on Deep Feature Enhancement and Bidirectional Temporal Modeling</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Summary: Solar energy constitutes an effective supplement to traditional energy sources. However, photovoltaic power generation (PVPG) is strongly weather-dependent, and thus highly intermittent. High-precision forecasting of PVPG forms the basis of the production, transmission, and distribution of electricity, ensuring the stability and reliability of power systems. In this work, we propose a deep learning based framework for accurate PVPG forecasting. In particular, taking advantage of the long short-term memory (LSTM) network in solving sequential-data based regression problems, this paper considers the specific domain knowledge of PV and proposes a physics-constrained LSTM (PC-LSTM) to forecast the hourly day-ahead PVPG. It aims to overcome the shortcoming of recent machine learning algorithms that are applied based only on massive data, and thus easily producing unreasonable forecasts. Real-life PV datasets are adopted to evaluate the feasibility and effectiveness of the models. Sensitivity analysis is conducted for the selection of input feature variables based on a two-stage hybrid method. The results indicate that the proposed PC-LSTM model possesses stronger forecasting capability than the standard LSTM model. It is more robust against PVPG forecasting, and more suitable for PVPG forecasting with sparse data in practice. The PC-LSTM model also demonstrates superior performance with higher accuracy of PVPG forecasting compared to conventional machine learning and statistical methods.</t>
+          <t>Summary: Introduction: The integration of photovoltaic (PV) power into the grid is challenged by the inherent uncertainty of PV power. This study aims to develop a probabilistic forecasting model for day-ahead PV power that effectively captures temporal dependencies while ensuring mathematically sound prediction intervals. Methods: This study develops a hybrid model integrating an Auto-Encoder (AE), a Bidirectional Long Short-Term Memory (BiLSTM) network, and Quantile Regression (QR). First, the AE was employed to learn a dense latent representation of input features, which was then concatenated with the original features. Next, the BiLSTM processed these features to capture bidirectional temporal dependencies. Finally, an Incremental Monotonicity Enforcement (IME) mechanism within the QR layer generated non-crossing prediction intervals by predicting a baseline value and nonnegative increments. Results: Experiments on a real-world PV dataset demonstrated that the proposed model outperforms several baseline models in day-ahead probabilistic forecasting. The generated prediction intervals were more reliable, sharper, and mathematically coherent. Discussion: These results suggest that integrating deep feature learning with monotonicity-enforced quantile regression effectively addresses the quantile crossing problem. The improved interval reliability has practical implications for grid scheduling. A limitation is the model's reliance on historical data quality. Conclusion: The proposed AE-BiLSTM-QR model with the IME mechanism provides an effective and reliable solution for day-ahead PV power probabilistic forecasting. It innovatively integrates deep feature learning, bidirectional temporal modeling, and structurally enforced quantile monotonicity, offering a reliable technical approach for the grid integration of solar energy.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Summary: The results indicate that the proposed PC-LSTM model possesses stronger forecasting capability than the standard LSTM model.</t>
+          <t>Summary: Results: Experiments on a real-world PV dataset demonstrated that the proposed model outperforms several baseline models in day-ahead probabilistic forecasting.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>physics-informed; domain knowledge; solar position; physically constrained forecasting; Computer science; Photovoltaic system; Artificial intelligence; Reliability (semiconductor); Machine learning</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.energy.2021.120240</t>
+          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Probabilistic logic; Probabilistic forecasting; Feature (linguistics); Quantile regression; Photovoltaic system</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.2174/0123520965458194260410052152</t>
         </is>
       </c>
     </row>
@@ -1723,47 +1747,47 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Mondal et al. (2024)</t>
+          <t>Feng et al. (2025)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Rakesh Mondal; Surajit Kr Roy; Chandan Giri</t>
+          <t>Haohao Feng; Yujing Shi; Mifeng Ren; Wenjie Zhang; Jianhua Zhang; Yusheng Zhao</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2024-9</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Energy</t>
+          <t>Elsevier BV / Solar Energy</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Solar power forecasting using domain knowledge</t>
+          <t>Distribution-Free photovoltaic power probability density forecasting based on hybrid deep learning</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Summary: Integrating renewable energy into the existing energy market is crucial. Solar power forecasting is essential since it depends on weather parameters and must integrate with the central grid to use the produced solar power effectively. Contemporary studies indicate that machine learning has the potential to predict the future generation of solar energy based on past data. This research demonstrates a broad range of solar power forecasting, combining one-year time series solar power generation data, solar panel physical features, and weather information with the help of machine learning and deep learning tools with domain knowledge. The dataset is curated and preprocessed. The authors propose a deep learning ensemble model based on Bi-LSTM. The proposed model can forecast well regardless of geographical position and is able to predict both short-term and long-term time horizons. The results are compared with the existing dataset and multiple standard deep learning models, and the proposed model is found to produce better performance than traditional models. The model is also validated using different solar plants in Durgapur, India, and for long-term forecasting it outperforms the base model.</t>
+          <t>Summary: Photovoltaic (PV) power generation exhibits high randomness, and probabilistic forecasting can effectively quantify its uncertainty. However, existing probabilistic forecasting models are constrained by prior distribution assumptions and incomplete representation, which weakens their ability to model the true data generation process, leading to suboptimal prediction results. To address this, this study proposes a distribution-free probabilistic density forecasting model for PV power based on B-spline-iTransformer-Multi-Head Cross Attention (BS-iMCFormer). The core of the model lies in: using B-splines to fit the probability density function (PDF), which is obtained through kernel density estimation (KDE), extracting control points that represent the characteristics of the PDF to construct the coefficient vector and transforming the PDF prediction into the prediction of the coefficient vector; utilizing iMCFormer to integrate meteorological, power, and coefficient vector cross-modal associations to achieve enhanced feature reconstruction; and employing B-spline interpolation to obtain the predicted PDF from the predicted coefficient vector, thus avoiding the constraints of parametric distribution assumptions and discrete representation. The study conducts experiments using data from a PV station in Hebei Province, China. The results show that the proposed model's predicted PDF significantly outperforms all comparison models in terms of visual overlap and statistical consistency with the real data's kernel density estimate. The core metric of distribution difference, KL divergence, is reduced by 54.82%, while MAE and RMSE decrease by 68.93% and 69.42%, respectively, and the correlation metric R2 improves by 6.76%.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Summary: The results are compared with the existing dataset and multiple standard deep learning models, and the proposed model is found to produce better performance than traditional models.</t>
+          <t>Summary: The results show that the proposed model's predicted PDF significantly outperforms all comparison models in terms of visual overlap and statistical consistency with the real data's kernel density estimate.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>physics-informed; domain knowledge; solar position; physically constrained forecasting; Domain (mathematical analysis); Power (physics); Solar power; Computer science; Environmental science</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.energy.2024.131709</t>
+          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Probability density function; Kernel density estimation; Probabilistic logic; Photovoltaic system; Probabilistic forecasting</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.solener.2025.113769</t>
         </is>
       </c>
     </row>
@@ -1773,47 +1797,47 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Singh et al. (2026)</t>
+          <t>Ozdemir et al. (2024)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Praveen Kumar Singh; Amit Saraswat; Yogesh Gupta</t>
+          <t>Gokcen Ozdemir; Murat Kuzlu; Ferhat Ozgur Catak</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2026-4</t>
+          <t>2024-12-28 (online); 2025-6 (issue)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Next Energy</t>
+          <t>Springer Science and Business Media LLC / Electrical Engineering</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Deep learning prediction models for short-term solar photovoltaic power generation forecasting</t>
+          <t>Machine learning insights into forecasting solar power generation with explainable AI</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Summary: The increasing concerns about the environmental impact of fossil fuels have emphasized the importance of clean solar energy, which offers a pollution-free alternative for meeting growing energy needs. However, the accurate prediction of solar photovoltaic (SPV) based power generation is a very challenging task because of its inherent variability and uncertainty. To address this challenging problem, this paper applies several machine-learning, deep-learning, and their hybrid models such as: One-Dimensional Convolutional Neural Network (1D CNN), Bi-Directional Long Short-Term Memory (Bi-LSTM), Stacked LSTM, Artificial Neural Network (ANN), Linear Regression (LR), Support Vector Regression (SVR), XGBoost, and a hybrid CNN-LSTM model. These models are examined and compared on four different data sequences of DKASC Alice Springs dataset. The prediction performances of all these models are evaluated based on various error metrics: MAE (mean absolute error), explained variance, RMSE (root mean square error), R², and sMAPE (symmetric mean absolute percentage error). The simulation results demonstrates that Stacked LSTM model outperforms all other benchmark forecasting models and able to obtains average values of performance metrics i.e. MAE of 1.1157, RMSE of 2.3408, an Explained Variance of 0.8998, R² of 0.9004, and sMAPE of 1.1795 as evaluated across all four different data sequences. Moreover, a comprehensive statistical analysis, using Diebold Mariano Test and boxplots, confirms the further superiority of Stacked-LSTM model to efficiently address inherent uncertainty of solar power generation.</t>
+          <t>Summary: Machine learning (ML) algorithms can provide highly accurate predictions, but their complexity often makes them difficult to interpret due to their black-box nature. Combining ML and Explainable Artificial Intelligence (XAI) makes these models more transparent and enables users to understand the key factors behind the predictions. This paper presents a variety of ML approaches combined with XAI to predict solar power generation, aiming to optimize energy management in smart grids. For this purpose, five different ML algorithms, namely Random Forest, Gradient Boosting, eXtreme Gradient Boosting, Light Gradient Boosting Machine, and Decision Three, and three different XAI models, namely Shapley Additive Explanation, Local Interpretable Model-agnostic Explanations, and Permutation Feature Importance were investigated. According to the findings, the Light Gradient Boosting Machine achieved the best performance, showing the lowest root mean squared error of 0.088, mean squared error of 0.007749, mean absolute error of 0.052896, and the highest R-squared value of 0.842645. XAI techniques provided detailed, actionable insights into the model behavior, helping to identify key features influencing predictions. While Permutation Feature Importance identified key features, Shapley Additive Explanations showed how this feature interacts with others, and Local Interpretable Model-Agnostic Explanations clarified individual predictions. This research provides the most comprehensive understanding in the literature on feature impact and model interpretability for solar power forecasting and contributes to sustainable energy applications by combining ML prediction with XAI interpretability for effective smart grid integration.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Summary: The simulation results demonstrates that Stacked LSTM model outperforms all other benchmark forecasting models and able to obtains average values of performance metrics i.e.</t>
+          <t>Summary: According to the findings, the Light Gradient Boosting Machine achieved the best performance, showing the lowest root mean squared error of 0.088, mean squared error of 0.007749, mean absolute error of 0.052896, and the highest R-squared value of 0.842645.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>physics-informed; domain knowledge; solar position; physically constrained forecasting; Mean squared error; Artificial neural network; Benchmark (surveying); Photovoltaic system; Linear regression</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.nxener.2026.100531</t>
+          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Artificial intelligence; Computer science; Power (physics); Solar power; Machine learning</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00202-024-02933-4</t>
         </is>
       </c>
     </row>
@@ -1823,47 +1847,47 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Li et al. (2026)</t>
+          <t>Zhang et al. (2026)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Dan Li; Yawen Zhen; Qihong Pan; Senzhe Lei; Xiangyang Liang; Minghan Qu; Zhaoxi Lin; Liu Chao; Bin Yao</t>
+          <t>Yujia Zhang; Yuzhou Zhang; Zhixiang Dai; Rita Zhang</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2026-4-14</t>
+          <t>2026-06-12 (online)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Bentham Science Publishers Ltd. / Recent Advances in Electrical &amp;amp; Electronic Engineering (Formerly Recent Patents on Electrical &amp;amp; Electronic Engineering)</t>
+          <t>Springer Science and Business Media LLC / Nature Communications</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Day-Ahead Probabilistic Photovoltaic Power Forecasting based on Deep Feature Enhancement and Bidirectional Temporal Modeling</t>
+          <t>Rethinking the use of deep learning methods for photovoltaic power forecasting</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Summary: Introduction: The integration of photovoltaic (PV) power into the grid is challenged by the inherent uncertainty of PV power. This study aims to develop a probabilistic forecasting model for day-ahead PV power that effectively captures temporal dependencies while ensuring mathematically sound prediction intervals. Methods: This study develops a hybrid model integrating an Auto-Encoder (AE), a Bidirectional Long Short-Term Memory (BiLSTM) network, and Quantile Regression (QR). First, the AE was employed to learn a dense latent representation of input features, which was then concatenated with the original features. Next, the BiLSTM processed these features to capture bidirectional temporal dependencies. Finally, an Incremental Monotonicity Enforcement (IME) mechanism within the QR layer generated non-crossing prediction intervals by predicting a baseline value and nonnegative increments. Results: Experiments on a real-world PV dataset demonstrated that the proposed model outperforms several baseline models in day-ahead probabilistic forecasting. The generated prediction intervals were more reliable, sharper, and mathematically coherent. Discussion: These results suggest that integrating deep feature learning with monotonicity-enforced quantile regression effectively addresses the quantile crossing problem. The improved interval reliability has practical implications for grid scheduling. A limitation is the model's reliance on historical data quality. Conclusion: The proposed AE-BiLSTM-QR model with the IME mechanism provides an effective and reliable solution for day-ahead PV power probabilistic forecasting. It innovatively integrates deep feature learning, bidirectional temporal modeling, and structurally enforced quantile monotonicity, offering a reliable technical approach for the grid integration of solar energy.</t>
+          <t>Summary: Accurate photovoltaic power forecasting is critical for grid stability, but remains challenged by weather uncertainties and difficulty integrating historical observations with forward-looking forecasts. We re-evaluate existing architectural choices in deep-learning models for time-series forecasting and demonstrate the importance of full encoder-decoder architectures and channel dependence modeling when both weather forecasts and historical data are available. Based on this insight, we propose Cross-Unet, a Transformer-based architecture featuring multi-scale temporal encoding, correlation-aware channel attention, and hierarchical cross-attention decoding to fuse historical generation data with weather forecasts. Evaluated on open-source datasets from four utility-scale plants in northern China and one aggregated plant in central Australia, using three types of forward-looking inputs: numerical weather prediction, satellite-derived irradiance, and AI-based weather model forecasts. Across the majority of evaluated configurations spanning five photovoltaic power stations, five forecasting horizons (4 hours to 7 days), and three forecast sources, Cross-Unet outperforms ten deep learning baselines and traditional operational benchmarks. By integrating advanced forecasting systems, such as modern AI weather models, into an end-to-end forecasting pipeline, Cross-Unet enables operational 15-minute-resolution predictions over 4-hour to 7-day horizons, supporting grid scheduling and energy trading.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Summary: Results: Experiments on a real-world PV dataset demonstrated that the proposed model outperforms several baseline models in day-ahead probabilistic forecasting.</t>
+          <t>Summary: Across the majority of evaluated configurations spanning five photovoltaic power stations, five forecasting horizons (4 hours to 7 days), and three forecast sources, Cross-Unet outperforms ten deep learning baselines and traditional operational benchmarks.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Probabilistic logic; Probabilistic forecasting; Feature (linguistics); Quantile regression; Photovoltaic system</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.2174/0123520965458194260410052152</t>
+          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Photovoltaic system; Deep learning; Fuse (electrical); Scheduling (production processes); Grid</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/s41467-026-73817-3</t>
         </is>
       </c>
     </row>
@@ -1873,47 +1897,47 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Feng et al. (2025)</t>
+          <t>Gaboitaolelwe et al. (2023)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Haohao Feng; Yujing Shi; Mifeng Ren; Wenjie Zhang; Jianhua Zhang; Yusheng Zhao</t>
+          <t>Jwaone Gaboitaolelwe; Adamu Murtala Zungeru; Abid Yahya; Caspar K. Lebekwe; Dasari Naga Vinod; Ayodeji Olalekan Salau</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Elsevier BV / Solar Energy</t>
+          <t>Institute of Electrical and Electronics Engineers (IEEE) / IEEE Access</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Distribution-Free photovoltaic power probability density forecasting based on hybrid deep learning</t>
+          <t>Machine Learning Based Solar Photovoltaic Power Forecasting: A Review and Comparison</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Summary: Photovoltaic (PV) power generation exhibits high randomness, and probabilistic forecasting can effectively quantify its uncertainty. However, existing probabilistic forecasting models are constrained by prior distribution assumptions and incomplete representation, which weakens their ability to model the true data generation process, leading to suboptimal prediction results. To address this, this study proposes a distribution-free probabilistic density forecasting model for PV power based on B-spline-iTransformer-Multi-Head Cross Attention (BS-iMCFormer). The core of the model lies in: using B-splines to fit the probability density function (PDF), which is obtained through kernel density estimation (KDE), extracting control points that represent the characteristics of the PDF to construct the coefficient vector and transforming the PDF prediction into the prediction of the coefficient vector; utilizing iMCFormer to integrate meteorological, power, and coefficient vector cross-modal associations to achieve enhanced feature reconstruction; and employing B-spline interpolation to obtain the predicted PDF from the predicted coefficient vector, thus avoiding the constraints of parametric distribution assumptions and discrete representation. The study conducts experiments using data from a PV station in Hebei Province, China. The results show that the proposed model's predicted PDF significantly outperforms all comparison models in terms of visual overlap and statistical consistency with the real data's kernel density estimate. The core metric of distribution difference, KL divergence, is reduced by 54.82%, while MAE and RMSE decrease by 68.93% and 69.42%, respectively, and the correlation metric R2 improves by 6.76%.</t>
+          <t>Summary: The growing interest in renewable energy and the falling prices of solar panels place solar electricity in a favourable position for adoption. However, the high-rate adoption of intermittent renewable energy introduces challenges and the potential to create power instability between the available power generation and the load demand. Hence, accurate solar Photovoltaic (PV) power forecasting is essential to maintain system reliability and maximize renewable energy integration. The current solar PV power forecasting approaches are an essential tool to maintain system reliability and maximize renewable energy integration. This paper presents a comprehensive and comparative review of existing Machine Learning (ML) based approaches used in PV power forecasting, focusing on short-term horizons. We provide an overview of factors affecting solar PV power forecasting and an overview of existing PV power forecasting methods in the literature, with a specific focus on ML-based models. To further enhance the comparison and provide more insights into the advancement in the area, we simulate the performance of different ML methods used in solar PV power forecasting and, finally, a discussion on the results of the work.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Summary: The results show that the proposed model's predicted PDF significantly outperforms all comparison models in terms of visual overlap and statistical consistency with the real data's kernel density estimate.</t>
+          <t>Summary: To further enhance the comparison and provide more insights into the advancement in the area, we simulate the performance of different ML methods used in solar PV power forecasting and, finally, a discussion on the results of the work.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Probability density function; Kernel density estimation; Probabilistic logic; Photovoltaic system; Probabilistic forecasting</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.solener.2025.113769</t>
+          <t>solar power forecasting review; machine learning; deep learning; survey; state of the art; Photovoltaic system; Renewable energy; Computer science; Solar power; Solar energy</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/access.2023.3270041</t>
         </is>
       </c>
     </row>
@@ -1923,47 +1947,47 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Ozdemir et al. (2024)</t>
+          <t>Khouili et al. (2025)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Gokcen Ozdemir; Murat Kuzlu; Ferhat Ozgur Catak</t>
+          <t>Oussama Khouili; Mohamed Hanine; Mohamed Louzazni; Miguel Angel López Flores; Eduardo García Villena; Imran Ashraf</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2024-12-28 (online); 2025-6 (issue)</t>
+          <t>2025-5</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Springer Science and Business Media LLC / Electrical Engineering</t>
+          <t>Elsevier BV / Energy Strategy Reviews</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Machine learning insights into forecasting solar power generation with explainable AI</t>
+          <t>Evaluating the impact of deep learning approaches on solar and photovoltaic power forecasting: A systematic review</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Summary: Machine learning (ML) algorithms can provide highly accurate predictions, but their complexity often makes them difficult to interpret due to their black-box nature. Combining ML and Explainable Artificial Intelligence (XAI) makes these models more transparent and enables users to understand the key factors behind the predictions. This paper presents a variety of ML approaches combined with XAI to predict solar power generation, aiming to optimize energy management in smart grids. For this purpose, five different ML algorithms, namely Random Forest, Gradient Boosting, eXtreme Gradient Boosting, Light Gradient Boosting Machine, and Decision Three, and three different XAI models, namely Shapley Additive Explanation, Local Interpretable Model-agnostic Explanations, and Permutation Feature Importance were investigated. According to the findings, the Light Gradient Boosting Machine achieved the best performance, showing the lowest root mean squared error of 0.088, mean squared error of 0.007749, mean absolute error of 0.052896, and the highest R-squared value of 0.842645. XAI techniques provided detailed, actionable insights into the model behavior, helping to identify key features influencing predictions. While Permutation Feature Importance identified key features, Shapley Additive Explanations showed how this feature interacts with others, and Local Interpretable Model-Agnostic Explanations clarified individual predictions. This research provides the most comprehensive understanding in the literature on feature impact and model interpretability for solar power forecasting and contributes to sustainable energy applications by combining ML prediction with XAI interpretability for effective smart grid integration.</t>
+          <t>Summary: Accurate solar and photovoltaic (PV) power forecasting is essential for optimizing grid integration, managing energy storage, and maximizing the efficiency of solar power systems. Deep learning (DL) models have shown promise in this area due to their ability to learn complex, non-linear relationships within large datasets. This study presents a systematic literature review (SLR) of deep learning applications for solar PV forecasting, addressing a gap in the existing literature, which often focuses on traditional ML or broader renewable energy applications. This review specifically aims to identify the DL architectures employed, preprocessing and feature engineering techniques used, the input features leveraged, evaluation metrics applied, and the persistent challenges in this field. Through a rigorous analysis of 26 selected papers from an initial set of 155 articles retrieved from the Web of Science database, we found that Long Short-Term Memory (LSTM) networks were the most frequently used algorithm (appearing in 32.69% of the papers), closely followed by Convolutional Neural Networks (CNNs) at 28.85%. Furthermore, Wavelet Transform (WT) was found to be the most prominent data decomposition technique, while Pearson Correlation was the most used for feature selection. We also found that ambient temperature, pressure, and humidity are the most common input features. Our systematic evaluation provides critical insights into state-of-the-art DL-based solar forecasting and identifies key areas for upcoming research. Future research should prioritize the development of more robust and interpretable models, as well as explore the integration of multi-source data to further enhance forecasting accuracy. Such advancements are crucial for the effective integration of solar energy into future power grids. • Review of DL approaches on solar and photovoltaic power forecasting. • Data preprocessing techniques and feature engineering approach for DL algorithms. • Prominent features employed for DL-based solar forecasting. • Obstacles in DL-based solar forecasting.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Summary: According to the findings, the Light Gradient Boosting Machine achieved the best performance, showing the lowest root mean squared error of 0.088, mean squared error of 0.007749, mean absolute error of 0.052896, and the highest R-squared value of 0.842645.</t>
+          <t>Summary: Through a rigorous analysis of 26 selected papers from an initial set of 155 articles retrieved from the Web of Science database, we found that Long Short-Term Memory (LSTM) networks were the most frequently used algorithm (appearing in 32.69% of the papers), closely followed by Convolutional Neural Networks (CNNs) at 28.85%.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Artificial intelligence; Computer science; Power (physics); Solar power; Machine learning</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s00202-024-02933-4</t>
+          <t>solar power forecasting review; machine learning; deep learning; survey; state of the art; Photovoltaic system; Computer science; Engineering; Electrical engineering</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.esr.2025.101735</t>
         </is>
       </c>
     </row>
@@ -1973,51 +1997,84 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Zhang et al. (2026)</t>
+          <t>Kumari &amp; Toshniwal (2021)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Yujia Zhang; Yuzhou Zhang; Zhixiang Dai; Rita Zhang</t>
+          <t>Pratima Kumari; Durga Toshniwal</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12 (online)</t>
+          <t>2021-10</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Springer Science and Business Media LLC / Nature Communications</t>
+          <t>Elsevier BV / Journal of Cleaner Production</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Rethinking the use of deep learning methods for photovoltaic power forecasting</t>
+          <t>Deep learning models for solar irradiance forecasting: A comprehensive review</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Summary: Accurate photovoltaic power forecasting is critical for grid stability, but remains challenged by weather uncertainties and difficulty integrating historical observations with forward-looking forecasts. We re-evaluate existing architectural choices in deep-learning models for time-series forecasting and demonstrate the importance of full encoder-decoder architectures and channel dependence modeling when both weather forecasts and historical data are available. Based on this insight, we propose Cross-Unet, a Transformer-based architecture featuring multi-scale temporal encoding, correlation-aware channel attention, and hierarchical cross-attention decoding to fuse historical generation data with weather forecasts. Evaluated on open-source datasets from four utility-scale plants in northern China and one aggregated plant in central Australia, using three types of forward-looking inputs: numerical weather prediction, satellite-derived irradiance, and AI-based weather model forecasts. Across the majority of evaluated configurations spanning five photovoltaic power stations, five forecasting horizons (4 hours to 7 days), and three forecast sources, Cross-Unet outperforms ten deep learning baselines and traditional operational benchmarks. By integrating advanced forecasting systems, such as modern AI weather models, into an end-to-end forecasting pipeline, Cross-Unet enables operational 15-minute-resolution predictions over 4-hour to 7-day horizons, supporting grid scheduling and energy trading.</t>
+          <t>Summary: NOT AVAILABLE - the source abstract is paywalled and was not retrievable from Crossref, OpenAlex, Semantic Scholar, the publisher landing page or any RePEc mirror. Bibliographic metadata for this record is fully verified, but no methodological or numerical claim is asserted here. Full-text consultation is required before citing this work.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Summary: Across the majority of evaluated configurations spanning five photovoltaic power stations, five forecasting horizons (4 hours to 7 days), and three forecast sources, Cross-Unet outperforms ten deep learning baselines and traditional operational benchmarks.</t>
+          <t>Summary: (No explicit conclusion sentence in the retrieved abstract. Reported outcome: Comprehensive review of deep learning models for solar irradiance forecasting (title and venue verified; 394 citations per Semantic Scholar).)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>probabilistic forecasting; prediction intervals; uncertainty quantification; explainable AI; SHAP; robustness; Photovoltaic system; Deep learning; Fuse (electrical); Scheduling (production processes); Grid</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41467-026-73817-3</t>
+          <t>solar power forecasting review; machine learning; deep learning; survey; state of the art; Solar irradiance; Irradiance; Environmental science; Meteorology; Computer science</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.jclepro.2021.128566</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J31"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2031,9 +2088,9 @@
   <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -2063,7 +2120,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Sr No</t>
         </is>
@@ -2215,25 +2272,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Gaboitaolelwe et al. (2023)</t>
+          <t>Niu et al. (2020)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PV power</t>
+          <t>PV power generation</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Short-term (day-ahead to sub-day); horizon grid not enumerated in abstract</t>
+          <t>Short-term (not enumerated in abstract)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Literature corpus plus authors' own ML simulation on PV data</t>
+          <t>Measurements from one PV power plant</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -2253,47 +2310,47 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Not enumerated in retrieved abstract; reviewed models use PV history and meteorological inputs</t>
+          <t>Meteorological and PV factors ranked by Random Forest importance</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Meteorological inputs discussed in reviewed studies (irradiance, temperature, cloud cover among them)</t>
+          <t>Meteorological factors affecting PV generation (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Classical machine learning (review + simulation)</t>
+          <t>Hybrid: feature selection + decomposition + neural network</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Multiple ML methods simulated by the authors for comparison; exact list not in abstract</t>
+          <t>RF-CEEMD-DIFPSO-BPNN (Random Forest importance, CEEMD decomposition, PSO-optimised backpropagation NN)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Persistence and previously published ML methods (as reviewed)</t>
+          <t>Contemporary ML/DL models (specific list not in abstract)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Not enumerated in retrieved abstract</t>
+          <t>Forecast accuracy metrics (specific list not enumerated in abstract)</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Not stated numerically in retrieved abstract</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Reviewed literature covers multiple conditions; no controlled regime evaluation in the review itself</t>
+          <t>Weather-type grouping used for similar-day screening (IGIVA); not a full regime evaluation</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - Random Forest importance ranking reported</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -2303,7 +2360,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No - single plant case study</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -2313,22 +2370,22 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive comparative review of ML-based short-term PV power forecasting, plus an independent simulation comparing ML methods to add evidence beyond the surveyed papers.</t>
+          <t>End-to-end hybrid pipeline coupling RF-based factor ranking, weather-type similar-day screening, CEEMD decomposition and PSO-tuned BPNN.</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>Review-level aggregation; models are compared across heterogeneous studies rather than on a common dataset and split, so cross-study numbers are not directly comparable.</t>
+          <t>Single-plant case study with a five-stage pipeline, so it is difficult to attribute gains to any single component; no ablation isolating contributions.</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Demonstrates the absence of a common-dataset benchmark; authors resort to their own simulation because the literature does not permit controlled comparison.</t>
+          <t>Composite pipelines without component-level ablation make the contribution of each stage unattributable.</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>Partial - review methodology described; reviewed studies' code not assessed</t>
+          <t>Low - many interacting stages, no code or parameter detail in abstract</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -2341,14 +2398,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>10.1109/access.2023.3270041</t>
+      <c r="AB2" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.asoc.2020.106389</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Systematic review / state of the field</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Classical / conventional machine learning</t>
         </is>
       </c>
     </row>
@@ -2358,95 +2415,95 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Khouili et al. (2025)</t>
+          <t>Fonseca et al. (2011)</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2025</v>
+        <v>2011</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Solar irradiance and PV power</t>
+          <t>PV plant power output</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Surveyed across studies; not fixed by the review</t>
+          <t>Hourly, 1 year of forecasts (day-ahead style)</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>26 selected studies screened from 155 Web of Science records</t>
+          <t>1 MW PV plant measurements plus numerically predicted weather variables</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Web of Science (literature corpus, not a PV dataset)</t>
+          <t>Kitakyushu, Japan</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>155 retrieved, 26 included</t>
+          <t>One 1-MW plant, 1 year of hourly forecasts</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Not applicable (literature corpus)</t>
+          <t>Hourly</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Ambient temperature, pressure and humidity reported as the most common input features across surveyed studies</t>
+          <t>Numerically predicted weather variables including cloudiness</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Ambient temperature, pressure, humidity (most common); Wavelet Transform most common decomposition; Pearson correlation most common feature selection</t>
+          <t>Cloudiness and other numerically predicted weather variables</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Deep learning (systematic review)</t>
+          <t>Classical machine learning</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>LSTM (32.69% of papers), CNN (28.85%); further architectures not enumerated in abstract</t>
+          <t>Support Vector Regression / support vector machine methodology</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Not applicable (review); baselines of surveyed studies are not aggregated in the abstract</t>
+          <t>Variant of the same model without cloudiness input (an internal ablation)</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Surveyed metrics catalogued but not enumerated in the retrieved abstract</t>
+          <t>RMSE, MAE, correlation between forecast and measured power</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Not applicable (review)</t>
+          <t>RMSE 0.0948 MWh, MAE 0.058 MWh; correlation 0.80-0.88 by season; removing cloudiness raises RMSE by more than 32% and MAE by more than 42%</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Identified as a persistent challenge; no regime-stratified synthesis reported in the abstract</t>
+          <t>Seasonal stratification (correlation reported by season); cloudiness as an explicit predictor</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - predictor ablation for cloudiness</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Identified as a persistent challenge; not itself quantified</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No - single plant</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -2456,22 +2513,22 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Systematic literature review (155 -&gt; 26 papers) quantifying which DL architectures, preprocessing techniques, input features, metrics and challenges dominate solar/PV forecasting.</t>
+          <t>Clean quantification of a single physically meaningful predictor's value: numerically forecast cloudiness is decisive for SVR PV forecasting.</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Corpus restricted to Web of Science; reported architecture frequencies describe the literature's choices, not their measured superiority.</t>
+          <t>Single 1-MW plant, hourly resolution only; no comparison against deep models, so conclusions are SVR-specific.</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>Quantifies the field's concentration on LSTM/CNN and identifies preprocessing, metrics and persistent challenges as under-examined dimensions.</t>
+          <t>Shows weather-predictor quality can dominate model choice, yet later deep-learning papers rarely ablate individual weather inputs.</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>Good - explicit inclusion/exclusion counts, database and frequencies reported</t>
+          <t>Moderate - plant, resolution, duration and metrics all stated</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -2484,14 +2541,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.esr.2025.101735</t>
+      <c r="AB3" s="5" t="inlineStr">
+        <is>
+          <t>10.1002/pip.1152</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Systematic review / state of the field</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Classical / conventional machine learning</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2558,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Kumari &amp; Toshniwal (2021)</t>
+          <t>Massaoudi et al. (2021)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2509,112 +2566,112 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Solar irradiance</t>
+          <t>PV power</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Short-term</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Actual database collected from weather sensors for a distributed PV system</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Weather measurements; a voted feature-weighting vector is constructed from attribute-selection ensembles</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Weather sensor measurements (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Deep learning (comprehensive review)</t>
+          <t>Classical machine learning + explainability-driven feature engineering</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Enhanced Random Forest with ensemble attribute selection (LIME, Extreme Boosting, Elastic Net)</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Several data-driven machine learning models</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Forecast accuracy metrics (specific list not in abstract)</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Not applicable (review)</t>
+          <t>Not stated numerically in retrieved abstract</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Motivated by sudden variations from stochastic weather; no named regime stratification reported</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>Yes - LIME used inside the feature-weighting procedure (explanations used to build the model, not only to interpret it)</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>No - a typical distributed PV system</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>Not stated - abstract not publicly retrievable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive review of deep learning models for solar irradiance forecasting (title and venue verified; 394 citations per Semantic Scholar).</t>
+          <t>Uses interpretability methods as a functional component of model construction (voted feature weighting) rather than as post-hoc commentary.</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>PROVENANCE LIMITATION: the abstract is not available from Crossref, OpenAlex, Semantic Scholar, the publisher landing page or any RePEc mirror (paywalled), so no claim beyond verified bibliographic metadata is asserted here. Full-text consultation is required before citing this work for any specific methodological or numerical detail.</t>
+          <t>Explainability is instrumentalised for feature selection, so it does not provide a faithful account of the final fitted model's behaviour.</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>Not assessable without full text; flagged as unverified rather than characterised.</t>
+          <t>Illustrates that XAI is used as a build tool rather than as a validation instrument; no XAI-based verification that explanations match model behaviour.</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>Not assessable without full text</t>
+          <t>Moderate - methods named, dataset not shared per abstract</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -2627,14 +2684,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.jclepro.2021.128566</t>
+      <c r="AB4" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/en14133992</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Systematic review / state of the field; FLAG: abstract_unavailable_paywalled</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Classical / conventional machine learning</t>
         </is>
       </c>
     </row>
@@ -2644,11 +2701,11 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Markovics &amp; Mayer (2022)</t>
+          <t>Rohini et al. (2026)</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2657,107 +2714,107 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Day-ahead deterministic</t>
+          <t>Very short-term</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Two-year 15-min resolution measurements from 16 PV plants</t>
+          <t>Real-world PV generation data</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16 PV plants x 2 years at 15-min resolution (exact record count not stated in abstract)</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15 minutes</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Numerical weather prediction variables; augmented with Sun position angles and statistically processed irradiance values</t>
+          <t>Meteorological and operational parameters: temperature, humidity, wind profile, cloudiness distribution, solar situation</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>NWP-derived variables plus solar position angles and processed irradiance</t>
+          <t>Temperature, humidity, wind profile, cloudiness, solar position</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Classical machine learning</t>
+          <t>Classical machine learning (stacked ensemble)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24 models compared; best two are kernel ridge regression and multilayer perceptron; linear regression used as the baseline scenario</t>
+          <t>Gradient Boosting + XGBoost base learners with Ridge Regression meta-learner</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Persistence; linear regression; 24 models in total</t>
+          <t>Gradient Boosting, XGBoost, LightGBM, CatBoost, multilayer perceptron, LSTM; evaluated with k-fold cross-validation</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>RMSE, forecast skill score relative to persistence</t>
+          <t>MAE, MSE, R2, nonparametric tests</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Up to 44.6% forecast skill score over persistence (kernel ridge regression and MLP); best forecasts 13.9% lower RMSE than the linear-regression baseline</t>
+          <t>MAE = 0.042 +/- 0.002, MSE = 0.0031 +/- 0.0002, R2 = 94% +/- 1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Two-year continuous evaluation implicitly spans seasons; no explicit regime stratification reported in the abstract</t>
+          <t>Cloudiness used as an input; no regime-stratified results reported in abstract</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>No (predictor-selection effects reported, which is a form of sensitivity analysis rather than post-hoc explanation)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - dispersion reported across k-fold repeats (MAE +/- 0.002), which is variability not calibrated prediction intervals</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>Yes - 16 plants, though pooled rather than as transfer tests</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>Yes - two-year span with chronological hold-out implied by the forecast setup</t>
+          <t>No - k-fold cross-validation, which is not a temporal hold-out</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>Largest controlled classical-ML comparison in this corpus: 24 models, 16 plants, two years, with explicit quantification of predictor-selection and hyperparameter-tuning effects.</t>
+          <t>Stacked GB-XGBoost ensemble with ridge meta-learner, benchmarked against four boosting variants, an MLP and an LSTM with nonparametric tests.</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Classical ML only - no deep or transformer architectures included, so the study cannot settle whether modern architectures beat well-tuned classical models.</t>
+          <t>Uses k-fold cross-validation on a time series, which leaks temporal information and inflates apparent accuracy relative to a chronological hold-out; this is a methodological weakness shared by much of the boosting literature.</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>Sets the classical-ML bar (persistence skill) that deep-learning PV papers frequently do not report, making cross-paper comparison impossible.</t>
+          <t>Direct evidence that random-fold validation is common in applied PV ML, making reported gains incomparable with chronological-split studies such as A5.</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>Good - dataset scale, model count, baselines and metric definitions all stated; code availability not stated in abstract</t>
+          <t>Moderate - pipeline and comparison set described; normalisation and feature selection named</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -2770,9 +2827,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.rser.2022.112364</t>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-026-47042-3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -2787,85 +2844,85 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Niu et al. (2020)</t>
+          <t>Markovics &amp; Mayer (2022)</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PV power generation</t>
+          <t>PV power</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Short-term (not enumerated in abstract)</t>
+          <t>Day-ahead deterministic</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Measurements from one PV power plant</t>
+          <t>Two-year 15-min resolution measurements from 16 PV plants</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>16 PV plants x 2 years at 15-min resolution (exact record count not stated in abstract)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>15 minutes</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Meteorological and PV factors ranked by Random Forest importance</t>
+          <t>Numerical weather prediction variables; augmented with Sun position angles and statistically processed irradiance values</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Meteorological factors affecting PV generation (specific list not in abstract)</t>
+          <t>NWP-derived variables plus solar position angles and processed irradiance</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Hybrid: feature selection + decomposition + neural network</t>
+          <t>Classical machine learning</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>RF-CEEMD-DIFPSO-BPNN (Random Forest importance, CEEMD decomposition, PSO-optimised backpropagation NN)</t>
+          <t>24 models compared; best two are kernel ridge regression and multilayer perceptron; linear regression used as the baseline scenario</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Contemporary ML/DL models (specific list not in abstract)</t>
+          <t>Persistence; linear regression; 24 models in total</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Forecast accuracy metrics (specific list not enumerated in abstract)</t>
+          <t>RMSE, forecast skill score relative to persistence</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Not stated numerically in retrieved abstract</t>
+          <t>Up to 44.6% forecast skill score over persistence (kernel ridge regression and MLP); best forecasts 13.9% lower RMSE than the linear-regression baseline</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Weather-type grouping used for similar-day screening (IGIVA); not a full regime evaluation</t>
+          <t>Two-year continuous evaluation implicitly spans seasons; no explicit regime stratification reported in the abstract</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Partial - Random Forest importance ranking reported</t>
+          <t>No (predictor-selection effects reported, which is a form of sensitivity analysis rather than post-hoc explanation)</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -2875,32 +2932,32 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>No - single plant case study</t>
+          <t>Yes - 16 plants, though pooled rather than as transfer tests</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - two-year span with chronological hold-out implied by the forecast setup</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>End-to-end hybrid pipeline coupling RF-based factor ranking, weather-type similar-day screening, CEEMD decomposition and PSO-tuned BPNN.</t>
+          <t>Largest controlled classical-ML comparison in this corpus: 24 models, 16 plants, two years, with explicit quantification of predictor-selection and hyperparameter-tuning effects.</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Single-plant case study with a five-stage pipeline, so it is difficult to attribute gains to any single component; no ablation isolating contributions.</t>
+          <t>Classical ML only - no deep or transformer architectures included, so the study cannot settle whether modern architectures beat well-tuned classical models.</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>Composite pipelines without component-level ablation make the contribution of each stage unattributable.</t>
+          <t>Sets the classical-ML bar (persistence skill) that deep-learning PV papers frequently do not report, making cross-paper comparison impossible.</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>Low - many interacting stages, no code or parameter detail in abstract</t>
+          <t>Good - dataset scale, model count, baselines and metric definitions all stated; code availability not stated in abstract</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -2913,9 +2970,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.asoc.2020.106389</t>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.rser.2022.112364</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -2930,85 +2987,85 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fonseca et al. (2011)</t>
+          <t>Wang et al. (2019)</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>PV plant power output</t>
+          <t>PV power</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Hourly, 1 year of forecasts (day-ahead style)</t>
+          <t>Not enumerated in retrieved abstract</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1 MW PV plant measurements plus numerically predicted weather variables</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Kitakyushu, Japan</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>One 1-MW plant, 1 year of hourly forecasts</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Hourly</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Numerically predicted weather variables including cloudiness</t>
+          <t>PV time-series history (temporal and spatial feature extraction)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Cloudiness and other numerically predicted weather variables</t>
+          <t>Not enumerated in retrieved abstract</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Classical machine learning</t>
+          <t>Hybrid deep learning (CNN + RNN)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Support Vector Regression / support vector machine methodology</t>
+          <t>LSTM-Convolutional Network (temporal features by LSTM first, then spatial features by CNN)</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Variant of the same model without cloudiness input (an internal ablation)</t>
+          <t>Standalone LSTM, standalone CNN, and the Convolutional-LSTM ordering (CNN first, then LSTM)</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>RMSE, MAE, correlation between forecast and measured power</t>
+          <t>Eight error evaluation indices</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>RMSE 0.0948 MWh, MAE 0.058 MWh; correlation 0.80-0.88 by season; removing cloudiness raises RMSE by more than 32% and MAE by more than 42%</t>
+          <t>Hybrid outperforms both single models and the reversed Conv-LSTM ordering (numbers not in abstract)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Seasonal stratification (correlation reported by season); cloudiness as an explicit predictor</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Partial - predictor ablation for cloudiness</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -3018,7 +3075,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>No - single plant</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3028,22 +3085,22 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>Clean quantification of a single physically meaningful predictor's value: numerically forecast cloudiness is decisive for SVR PV forecasting.</t>
+          <t>Establishes and empirically justifies the ordering of recurrent-then-convolutional feature extraction against the reversed ordering, a control often omitted elsewhere.</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>Single 1-MW plant, hourly resolution only; no comparison against deep models, so conclusions are SVR-specific.</t>
+          <t>Single dataset with no persistence reference reported, so the absolute gain over a trivial baseline cannot be judged.</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>Shows weather-predictor quality can dominate model choice, yet later deep-learning papers rarely ablate individual weather inputs.</t>
+          <t>No strong-baseline reference (persistence) reported, so headline hybrid gains are unanchored.</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>Moderate - plant, resolution, duration and metrics all stated</t>
+          <t>Low to moderate - architecture described, code and data not released per abstract</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -3056,14 +3113,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>10.1002/pip.1152</t>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2019.116225</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Classical / conventional machine learning</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Recurrent / RNN-based forecasting</t>
         </is>
       </c>
     </row>
@@ -3073,25 +3130,25 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Massaoudi et al. (2021)</t>
+          <t>Gupta &amp; Singh (2023)</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PV power</t>
+          <t>PV power generation (hourly, day-ahead)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>Day-ahead hourly (sunshine hours of a day predicted jointly)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Actual database collected from weather sensors for a distributed PV system</t>
+          <t>Measurements from three locations</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3101,57 +3158,57 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Three sites; exact record counts not stated in abstract</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Hourly</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Weather measurements; a voted feature-weighting vector is constructed from attribute-selection ensembles</t>
+          <t>Multivariate series decomposed by NA-MEMD into intrinsic mode functions</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Weather sensor measurements (specific list not in abstract)</t>
+          <t>Multivariate weather series (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Classical machine learning + explainability-driven feature engineering</t>
+          <t>Hybrid deep learning (decomposition + recurrent)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Enhanced Random Forest with ensemble attribute selection (LIME, Extreme Boosting, Elastic Net)</t>
+          <t>NA-MEMD decomposition with one LSTM per set of multivariate IMFs, jointly predicting the target IMF for a full day</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Several data-driven machine learning models</t>
+          <t>Standalone LSTM; MEMD-based LSTM</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Forecast accuracy metrics (specific list not in abstract)</t>
+          <t>RMSE, MAE (reported as percentage reductions); also decomposition runtime</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Not stated numerically in retrieved abstract</t>
+          <t>Average RMSE 65.08 W/m2 across three locations; %RMSE (%MAE) reduction of 47.65 (50.99) vs standalone LSTM and 11.11 (15.76) vs MEMD-LSTM</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Motivated by sudden variations from stochastic weather; no named regime stratification reported</t>
+          <t>Three locations imply differing climates; no explicit regime stratification reported</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Yes - LIME used inside the feature-weighting procedure (explanations used to build the model, not only to interpret it)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -3161,32 +3218,32 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>No - a typical distributed PV system</t>
+          <t>Yes - three locations</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - three sites, but all used within the same train/test protocol rather than as transfer tests</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Uses interpretability methods as a functional component of model construction (voted feature weighting) rather than as post-hoc commentary.</t>
+          <t>Decomposition-based day-ahead multi-step forecasting with a per-IMF LSTM design, plus a decomposition-cost comparison (NA-MEMD 195 s vs MEMD 251 s).</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Explainability is instrumentalised for feature selection, so it does not provide a faithful account of the final fitted model's behaviour.</t>
+          <t>Target reported in W/m2 (irradiance units) rather than PV power, so comparability with power-forecasting studies is limited; decomposition adds a substantial preprocessing stage.</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>Illustrates that XAI is used as a build tool rather than as a validation instrument; no XAI-based verification that explanations match model behaviour.</t>
+          <t>One of the few studies reporting preprocessing cost alongside accuracy, yet the accuracy gain is confounded with an added decomposition stage that itself requires tuning.</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>Moderate - methods named, dataset not shared per abstract</t>
+          <t>Moderate - decomposition and architecture described with runtimes</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -3199,14 +3256,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/en14133992</t>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.segan.2023.101133</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Classical / conventional machine learning</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Recurrent / RNN-based forecasting</t>
         </is>
       </c>
     </row>
@@ -3216,80 +3273,80 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Rohini et al. (2026)</t>
+          <t>Yu et al. (2019)</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PV power</t>
+          <t>Global horizontal irradiance (GHI) and derived PV power</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Very short-term</t>
+          <t>1 hour ahead and 1 day ahead</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Real-world PV generation data</t>
+          <t>Weather and irradiance measurements with k-means weather typing</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>Not stated in retrieved abstract (cross-regional study performed)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Not stated in retrieved abstract</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Hourly</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Meteorological and operational parameters: temperature, humidity, wind profile, cloudiness distribution, solar situation</t>
+          <t>Multivariate sequence plus clearness index used to classify weather type</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Temperature, humidity, wind profile, cloudiness, solar position</t>
+          <t>GHI, clearness index, and other multivariate weather variables</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Classical machine learning (stacked ensemble)</t>
+          <t>Recurrent deep learning</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Gradient Boosting + XGBoost base learners with Ridge Regression meta-learner</t>
+          <t>LSTM</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Gradient Boosting, XGBoost, LightGBM, CatBoost, multilayer perceptron, LSTM; evaluated with k-fold cross-validation</t>
+          <t>RNN; ANN and SVR cited from literature for cloudy-day behaviour</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>MAE, MSE, R2, nonparametric tests</t>
+          <t>R2 (plus other indices not enumerated in abstract)</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>MAE = 0.042 +/- 0.002, MSE = 0.0031 +/- 0.0002, R2 = 94% +/- 1%</t>
+          <t>R2 reported for hourly and daily forecasts (values truncated in retrieved abstract)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Cloudiness used as an input; no regime-stratified results reported in abstract</t>
+          <t>Yes - k-means weather classification into clear, cloudy and mixed/partially cloudy, motivated by cloudy-day error</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -3299,37 +3356,37 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Partial - dispersion reported across k-fold repeats (MAE +/- 0.002), which is variability not calibrated prediction intervals</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Yes - explicit cross-regional study to test generalisability</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>No - k-fold cross-validation, which is not a temporal hold-out</t>
+          <t>Yes - cross-regional transfer is the stated purpose</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>Stacked GB-XGBoost ensemble with ridge meta-learner, benchmarked against four boosting variants, an MLP and an LSTM with nonparametric tests.</t>
+          <t>Introduces clearness index as an LSTM input and combines k-means weather typing with a cross-regional generalisation test.</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Uses k-fold cross-validation on a time series, which leaks temporal information and inflates apparent accuracy relative to a chronological hold-out; this is a methodological weakness shared by much of the boosting literature.</t>
+          <t>Forecasts irradiance rather than PV power directly, and the weather classes are derived from an input feature (clearness index) rather than an independent physical classification.</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>Direct evidence that random-fold validation is common in applied PV ML, making reported gains incomparable with chronological-split studies such as G4.</t>
+          <t>Weather-regime evaluation is present but the regime labels are derived from the same signal being forecast, which can confound regime-wise error analysis.</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>Moderate - pipeline and comparison set described; normalisation and feature selection named</t>
+          <t>Moderate - method described; code not released per abstract</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -3342,14 +3399,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-026-47042-3</t>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/access.2019.2946057</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Classical / conventional machine learning</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Recurrent / RNN-based forecasting</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3416,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Wang et al. (2019)</t>
+          <t>Sun et al. (2019)</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -3367,72 +3424,72 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PV power</t>
+          <t>PV output (minutely averaged)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Not enumerated in retrieved abstract</t>
+          <t>15 minutes ahead</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>One-year database of PV output history and sky images</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Not stated in retrieved abstract</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>1 year of data at minutely resolution (exact count not stated)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Minutely averaged, 15-min ahead target</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>PV time-series history (temporal and spatial feature extraction)</t>
+          <t>Hybrid input: PV output history plus sky images; lag-term configuration studied explicitly</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Not enumerated in retrieved abstract</t>
+          <t>Sky images; cloud movement is the driver of forecast uncertainty</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid deep learning (CNN + RNN)</t>
+          <t>Convolutional deep learning</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>LSTM-Convolutional Network (temporal features by LSTM first, then spatial features by CNN)</t>
+          <t>SUNSET - a specialised CNN with hybrid input and strong regularisation</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Standalone LSTM, standalone CNN, and the Convolutional-LSTM ordering (CNN first, then LSTM)</t>
+          <t>Smart persistence forecast (explicit reference); input and output configuration variants</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Eight error evaluation indices</t>
+          <t>Forecast skill relative to smart persistence, stratified by cloudy vs all-weather</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Hybrid outperforms both single models and the reversed Conv-LSTM ordering (numbers not in abstract)</t>
+          <t>16.3% forecast skill in cloudy conditions and 15.7% in all weather relative to smart persistence</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Yes - cloudy versus all-weather skill reported</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
@@ -3457,27 +3514,27 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Establishes and empirically justifies the ordering of recurrent-then-convolutional feature extraction against the reversed ordering, a control often omitted elsewhere.</t>
+          <t>Systematic study of input and output configuration (history length, downsampling, PV-output versus clear-sky-index targets) with results reported as skill over smart persistence, plus public code.</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>Single dataset with no persistence reference reported, so the absolute gain over a trivial baseline cannot be judged.</t>
+          <t>Single site and one year; requires sky images, which many operational sites lack.</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>No strong-baseline reference (persistence) reported, so headline hybrid gains are unanchored.</t>
+          <t>Rare example of a rigorous, openly reproducible study anchored to a smart-persistence reference - precisely the practice this corpus otherwise lacks.</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate - architecture described, code and data not released per abstract</t>
+          <t>High - code publicly released on GitHub (YuchiSun/SUNSET) and configuration recommendations stated</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -3485,9 +3542,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2019.116225</t>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.solener.2019.06.041</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -3502,25 +3559,25 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Gupta &amp; Singh (2023)</t>
+          <t>Mishra et al. (2020)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>PV power generation (hourly, day-ahead)</t>
+          <t>Solar PV power</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Day-ahead hourly (sunshine hours of a day predicted jointly)</t>
+          <t>Hourly and day-ahead</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Measurements from three locations</t>
+          <t>Recorded solar energy time-series data</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3530,52 +3587,52 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Three sites; exact record counts not stated in abstract</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Hourly</t>
+          <t>Hourly (with day-level targets)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Multivariate series decomposed by NA-MEMD into intrinsic mode functions</t>
+          <t>Statistical wavelet-transform features of the time series plus temperature, wind speed, pressure, cloudy index, humidity, altimeter index</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Multivariate weather series (specific list not in abstract)</t>
+          <t>Temperature, wind speed, pressure, cloudy index, humidity, altimeter index</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Hybrid deep learning (decomposition + recurrent)</t>
+          <t>Hybrid deep learning (signal decomposition + recurrent)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>NA-MEMD decomposition with one LSTM per set of multivariate IMFs, jointly predicting the target IMF for a full day</t>
+          <t>WT-LSTM: wavelet transform decomposition plus statistical feature extraction, then dropout-regularised LSTM</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Standalone LSTM; MEMD-based LSTM</t>
+          <t>Contemporary machine learning and deep learning models</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>RMSE, MAE (reported as percentage reductions); also decomposition runtime</t>
+          <t>RMSE, MAPE, MAE, R2</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Average RMSE 65.08 W/m2 across three locations; %RMSE (%MAE) reduction of 47.65 (50.99) vs standalone LSTM and 11.11 (15.76) vs MEMD-LSTM</t>
+          <t>Not stated numerically in retrieved abstract</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Three locations imply differing climates; no explicit regime stratification reported</t>
+          <t>Cloudy index used as an input; no regime-stratified evaluation reported</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -3590,32 +3647,32 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Yes - three locations</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>Partial - three sites, but all used within the same train/test protocol rather than as transfer tests</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Decomposition-based day-ahead multi-step forecasting with a per-IMF LSTM design, plus a decomposition-cost comparison (NA-MEMD 195 s vs MEMD 251 s).</t>
+          <t>Couples wavelet-domain feature extraction with an LSTM and evaluates at two horizons (hourly and daily).</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>Target reported in W/m2 (irradiance units) rather than PV power, so comparability with power-forecasting studies is limited; decomposition adds a substantial preprocessing stage.</t>
+          <t>Reports MAPE on a target that is zero at night, which makes the percentage metric unstable; no night-time masking described in the abstract.</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>One of the few studies reporting preprocessing cost alongside accuracy, yet the accuracy gain is confounded with an added decomposition stage that itself requires tuning.</t>
+          <t>Exemplifies inconsistent metric practice: MAPE is reported without justification despite a target containing exact zeros.</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>Moderate - decomposition and architecture described with runtimes</t>
+          <t>Moderate - inputs enumerated explicitly</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -3628,14 +3685,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.segan.2023.101133</t>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.measurement.2020.108250</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Recurrent / RNN-based forecasting</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Hybrid deep learning</t>
         </is>
       </c>
     </row>
@@ -3645,82 +3702,82 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Yu et al. (2019)</t>
+          <t>Yao et al. (2022)</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Global horizontal irradiance (GHI) and derived PV power</t>
+          <t>PV generation (intra-hour)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1 hour ahead and 1 day ahead</t>
+          <t>Intra-hour (sub-hourly)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Weather and irradiance measurements with k-means weather typing</t>
+          <t>Multi-source data: local measurements, NWP and satellite images, from 50 PV power stations</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract (cross-regional study performed)</t>
+          <t>50 real-world PV power stations (region not stated in abstract)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>50 PV power stations</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Intra-hour / sub-hourly</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Time-series records plus satellite images; local measurements and NWP</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Satellite imagery, NWP fields, local sensor measurements</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid deep learning (multi-source encoder-decoder)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>U-Net combined with an encoder-decoder architecture, cooperatively processing time-series and image data</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Several baseline models (not enumerated in abstract)</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy metrics (not enumerated in abstract)</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Reported as higher accuracy than baselines across 50 stations (numbers not in abstract)</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Hourly</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Multivariate sequence plus clearness index used to classify weather type</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>GHI, clearness index, and other multivariate weather variables</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Recurrent deep learning</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>LSTM</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>RNN; ANN and SVR cited from literature for cloudy-day behaviour</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>R2 (plus other indices not enumerated in abstract)</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>R2 reported for hourly and daily forecasts (values truncated in retrieved abstract)</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Yes - k-means weather classification into clear, cloudy and mixed/partially cloudy, motivated by cloudy-day error</t>
-        </is>
-      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>No</t>
@@ -3733,32 +3790,32 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Yes - explicit cross-regional study to test generalisability</t>
+          <t>Yes - 50 stations</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>Yes - cross-regional transfer is the stated purpose</t>
+          <t>Yes - large multi-site sample</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Introduces clearness index as an LSTM input and combines k-means weather typing with a cross-regional generalisation test.</t>
+          <t>Demonstrates that fusing satellite imagery with local time series via U-Net plus encoder-decoder improves intra-hour forecasting, validated at unusual scale (50 stations).</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>Forecasts irradiance rather than PV power directly, and the weather classes are derived from an input feature (clearness index) rather than an independent physical classification.</t>
+          <t>Requires satellite imagery, which imposes latency and licensing constraints for real-time operation; accuracy figures are not recoverable from the abstract.</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>Weather-regime evaluation is present but the regime labels are derived from the same signal being forecast, which can confound regime-wise error analysis.</t>
+          <t>Multi-source models are evaluated at scale but their dependence on exogenous imagery makes latency and cost trade-offs unexamined.</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>Moderate - method described; code not released per abstract</t>
+          <t>Moderate - architecture and station count given; data access not described</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -3771,14 +3828,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>10.1109/access.2019.2946057</t>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/tste.2021.3123337</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Recurrent / RNN-based forecasting</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Hybrid deep learning</t>
         </is>
       </c>
     </row>
@@ -3788,80 +3845,80 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Sun et al. (2019)</t>
+          <t>Liu &amp; Mao (2024)</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PV output (minutely averaged)</t>
+          <t>PV power</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15 minutes ahead</t>
+          <t>Short-term</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>One-year database of PV output history and sky images</t>
+          <t>Actual data from a 1 MW PV power station</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>One 1-MW station (record count not stated in abstract)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1 year of data at minutely resolution (exact count not stated)</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Minutely averaged, 15-min ahead target</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Hybrid input: PV output history plus sky images; lag-term configuration studied explicitly</t>
+          <t>Multidimensional time-series features with learned feature extraction and attention weighting</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Sky images; cloud movement is the driver of forecast uncertainty</t>
+          <t>Multidimensional weather time series (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Convolutional deep learning</t>
+          <t>Hybrid deep learning (CNN + BiRNN + attention)</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SUNSET - a specialised CNN with hybrid input and strong regularisation</t>
+          <t>CNN-BiLSTM with an attention mechanism</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Smart persistence forecast (explicit reference); input and output configuration variants</t>
+          <t>Eight advanced prediction models</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Forecast skill relative to smart persistence, stratified by cloudy vs all-weather</t>
+          <t>MAE, RMSE, maximum error</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16.3% forecast skill in cloudy conditions and 15.7% in all weather relative to smart persistence</t>
+          <t>Ablation: removing the CNN component increased MAE by 58.2% and RMSE by 53.9%; removing attention increased maximum error by 83.8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Yes - cloudy versus all-weather skill reported</t>
+          <t>Weather variability is the stated motivation; no regime-stratified results reported in the abstract</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -3876,7 +3933,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No - single 1-MW station</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3886,27 +3943,27 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Systematic study of input and output configuration (history length, downsampling, PV-output versus clear-sky-index targets) with results reported as skill over smart persistence, plus public code.</t>
+          <t>Component-level ablation quantifying the contribution of the CNN stage and the attention mechanism separately - one of the few papers in this corpus that isolates architectural components.</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>Single site and one year; requires sky images, which many operational sites lack.</t>
+          <t>Single station; relative percentage changes are reported without absolute error levels, making practical significance unclear.</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>Rare example of a rigorous, openly reproducible study anchored to a smart-persistence reference - precisely the practice this corpus otherwise lacks.</t>
+          <t>Shows ablation is possible and informative, yet the paper still reports only relative degradation rather than absolute calibrated errors, and does not test robustness across regimes or sites.</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>High - code publicly released on GitHub (YuchiSun/SUNSET) and configuration recommendations stated</t>
+          <t>Moderate - ablation design is explicit</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -3914,14 +3971,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.solener.2019.06.041</t>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.renene.2024.120437</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Recurrent / RNN-based forecasting</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Hybrid deep learning</t>
         </is>
       </c>
     </row>
@@ -3931,25 +3988,25 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Mishra et al. (2020)</t>
+          <t>Hu et al. (2024)</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Solar PV power</t>
+          <t>PV power</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Hourly and day-ahead</t>
+          <t>Short-term</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Recorded solar energy time-series data</t>
+          <t>Target station NWP data plus highly correlated features from nearby PV stations</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3959,57 +4016,57 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>Target station plus a set of selected neighbouring stations (count not stated in abstract)</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Hourly (with day-level targets)</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Statistical wavelet-transform features of the time series plus temperature, wind speed, pressure, cloudy index, humidity, altimeter index</t>
+          <t>NWP data of the target station plus correlated features from nearby stations, selected via a distance-weighted similarity index and fused at a Bayesian-optimised ratio</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Temperature, wind speed, pressure, cloudy index, humidity, altimeter index</t>
+          <t>NWP fields and neighbouring-station irradiance/power features</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Hybrid deep learning (signal decomposition + recurrent)</t>
+          <t>Hybrid deep learning (CNN + LSTM + attention)</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>WT-LSTM: wavelet transform decomposition plus statistical feature extraction, then dropout-regularised LSTM</t>
+          <t>Conv-LSTM-ATT with Bayesian-optimised multi-station data fusion</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Contemporary machine learning and deep learning models</t>
+          <t>Three classical models</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>RMSE, MAPE, MAE, R2</t>
+          <t>RME, stratified by weather condition</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Not stated numerically in retrieved abstract</t>
+          <t>Data fusion reduces test RMSE by 20.04% (sunny), 28.24% (cloudy) and 30.94% (rainy)</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Cloudy index used as an input; no regime-stratified evaluation reported</t>
+          <t>Yes - sunny, cloudy and rainy conditions reported separately</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - station similarity index and fusion ratio provide an interpretable selection mechanism</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -4019,32 +4076,32 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Yes - multi-station data fusion</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - neighbouring stations supply inputs; the model is not transferred to unseen sites</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Couples wavelet-domain feature extraction with an LSTM and evaluates at two horizons (hourly and daily).</t>
+          <t>Quantifies how much neighbouring-station data fusion helps, and reports the benefit separately for sunny, cloudy and rainy conditions.</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>Reports MAPE on a target that is zero at night, which makes the percentage metric unstable; no night-time masking described in the abstract.</t>
+          <t>Fusion assumes neighbouring stations are available and correlated at inference time; no test of generalisation to sites absent from the training pool.</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>Exemplifies inconsistent metric practice: MAPE is reported without justification despite a target containing exact zeros.</t>
+          <t>Demonstrates the value of spatial context while leaving open whether a model trained on a station pool generalises to a new site - the transfer question remains unaddressed.</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>Moderate - inputs enumerated explicitly</t>
+          <t>Moderate - selection index and optimisation procedure described</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -4057,9 +4114,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.measurement.2020.108250</t>
+      <c r="AB14" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/app14125189</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -4074,7 +4131,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Yao et al. (2022)</t>
+          <t>Dai et al. (2022)</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -4082,67 +4139,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PV generation (intra-hour)</t>
+          <t>PV power generation (daily resolution)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Intra-hour (sub-hourly)</t>
+          <t>Short-term (days), compared against medium and long-term (months)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Multi-source data: local measurements, NWP and satellite images, from 50 PV power stations</t>
+          <t>Daily PV power generation from Xuhui District, Shanghai, plus DKASC Alice Springs data</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50 real-world PV power stations (region not stated in abstract)</t>
+          <t>Shanghai, China and Alice Springs, Australia</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>50 PV power stations</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Intra-hour / sub-hourly</t>
+          <t>Daily (with monthly aggregation for medium/long-term comparison)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Time-series records plus satellite images; local measurements and NWP</t>
+          <t>Daily generation smoothed by LOWESS, plus natural factors selected by Random Forest</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Satellite imagery, NWP fields, local sensor measurements</t>
+          <t>Natural factors affecting daily generation (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Hybrid deep learning (multi-source encoder-decoder)</t>
+          <t>Hybrid: smoothing + feature selection + recurrent deep learning</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>U-Net combined with an encoder-decoder architecture, cooperatively processing time-series and image data</t>
+          <t>Improved GRU with RepeatVector and TimeDistributed layers, on LOWESS-smoothed, RF-selected inputs</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Several baseline models (not enumerated in abstract)</t>
+          <t>Three prediction models (not enumerated in abstract); original GRU as the base model</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Accuracy metrics (not enumerated in abstract)</t>
+          <t>Forecast error metrics (not enumerated in abstract)</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Reported as higher accuracy than baselines across 50 stations (numbers not in abstract)</t>
+          <t>Not stated numerically in retrieved abstract</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4152,7 +4209,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - Random Forest used for feature selection</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -4162,32 +4219,32 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Yes - 50 stations</t>
+          <t>Yes - Shanghai and Alice Springs</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>Yes - large multi-site sample</t>
+          <t>Yes - second dataset used to test short vs medium/long-term suitability</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Demonstrates that fusing satellite imagery with local time series via U-Net plus encoder-decoder improves intra-hour forecasting, validated at unusual scale (50 stations).</t>
+          <t>Compares five smoothing techniques head-to-head, adds RF feature selection, and augments GRU with RepeatVector/TimeDistributed layers; tests the method on a second, climatically distinct dataset.</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>Requires satellite imagery, which imposes latency and licensing constraints for real-time operation; accuracy figures are not recoverable from the abstract.</t>
+          <t>Operates at daily resolution, which sidesteps the intra-day ramping problem that dominates operational PV forecasting relevance.</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>Multi-source models are evaluated at scale but their dependence on exogenous imagery makes latency and cost trade-offs unexamined.</t>
+          <t>Cross-site validation is used to justify generality, but at a temporal resolution too coarse to answer questions about intra-day robustness.</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>Moderate - architecture and station count given; data access not described</t>
+          <t>Moderate - all processing stages enumerated; no code released per abstract</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -4197,12 +4254,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>10.1109/tste.2021.3123337</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2022.124661</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -4217,11 +4274,11 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Liu &amp; Mao (2024)</t>
+          <t>Lei et al. (2026)</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -4230,72 +4287,72 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>Short-term (minute-level ramping detection)</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Actual data from a 1 MW PV power station</t>
+          <t>Field validation at a 150 kW PV power plant</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ningxia, China</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>One 1-MW station (record count not stated in abstract)</t>
+          <t>One 150-kW plant (record count not stated in abstract)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Minute-level (implied by 'minute-level ramping detection')</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Multidimensional time-series features with learned feature extraction and attention weighting</t>
+          <t>Time-series features with SE-based (squeeze-and-excitation) dynamic attention weighting</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Multidimensional weather time series (specific list not in abstract)</t>
+          <t>Meteorological inputs (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Hybrid deep learning (CNN + BiRNN + attention)</t>
+          <t>Hybrid deep learning (CNN + LSTM + attention)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>CNN-BiLSTM with an attention mechanism</t>
+          <t>CNN-LSTM-Attention with squeeze-and-excitation attention</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Eight advanced prediction models</t>
+          <t>Standard LSTM; CNN-LSTM (suboptimal baseline); further baselines not enumerated</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>MAE, RMSE, maximum error</t>
+          <t>RMSE, Diebold-Mariano test, Dynamic Time Warping, residual distribution analysis</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Ablation: removing the CNN component increased MAE by 58.2% and RMSE by 53.9%; removing attention increased maximum error by 83.8%</t>
+          <t>RMSE convergence of 2.157 kW; 41.92% reduction vs standard LSTM; 16.46% improvement over the CNN-LSTM baseline</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Weather variability is the stated motivation; no regime-stratified results reported in the abstract</t>
+          <t>Yes - multi-weather evaluations reported</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No - attention weights are used for weighting, not interpreted</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -4305,7 +4362,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>No - single 1-MW station</t>
+          <t>No - single plant</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4315,22 +4372,22 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Component-level ablation quantifying the contribution of the CNN stage and the attention mechanism separately - one of the few papers in this corpus that isolates architectural components.</t>
+          <t>One of very few papers in this corpus that applies a Diebold-Mariano test and analyses residual distributions to support a superiority claim, and quantifies the attention module's marginal contribution.</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>Single station; relative percentage changes are reported without absolute error levels, making practical significance unclear.</t>
+          <t>Single small (150 kW) plant; the DM test details (loss function, horizon, sample size) are not recoverable from the abstract.</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>Shows ablation is possible and informative, yet the paper still reports only relative degradation rather than absolute calibrated errors, and does not test robustness across regimes or sites.</t>
+          <t>Demonstrates that significance testing is achievable in applied PV forecasting, yet remains isolated - this corpus contains no other paper that formally tests model differences.</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>Moderate - ablation design is explicit</t>
+          <t>Moderate - tests and metrics named; code not released per abstract</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -4343,9 +4400,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.renene.2024.120437</t>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/en19071747</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -4360,7 +4417,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Hu et al. (2024)</t>
+          <t>Kim et al. (2024)</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -4368,17 +4425,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PV power</t>
+          <t>PV power generation</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>Day-ahead, multi-step (next-day hourly)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Target station NWP data plus highly correlated features from nearby PV stations</t>
+          <t>Data from two PV power plants</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4388,57 +4445,57 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Target station plus a set of selected neighbouring stations (count not stated in abstract)</t>
+          <t>Two PV plants (record counts not stated in abstract)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>Hourly (day-ahead hourly targets)</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Historical solar power generation, weather observation, weather forecast and solar geometry data</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Weather observations, weather forecasts, solar geometry (solar position angles)</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Transformer + recurrent hybrid</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>PVTransNet - three transformer variants, the third (PVTransNet-EDR) combining LSTM with the transformer to supplement weather-station forecasts</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Individual LSTM; other transformer variants; traditional operational benchmarks implied</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>MAE (primary), plus other metrics not enumerated in abstract</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>PVTransNet-EDR performed 48.3% better in MAE than simple LSTM</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>NWP data of the target station plus correlated features from nearby stations, selected via a distance-weighted similarity index and fused at a Bayesian-optimised ratio</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>NWP fields and neighbouring-station irradiance/power features</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>Hybrid deep learning (CNN + LSTM + attention)</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Conv-LSTM-ATT with Bayesian-optimised multi-station data fusion</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Three classical models</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>RME, stratified by weather condition</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Data fusion reduces test RMSE by 20.04% (sunny), 28.24% (cloudy) and 30.94% (rainy)</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Yes - sunny, cloudy and rainy conditions reported separately</t>
-        </is>
-      </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>Partial - station similarity index and fusion ratio provide an interpretable selection mechanism</t>
+          <t>No - solar geometry is an input, not an explanation</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -4448,32 +4505,32 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>Yes - multi-station data fusion</t>
+          <t>Yes - two PV plants</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>Partial - neighbouring stations supply inputs; the model is not transferred to unseen sites</t>
+          <t>Partial - two plants, but not framed as cross-site transfer</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Quantifies how much neighbouring-station data fusion helps, and reports the benefit separately for sunny, cloudy and rainy conditions.</t>
+          <t>Shows that combining an LSTM encoder with a transformer, and adding solar geometry alongside weather data, yields large day-ahead gains over plain LSTM on two plants.</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>Fusion assumes neighbouring stations are available and correlated at inference time; no test of generalisation to sites absent from the training pool.</t>
+          <t>The 48.3% MAE improvement is against plain LSTM rather than a tuned classical baseline, so it does not establish superiority over well-tuned gradient boosting.</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>Demonstrates the value of spatial context while leaving open whether a model trained on a station pool generalises to a new site - the transfer question remains unaddressed.</t>
+          <t>Advanced architectures are typically compared against weak neural baselines, not against tuned classical ML with persistence-relative skill, leaving their true margin unestablished.</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>Moderate - selection index and optimisation procedure described</t>
+          <t>Moderate - inputs and variants described; code not released per abstract</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -4486,14 +4543,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/app14125189</t>
+      <c r="AB17" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.rser.2024.114479</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Hybrid deep learning</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Advanced / attention-based architectures</t>
         </is>
       </c>
     </row>
@@ -4503,30 +4560,30 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dai et al. (2022)</t>
+          <t>Piantadosi et al. (2024)</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>PV power generation (daily resolution)</t>
+          <t>PV power output</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Short-term (days), compared against medium and long-term (months)</t>
+          <t>Not enumerated in retrieved abstract</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Daily PV power generation from Xuhui District, Shanghai, plus DKASC Alice Springs data</t>
+          <t>OpenMeteo meteorological data combined with an irradiance model</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Shanghai, China and Alice Springs, Australia</t>
+          <t>OpenMeteo (open meteorological data provider); site not stated in abstract</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -4536,87 +4593,87 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Daily (with monthly aggregation for medium/long-term comparison)</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Daily generation smoothed by LOWESS, plus natural factors selected by Random Forest</t>
+          <t>Irradiance from a meteorological provider, local weather data, modelled irradiance and PV plant configuration data</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Natural factors affecting daily generation (specific list not in abstract)</t>
+          <t>Provider meteorological forecasts and modelled irradiance</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Hybrid: smoothing + feature selection + recurrent deep learning</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Improved GRU with RepeatVector and TimeDistributed layers, on LOWESS-smoothed, RF-selected inputs</t>
+          <t>Transformer Neural Network trained on OpenMeteo data</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Three prediction models (not enumerated in abstract); original GRU as the base model</t>
+          <t>Other machine learning techniques and other meteorological forecast providers, systematically compared</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Forecast error metrics (not enumerated in abstract)</t>
+          <t>MAE, MAPE, R2</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Not stated numerically in retrieved abstract</t>
+          <t>MAE 1.22 kW (0.95%), MAPE 2.21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
+          <t>Meteorological provider comparison acts as a proxy for condition sensitivity; no named regime stratification reported</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>Partial - Random Forest used for feature selection</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>Yes - Shanghai and Alice Springs</t>
-        </is>
-      </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>Yes - second dataset used to test short vs medium/long-term suitability</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Compares five smoothing techniques head-to-head, adds RF feature selection, and augments GRU with RepeatVector/TimeDistributed layers; tests the method on a second, climatically distinct dataset.</t>
+          <t>Systematically quantifies the effect of the meteorological forecast provider on PV forecasting accuracy, decoupling accuracy from model architecture.</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>Operates at daily resolution, which sidesteps the intra-day ramping problem that dominates operational PV forecasting relevance.</t>
+          <t>Reports MAPE on a target that is zero outside daylight hours; the irradiance model is coupled to a single provider, so results depend on that provider's skill.</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>Cross-site validation is used to justify generality, but at a temporal resolution too coarse to answer questions about intra-day robustness.</t>
+          <t>Isolates input-source quality as a confounder of model comparison - an important control that most architecture-focused papers omit, yet rarely combined with persistence-anchored skill.</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>Moderate - all processing stages enumerated; no code released per abstract</t>
+          <t>Good - open data source (OpenMeteo) named, provider comparison explicit</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -4629,14 +4686,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2022.124661</t>
+      <c r="AB18" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.egyai.2024.100444</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Hybrid deep learning</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Advanced / attention-based architectures</t>
         </is>
       </c>
     </row>
@@ -4646,85 +4703,85 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Lei et al. (2026)</t>
+          <t>Sima et al. (2025)</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PV power</t>
+          <t>PV power (multi-site)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Short-term (minute-level ramping detection)</t>
+          <t>Not enumerated in retrieved abstract</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Field validation at a 150 kW PV power plant</t>
+          <t>Multi-site PV power data at multiple temporal scales via average downsampling</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Ningxia, China</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>One 150-kW plant (record count not stated in abstract)</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Minute-level (implied by 'minute-level ramping detection')</t>
+          <t>Multi-scale (minute-level and hourly scales constructed by downsampling)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Time-series features with SE-based (squeeze-and-excitation) dynamic attention weighting</t>
+          <t>Historical PV power from multiple sites; graphs from geographic topology and self-learned adjacency matrices</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Meteorological inputs (specific list not in abstract)</t>
+          <t>Historical PV power sequences (weather variables not the primary input)</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Hybrid deep learning (CNN + LSTM + attention)</t>
+          <t>Graph neural network / spatial-temporal deep learning</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>CNN-LSTM-Attention with squeeze-and-excitation attention</t>
+          <t>MSF-GCN - Multi-Scale Fused Graph Convolutional Network with Multi-Graph Convolution (MGCN), Decomposed-Bidirectional-Fusion (DBF) MLP block and multiple unshared-weight predictors</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Standard LSTM; CNN-LSTM (suboptimal baseline); further baselines not enumerated</t>
+          <t>Existing multi-site and spatiotemporal methods (not enumerated in abstract)</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>RMSE, Diebold-Mariano test, Dynamic Time Warping, residual distribution analysis</t>
+          <t>Accuracy metrics plus run-time efficiency; ablation per block</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>RMSE convergence of 2.157 kW; 41.92% reduction vs standard LSTM; 16.46% improvement over the CNN-LSTM baseline</t>
+          <t>Consistent accuracy improvement over existing methods with favourable run-time efficiency (numbers not in abstract)</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Yes - multi-weather evaluations reported</t>
+          <t>Not stated in retrieved abstract; inter-site correlation variation across time scales is the explicit focus</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>No - attention weights are used for weighting, not interpreted</t>
+          <t>Partial - learned adjacency matrices and per-block ablations provide architectural interpretability</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -4734,32 +4791,32 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>No - single plant</t>
+          <t>Yes - multi-site modelling is the core contribution</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No - models sites jointly rather than testing transfer to unseen sites</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>One of very few papers in this corpus that applies a Diebold-Mariano test and analyses residual distributions to support a superiority claim, and quantifies the attention module's marginal contribution.</t>
+          <t>Formalises the observation that inter-site correlation strength is time-scale dependent (geographic at hourly scales, decorrelated at minute scales) and builds a multi-scale graph architecture around it, with per-block ablation.</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>Single small (150 kW) plant; the DM test details (loss function, horizon, sample size) are not recoverable from the abstract.</t>
+          <t>Requires a dense multi-site panel with aligned measurements, which many operators lack; the architecture is complex, raising the computational bar without a cost/accuracy frontier analysis.</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>Demonstrates that significance testing is achievable in applied PV forecasting, yet remains isolated - this corpus contains no other paper that formally tests model differences.</t>
+          <t>Multi-site work optimises joint modelling but does not quantify the accuracy-versus-complexity trade-off, nor test whether a model trained on a site pool transfers to an unseen site.</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>Moderate - tests and metrics named; code not released per abstract</t>
+          <t>Moderate - architecture and ablations detailed; data access not described</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4772,14 +4829,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/en19071747</t>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.enconman.2025.119773</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Hybrid deep learning</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Advanced / attention-based architectures</t>
         </is>
       </c>
     </row>
@@ -4789,25 +4846,25 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Kim et al. (2024)</t>
+          <t>Cantillo-Luna et al. (2023)</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PV power generation</t>
+          <t>Residential PV power production (low-volume, univariate time series)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Day-ahead, multi-step (next-day hourly)</t>
+          <t>Multiple forecast horizons (univariate, various scenarios)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Data from two PV power plants</t>
+          <t>Low-volume residential PV production time series</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4817,47 +4874,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Two PV plants (record counts not stated in abstract)</t>
+          <t>Not stated in retrieved abstract; characterised as low-volume</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Hourly (day-ahead hourly targets)</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Historical solar power generation, weather observation, weather forecast and solar geometry data</t>
+          <t>Univariate PV production history</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Weather observations, weather forecasts, solar geometry (solar position angles)</t>
+          <t>None - univariate setting (an explicit and unusual design choice)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Transformer + recurrent hybrid</t>
+          <t>Classical ML + deep learning benchmark</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>PVTransNet - three transformer variants, the third (PVTransNet-EDR) combining LSTM with the transformer to supplement weather-station forecasts</t>
+          <t>XGBoost, random forest, SVR, multilayer perceptron, tuned LSTM, and a proposed ConvLSTM1D</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Individual LSTM; other transformer variants; traditional operational benchmarks implied</t>
+          <t>The other five models in the benchmark; results considered alongside technical and economic impacts</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>MAE (primary), plus other metrics not enumerated in abstract</t>
+          <t>RMSE, MAPE, MAE</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>PVTransNet-EDR performed 48.3% better in MAE than simple LSTM</t>
+          <t>Random forest and ConvLSTM1D yielded the most accurate performance (lowest RMSE, MAPE, MAE) across scenarios</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4867,7 +4924,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>No - solar geometry is an input, not an explanation</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -4877,32 +4934,32 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Yes - two PV plants</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>Partial - two plants, but not framed as cross-site transfer</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>Shows that combining an LSTM encoder with a transformer, and adding solar geometry alongside weather data, yields large day-ahead gains over plain LSTM on two plants.</t>
+          <t>Univariate benchmark of six models on low-volume residential PV, and notably finds random forest competitive with the best deep model - an important counterweight to deep-learning dominance.</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>The 48.3% MAE improvement is against plain LSTM rather than a tuned classical baseline, so it does not establish superiority over well-tuned gradient boosting.</t>
+          <t>Univariate inputs discard weather information, so accuracy is capped; reported MAPE on a zero-containing target is not justified.</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>Advanced architectures are typically compared against weak neural baselines, not against tuned classical ML with persistence-relative skill, leaving their true margin unestablished.</t>
+          <t>Provides direct evidence that a classical ensemble can match a deep architecture, reinforcing that deep models are not automatically superior - a claim most PV forecasting papers do not test.</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>Moderate - inputs and variants described; code not released per abstract</t>
+          <t>Moderate - model list and metrics explicit; data not shared per abstract</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4915,9 +4972,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.rser.2024.114479</t>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/en16104097</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -4932,80 +4989,80 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Piantadosi et al. (2024)</t>
+          <t>Radzi et al. (2026)</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PV power output</t>
+          <t>PV power (two array technologies)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Not enumerated in retrieved abstract</t>
+          <t>Hour-ahead</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>OpenMeteo meteorological data combined with an irradiance model</t>
+          <t>Measurements from two PV arrays: poly-crystalline (Array 1) and mono-crystalline (Array 2)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>OpenMeteo (open meteorological data provider); site not stated in abstract</t>
+          <t>Tropical climate (region not named in abstract)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Two arrays (record counts not stated in abstract)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Hourly (hour-ahead target)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Irradiance from a meteorological provider, local weather data, modelled irradiance and PV plant configuration data</t>
+          <t>Time-indexed series used with a recursive forecasting strategy</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Provider meteorological forecasts and modelled irradiance</t>
+          <t>Meteorological inputs (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Hybrid deep learning</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Transformer Neural Network trained on OpenMeteo data</t>
+          <t>Sequential GRU-LSTM hybrid with GRU as the primary connector passing short-term dependencies to an LSTM layer, with recursive forecasting</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Other machine learning techniques and other meteorological forecast providers, systematically compared</t>
+          <t>Standalone ML and DL models, including standalone GRU and LSTM</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MAE, MAPE, R2</t>
+          <t>RMSE, MAE, R2, residual analysis</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>MAE 1.22 kW (0.95%), MAPE 2.21%</t>
+          <t>Array 1: RMSE 28.55 W, MAE 19.43 W, R2 0.9961</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Meteorological provider comparison acts as a proxy for condition sensitivity; no named regime stratification reported</t>
+          <t>Tropical climatic variability is the stated context; no named regime stratification reported</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
@@ -5020,32 +5077,32 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Partial - two co-located arrays of different technology, which tests technology transfer rather than geographic transfer</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Systematically quantifies the effect of the meteorological forecast provider on PV forecasting accuracy, decoupling accuracy from model architecture.</t>
+          <t>Tests a GRU-LSTM sequential hybrid under recursive forecasting and compares two PV technologies, which probes whether architecture conclusions are technology-dependent.</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>Reports MAPE on a target that is zero outside daylight hours; the irradiance model is coupled to a single provider, so results depend on that provider's skill.</t>
+          <t>Recursive multi-step prediction accumulates error; a very high R2 (0.9961) on a single array is not evidence of robustness under regime change.</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>Isolates input-source quality as a confounder of model comparison - an important control that most architecture-focused papers omit, yet rarely combined with persistence-anchored skill.</t>
+          <t>Near-perfect aggregate R2 coexists with no regime, seasonal or cross-site analysis - direct evidence that aggregate metrics can mask operational failure modes.</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>Good - open data source (OpenMeteo) named, provider comparison explicit</t>
+          <t>Moderate - architecture and metrics explicit; data not shared per abstract</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -5055,12 +5112,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.egyai.2024.100444</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecmx.2025.101431</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -5075,25 +5132,25 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Sima et al. (2025)</t>
+          <t>Luo et al. (2021)</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>PV power (multi-site)</t>
+          <t>PV power generation (hourly day-ahead)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Not enumerated in retrieved abstract</t>
+          <t>Hourly day-ahead</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Multi-site PV power data at multiple temporal scales via average downsampling</t>
+          <t>Real-life PV datasets</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5108,52 +5165,52 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Multi-scale (minute-level and hourly scales constructed by downsampling)</t>
+          <t>Hourly</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Historical PV power from multiple sites; graphs from geographic topology and self-learned adjacency matrices</t>
+          <t>Selected via a two-stage hybrid sensitivity analysis; includes PV domain knowledge as constraints</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Historical PV power sequences (weather variables not the primary input)</t>
+          <t>PV domain knowledge and meteorological inputs (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Graph neural network / spatial-temporal deep learning</t>
+          <t>Physics-informed deep learning</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>MSF-GCN - Multi-Scale Fused Graph Convolutional Network with Multi-Graph Convolution (MGCN), Decomposed-Bidirectional-Fusion (DBF) MLP block and multiple unshared-weight predictors</t>
+          <t>PC-LSTM - physics-constrained LSTM enforcing PV physical consistency</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Existing multi-site and spatiotemporal methods (not enumerated in abstract)</t>
+          <t>Standard LSTM; data-only machine learning models</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Accuracy metrics plus run-time efficiency; ablation per block</t>
+          <t>Forecast accuracy and robustness (not enumerated in abstract)</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Consistent accuracy improvement over existing methods with favourable run-time efficiency (numbers not in abstract)</t>
+          <t>PC-LSTM stronger than standard LSTM, more robust and better suited to sparse-data settings (numbers not in abstract)</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract; inter-site correlation variation across time scales is the explicit focus</t>
+          <t>Robustness emphasised; no named regime stratification reported</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>Partial - learned adjacency matrices and per-block ablations provide architectural interpretability</t>
+          <t>Partial - physical constraints make behaviour interpretable by construction</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -5163,32 +5220,32 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>Yes - multi-site modelling is the core contribution</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>No - models sites jointly rather than testing transfer to unseen sites</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Formalises the observation that inter-site correlation strength is time-scale dependent (geographic at hourly scales, decorrelated at minute scales) and builds a multi-scale graph architecture around it, with per-block ablation.</t>
+          <t>Introduces a physics-constrained LSTM that prevents physically unreasonable forecasts and claims improved robustness and data efficiency, targeting a known failure mode of pure data-driven models.</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>Requires a dense multi-site panel with aligned measurements, which many operators lack; the architecture is complex, raising the computational bar without a cost/accuracy frontier analysis.</t>
+          <t>Constraint design and penalty weighting are not described in the abstract, so the mechanism behind the gains cannot be assessed; robustness claims are not tied to a formal regime protocol.</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>Multi-site work optimises joint modelling but does not quantify the accuracy-versus-complexity trade-off, nor test whether a model trained on a site pool transfers to an unseen site.</t>
+          <t>Physics-informed models claim robustness benefits but do not quantify them against a transparent weather-regime protocol, leaving the central claim untested.</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>Moderate - architecture and ablations detailed; data access not described</t>
+          <t>Low to moderate - constraint mechanism not detailed in abstract; code not released per abstract</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -5201,14 +5258,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.enconman.2025.119773</t>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2021.120240</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Advanced / attention-based architectures</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Physics-informed / domain-aware</t>
         </is>
       </c>
     </row>
@@ -5218,85 +5275,85 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Cantillo-Luna et al. (2023)</t>
+          <t>Mondal et al. (2024)</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Residential PV power production (low-volume, univariate time series)</t>
+          <t>Solar power generation</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Multiple forecast horizons (univariate, various scenarios)</t>
+          <t>Short-term and long-term horizons (both claimed)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Low-volume residential PV production time series</t>
+          <t>One-year time series of solar power generation plus panel physical features and weather information</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>Durgapur, India (validation on multiple plants)</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>One year of time series; multiple plants in validation</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Not stated in retrieved abstract; characterised as low-volume</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Solar generation time series, solar panel physical features and weather information</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Weather information (specific list not in abstract)</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Domain-aware deep learning ensemble</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Deep learning ensemble based on Bi-LSTM, incorporating domain knowledge and panel physical characteristics</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Multiple standard deep learning models and traditional models</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Forecast accuracy (not enumerated in abstract)</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Reported as better than traditional models on both short and long horizons (numbers not in abstract)</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Univariate PV production history</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>None - univariate setting (an explicit and unusual design choice)</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Classical ML + deep learning benchmark</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>XGBoost, random forest, SVR, multilayer perceptron, tuned LSTM, and a proposed ConvLSTM1D</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>The other five models in the benchmark; results considered alongside technical and economic impacts</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>RMSE, MAPE, MAE</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>Random forest and ConvLSTM1D yielded the most accurate performance (lowest RMSE, MAPE, MAE) across scenarios</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>Not stated in retrieved abstract</t>
-        </is>
-      </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - physical panel features and domain knowledge are explicit inputs</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -5306,32 +5363,32 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - validated on different solar plants in Durgapur, India</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Yes - second location</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Univariate benchmark of six models on low-volume residential PV, and notably finds random forest competitive with the best deep model - an important counterweight to deep-learning dominance.</t>
+          <t>Integrates panel physical characteristics alongside weather and generation history, and claims the model forecasts well regardless of geographical position.</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>Univariate inputs discard weather information, so accuracy is capped; reported MAPE on a zero-containing target is not justified.</t>
+          <t>The generalisation claim is supported by validation at a second site within one city and climate, which is a weak test of geographic generalisation; long-horizon claims are not quantified in the abstract.</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>Provides direct evidence that a classical ensemble can match a deep architecture, reinforcing that deep models are not automatically superior - a claim most PV forecasting papers do not test.</t>
+          <t>'Generalises regardless of location' is asserted from same-climate validation - the corpus contains no true cross-climate transfer experiment to test such claims.</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>Moderate - model list and metrics explicit; data not shared per abstract</t>
+          <t>Low to moderate - inputs described qualitatively; code not released per abstract</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -5344,14 +5401,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/en16104097</t>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2024.131709</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Advanced / attention-based architectures</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Physics-informed / domain-aware</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5418,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Radzi et al. (2026)</t>
+          <t>Singh et al. (2026)</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -5369,72 +5426,72 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PV power (two array technologies)</t>
+          <t>Solar PV power generation</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Hour-ahead</t>
+          <t>Short-term</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Measurements from two PV arrays: poly-crystalline (Array 1) and mono-crystalline (Array 2)</t>
+          <t>DKASC Alice Springs dataset, four different data sequences</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tropical climate (region not named in abstract)</t>
+          <t>Alice Springs, Australia (DKASC)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Two arrays (record counts not stated in abstract)</t>
+          <t>Four data sequences from the DKASC dataset (record counts not stated in abstract)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Hourly (hour-ahead target)</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Time-indexed series used with a recursive forecasting strategy</t>
+          <t>PV generation and associated inputs across four data sequences</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Meteorological inputs (specific list not in abstract)</t>
+          <t>Meteorological inputs from the DKASC dataset (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Hybrid deep learning</t>
+          <t>Classical ML + deep learning benchmark</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Sequential GRU-LSTM hybrid with GRU as the primary connector passing short-term dependencies to an LSTM layer, with recursive forecasting</t>
+          <t>1D CNN, Bi-LSTM, Stacked LSTM, ANN, Linear Regression, SVR, XGBoost, and a hybrid CNN-LSTM</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Standalone ML and DL models, including standalone GRU and LSTM</t>
+          <t>The seven other models in the comparison</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>RMSE, MAE, R2, residual analysis</t>
+          <t>MAE, explained variance, RMSE, R2, sMAPE</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Array 1: RMSE 28.55 W, MAE 19.43 W, R2 0.9961</t>
+          <t>Stacked LSTM best: MAE 1.1157, RMSE 2.3408, explained variance 0.8998, R2 0.9004, sMAPE 1.1795 (averaged across the four sequences)</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>Tropical climatic variability is the stated context; no named regime stratification reported</t>
+          <t>Not stated in retrieved abstract; four data sequences are used but not characterised as weather regimes</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
@@ -5449,32 +5506,32 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>Partial - two co-located arrays of different technology, which tests technology transfer rather than geographic transfer</t>
+          <t>No - single site, four sequences</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - four distinct sequences act as repeated evaluation slices of one site</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tests a GRU-LSTM sequential hybrid under recursive forecasting and compares two PV technologies, which probes whether architecture conclusions are technology-dependent.</t>
+          <t>Benchmarks eight models including four classical ones on four DKASC sequences and reports sMAPE alongside MAE/RMSE/R2, which is the more defensible metric choice for a zero-containing target.</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>Recursive multi-step prediction accumulates error; a very high R2 (0.9961) on a single array is not evidence of robustness under regime change.</t>
+          <t>All four sequences come from one site, so between-site and between-climate generalisation is untested; no weather stratification despite using four separate sequences.</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>Near-perfect aggregate R2 coexists with no regime, seasonal or cross-site analysis - direct evidence that aggregate metrics can mask operational failure modes.</t>
+          <t>Demonstrates correct metric practice (sMAPE) and a broad model sweep, yet still analyses only one site and no weather regimes - showing that good metric hygiene has not been paired with robustness evaluation.</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>Moderate - architecture and metrics explicit; data not shared per abstract</t>
+          <t>Good - named public dataset (DKASC), explicit model list and full metric set</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -5484,17 +5541,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.ecmx.2025.101431</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB24" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.nxener.2026.100531</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Advanced / attention-based architectures</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Physics-informed / domain-aware</t>
         </is>
       </c>
     </row>
@@ -5504,25 +5561,25 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Luo et al. (2021)</t>
+          <t>Li et al. (2026)</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>PV power generation (hourly day-ahead)</t>
+          <t>PV power (probabilistic, day-ahead)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Hourly day-ahead</t>
+          <t>Day-ahead</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Real-life PV datasets</t>
+          <t>Real-world PV dataset</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5537,57 +5594,57 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Hourly</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Selected via a two-stage hybrid sensitivity analysis; includes PV domain knowledge as constraints</t>
+          <t>Input features compressed by an auto-encoder into a dense latent representation, concatenated back with the original features</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>PV domain knowledge and meteorological inputs (specific list not in abstract)</t>
+          <t>Meteorological features (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Physics-informed deep learning</t>
+          <t>Probabilistic deep learning</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>PC-LSTM - physics-constrained LSTM enforcing PV physical consistency</t>
+          <t>AE-BiLSTM-QR: auto-encoder feature enhancement, BiLSTM temporal modelling, and quantile regression with an Incremental Monotonicity Enforcement (IME) mechanism producing non-crossing prediction intervals</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Standard LSTM; data-only machine learning models</t>
+          <t>Several baseline models (not enumerated in abstract)</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Forecast accuracy and robustness (not enumerated in abstract)</t>
+          <t>Interval reliability, sharpness and mathematical coherence; probabilistic forecasting metrics (not enumerated in abstract)</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>PC-LSTM stronger than standard LSTM, more robust and better suited to sparse-data settings (numbers not in abstract)</t>
+          <t>Intervals reported as more reliable, sharper and mathematically coherent than baselines (numbers not in abstract)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Robustness emphasised; no named regime stratification reported</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>Partial - physical constraints make behaviour interpretable by construction</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - this is the paper's central contribution; quantile regression with enforced monotonicity</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -5602,22 +5659,22 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Introduces a physics-constrained LSTM that prevents physically unreasonable forecasts and claims improved robustness and data efficiency, targeting a known failure mode of pure data-driven models.</t>
+          <t>Addresses the quantile-crossing problem directly by predicting a baseline plus non-negative increments, yielding coherent prediction intervals from a hybrid deep model.</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>Constraint design and penalty weighting are not described in the abstract, so the mechanism behind the gains cannot be assessed; robustness claims are not tied to a formal regime protocol.</t>
+          <t>Very recent (0 citations at time of verification) and interval calibration is reported without a named coverage metric such as PICP or PINAW in the abstract, so sharpness/reliability cannot be independently judged.</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>Physics-informed models claim robustness benefits but do not quantify them against a transparent weather-regime protocol, leaving the central claim untested.</t>
+          <t>Probabilistic work exists but does not report standard calibration metrics in the abstract, and is not paired with deterministic benchmarks on a common split - limiting comparability.</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate - constraint mechanism not detailed in abstract; code not released per abstract</t>
+          <t>Low to moderate - architecture described; code and data not released per abstract</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -5630,14 +5687,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2021.120240</t>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>10.2174/0123520965458194260410052152</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Physics-informed / domain-aware</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Probabilistic / explainable / robust</t>
         </is>
       </c>
     </row>
@@ -5647,35 +5704,35 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Mondal et al. (2024)</t>
+          <t>Feng et al. (2025)</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Solar power generation</t>
+          <t>PV power probability density function (full PDF)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Short-term and long-term horizons (both claimed)</t>
+          <t>Not enumerated in retrieved abstract</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>One-year time series of solar power generation plus panel physical features and weather information</t>
+          <t>Data from a PV station in Hebei Province, China</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Durgapur, India (validation on multiple plants)</t>
+          <t>Hebei Province, China</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>One year of time series; multiple plants in validation</t>
+          <t>One PV station (record count not stated in abstract)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -5685,37 +5742,37 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Solar generation time series, solar panel physical features and weather information</t>
+          <t>Meteorological, power and coefficient-vector cross-modal inputs</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Weather information (specific list not in abstract)</t>
+          <t>Meteorological variables (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Domain-aware deep learning ensemble</t>
+          <t>Probabilistic / distribution-free deep learning with transformer</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Deep learning ensemble based on Bi-LSTM, incorporating domain knowledge and panel physical characteristics</t>
+          <t>BS-iMCFormer - B-spline approximation of a KDE-derived PDF combined with an iTransformer and multi-head cross attention; predicts B-spline control points then interpolates to a PDF</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Multiple standard deep learning models and traditional models</t>
+          <t>Comparison models (not enumerated in abstract)</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Forecast accuracy (not enumerated in abstract)</t>
+          <t>KL divergence, MAE, RMSE, R2, visual PDF overlap</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Reported as better than traditional models on both short and long horizons (numbers not in abstract)</t>
+          <t>KL divergence reduced by 54.82%; MAE and RMSE reduced by 68.93% and 69.42%; R2 improved by 6.76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -5725,42 +5782,42 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Partial - physical panel features and domain knowledge are explicit inputs</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - central contribution; distribution-free PDF forecasting avoids parametric assumptions</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Yes - validated on different solar plants in Durgapur, India</t>
+          <t>No - single station</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>Yes - second location</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Integrates panel physical characteristics alongside weather and generation history, and claims the model forecasts well regardless of geographical position.</t>
+          <t>Removes the parametric distribution assumption common to probabilistic PV methods by representing the PDF through B-spline control points predicted by a transformer with cross-modal attention.</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>The generalisation claim is supported by validation at a second site within one city and climate, which is a weak test of geographic generalisation; long-horizon claims are not quantified in the abstract.</t>
+          <t>Complex three-stage pipeline (KDE, spline coefficient prediction, interpolation) whose added cost is never reported; the headline MAE/RMSE reductions come with no deterministic baseline on a common split.</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>'Generalises regardless of location' is asserted from same-climate validation - the corpus contains no true cross-climate transfer experiment to test such claims.</t>
+          <t>Uncertainty research is architecturally sophisticated but does not report computational cost or compare against simple conformal/quantile baselines, so the accuracy-cost trade-off is unknown.</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate - inputs described qualitatively; code not released per abstract</t>
+          <t>Low to moderate - method described in detail; code not released per abstract</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5773,14 +5830,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2024.131709</t>
+      <c r="AB26" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.solener.2025.113769</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Physics-informed / domain-aware</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Probabilistic / explainable / robust</t>
         </is>
       </c>
     </row>
@@ -5790,35 +5847,35 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Singh et al. (2026)</t>
+          <t>Ozdemir et al. (2024)</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Solar PV power generation</t>
+          <t>Solar power generation</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Short-term</t>
+          <t>Not enumerated in retrieved abstract</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>DKASC Alice Springs dataset, four different data sequences</t>
+          <t>Solar power generation data (source not stated in abstract)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Alice Springs, Australia (DKASC)</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Four data sequences from the DKASC dataset (record counts not stated in abstract)</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -5828,47 +5885,47 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>PV generation and associated inputs across four data sequences</t>
+          <t>Meteorological and derived features; feature identities discussed via XAI</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Meteorological inputs from the DKASC dataset (specific list not in abstract)</t>
+          <t>Weather-related features (specific list not in abstract)</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>Classical ML + deep learning benchmark</t>
+          <t>Classical ML + explainability</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1D CNN, Bi-LSTM, Stacked LSTM, ANN, Linear Regression, SVR, XGBoost, and a hybrid CNN-LSTM</t>
+          <t>Random Forest, Gradient Boosting, XGBoost, LightGBM, Decision Tree, each paired with three XAI methods</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>The seven other models in the comparison</t>
+          <t>The other tree ensembles in the comparison</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>MAE, explained variance, RMSE, R2, sMAPE</t>
+          <t>RMSE, MSE, MAE, R2</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Stacked LSTM best: MAE 1.1157, RMSE 2.3408, explained variance 0.8998, R2 0.9004, sMAPE 1.1795 (averaged across the four sequences)</t>
+          <t>LightGBM best: RMSE 0.088, MSE 0.007749, MAE 0.052896, R2 0.842645</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract; four data sequences are used but not characterised as weather regimes</t>
+          <t>Not stated in retrieved abstract</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes - this is the paper's central contribution: SHAP, LIME and Permutation Feature Importance applied across five models</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -5878,32 +5935,32 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>No - single site, four sequences</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>Partial - four distinct sequences act as repeated evaluation slices of one site</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Benchmarks eight models including four classical ones on four DKASC sequences and reports sMAPE alongside MAE/RMSE/R2, which is the more defensible metric choice for a zero-containing target.</t>
+          <t>Applies three distinct XAI techniques to five tree ensembles and articulates their complementary roles: permutation importance identifies key features, SHAP reveals feature interactions, LIME provides local explanations.</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>All four sequences come from one site, so between-site and between-climate generalisation is untested; no weather stratification despite using four separate sequences.</t>
+          <t>Only tree ensembles are explained, so the findings do not transfer to the recurrent or attention architectures that dominate the rest of the corpus; no explanation-faithfulness validation is reported.</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>Demonstrates correct metric practice (sMAPE) and a broad model sweep, yet still analyses only one site and no weather regimes - showing that good metric hygiene has not been paired with robustness evaluation.</t>
+          <t>Explainability is confined to interpretable model families and validated only qualitatively, so the black-box architectures that most need explanation remain unexamined.</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>Good - named public dataset (DKASC), explicit model list and full metric set</t>
+          <t>Moderate - models and XAI methods explicit; dataset not shared per abstract</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -5913,17 +5970,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.nxener.2026.100531</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB27" s="5" t="inlineStr">
+        <is>
+          <t>10.1007/s00202-024-02933-4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Physics-informed / domain-aware</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Probabilistic / explainable / robust</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5990,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Li et al. (2026)</t>
+          <t>Zhang et al. (2026)</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -5941,112 +5998,112 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PV power (probabilistic, day-ahead)</t>
+          <t>PV power</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Day-ahead</t>
+          <t>Five horizons from 4 hours to 7 days (multi-horizon)</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Real-world PV dataset</t>
+          <t>Open-source datasets from four utility-scale plants in northern China and one aggregated plant in central Australia</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>Northern China (4 plants) and central Australia (1 aggregated plant)</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Five PV plants/stations</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Not stated in retrieved abstract</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Not stated in retrieved abstract</t>
-        </is>
-      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Input features compressed by an auto-encoder into a dense latent representation, concatenated back with the original features</t>
+          <t>Historical generation data fused with forward-looking inputs: numerical weather prediction, satellite-derived irradiance, and AI-based weather model forecasts</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Meteorological features (specific list not in abstract)</t>
+          <t>NWP, satellite-derived irradiance, AI weather model forecasts (three distinct forecast sources)</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Probabilistic deep learning</t>
+          <t>Transformer (encoder-decoder)</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>AE-BiLSTM-QR: auto-encoder feature enhancement, BiLSTM temporal modelling, and quantile regression with an Incremental Monotonicity Enforcement (IME) mechanism producing non-crossing prediction intervals</t>
+          <t>Cross-Unet - Transformer-based architecture with multi-scale temporal encoding, correlation-aware channel attention, and hierarchical cross-attention decoding</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Several baseline models (not enumerated in abstract)</t>
+          <t>Ten deep learning baselines plus traditional operational benchmarks</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Interval reliability, sharpness and mathematical coherence; probabilistic forecasting metrics (not enumerated in abstract)</t>
+          <t>Forecast accuracy metrics (not enumerated in abstract); horizon-resolved comparison</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Intervals reported as more reliable, sharper and mathematically coherent than baselines (numbers not in abstract)</t>
+          <t>Outperforms ten deep learning baselines and traditional operational benchmarks across the majority of evaluated configurations spanning five plants, five horizons and three forecast sources (absolute values not in abstract)</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Not stated as named regimes; conditions varied implicitly through the three forecast sources and five horizons</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial - channel attention provides architectural interpretability, but attention weights are not validated as explanations</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Yes - this is the paper's central contribution; quantile regression with enforced monotonicity</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Yes - five plants across two countries</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Yes - genuine cross-country, cross-climate evaluation</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Addresses the quantile-crossing problem directly by predicting a baseline plus non-negative increments, yielding coherent prediction intervals from a hybrid deep model.</t>
+          <t>The most rigorous benchmark in this corpus: five horizons (4 h to 7 days) x five plants x three forecast sources, against ten deep baselines and operational benchmarks, re-evaluating architectural choices and emphasising full encoder-decoder designs and channel-dependence modelling.</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>Very recent (0 citations at time of verification) and interval calibration is reported without a named coverage metric such as PICP or PINAW in the abstract, so sharpness/reliability cannot be independently judged.</t>
+          <t>Does not report weather-regime-stratified accuracy, uncertainty quantification, or computational cost, so robustness under specific conditions and the accuracy-cost trade-off remain unquantified.</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>Probabilistic work exists but does not report standard calibration metrics in the abstract, and is not paired with deterministic benchmarks on a common split - limiting comparability.</t>
+          <t>Even the most rigorous multi-horizon, multi-site benchmark in the literature omits regime-stratified evaluation, uncertainty quantification and cost reporting - showing these are systematically absent rather than merely rare.</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate - architecture described; code and data not released per abstract</t>
+          <t>Good - datasets described as open-source, full experimental grid stated; code availability not stated in abstract</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -6056,12 +6113,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>10.2174/0123520965458194260410052152</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB28" s="5" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-73817-3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -6076,80 +6133,80 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Feng et al. (2025)</t>
+          <t>Gaboitaolelwe et al. (2023)</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>PV power probability density function (full PDF)</t>
+          <t>PV power</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>Short-term (day-ahead to sub-day); horizon grid not enumerated in abstract</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Literature corpus plus authors' own ML simulation on PV data</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in retrieved abstract</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in retrieved abstract</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in retrieved abstract</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Not enumerated in retrieved abstract; reviewed models use PV history and meteorological inputs</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Meteorological inputs discussed in reviewed studies (irradiance, temperature, cloud cover among them)</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Classical machine learning (review + simulation)</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Multiple ML methods simulated by the authors for comparison; exact list not in abstract</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Persistence and previously published ML methods (as reviewed)</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>Not enumerated in retrieved abstract</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Data from a PV station in Hebei Province, China</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Hebei Province, China</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>One PV station (record count not stated in abstract)</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>Not stated in retrieved abstract</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Meteorological, power and coefficient-vector cross-modal inputs</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Meteorological variables (specific list not in abstract)</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>Probabilistic / distribution-free deep learning with transformer</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>BS-iMCFormer - B-spline approximation of a KDE-derived PDF combined with an iTransformer and multi-head cross attention; predicts B-spline control points then interpolates to a PDF</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Comparison models (not enumerated in abstract)</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>KL divergence, MAE, RMSE, R2, visual PDF overlap</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>KL divergence reduced by 54.82%; MAE and RMSE reduced by 68.93% and 69.42%; R2 improved by 6.76%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Reviewed literature covers multiple conditions; no controlled regime evaluation in the review itself</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -6159,12 +6216,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Yes - central contribution; distribution-free PDF forecasting avoids parametric assumptions</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>No - single station</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6174,22 +6231,22 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Removes the parametric distribution assumption common to probabilistic PV methods by representing the PDF through B-spline control points predicted by a transformer with cross-modal attention.</t>
+          <t>Comprehensive comparative review of ML-based short-term PV power forecasting, plus an independent simulation comparing ML methods to add evidence beyond the surveyed papers.</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>Complex three-stage pipeline (KDE, spline coefficient prediction, interpolation) whose added cost is never reported; the headline MAE/RMSE reductions come with no deterministic baseline on a common split.</t>
+          <t>Review-level aggregation; models are compared across heterogeneous studies rather than on a common dataset and split, so cross-study numbers are not directly comparable.</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>Uncertainty research is architecturally sophisticated but does not report computational cost or compare against simple conformal/quantile baselines, so the accuracy-cost trade-off is unknown.</t>
+          <t>Demonstrates the absence of a common-dataset benchmark; authors resort to their own simulation because the literature does not permit controlled comparison.</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>Low to moderate - method described in detail; code not released per abstract</t>
+          <t>Partial - review methodology described; reviewed studies' code not assessed</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -6202,14 +6259,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.solener.2025.113769</t>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/access.2023.3270041</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Probabilistic / explainable / robust</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Systematic review / state of the field</t>
         </is>
       </c>
     </row>
@@ -6219,90 +6276,90 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Ozdemir et al. (2024)</t>
+          <t>Khouili et al. (2025)</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Solar power generation</t>
+          <t>Solar irradiance and PV power</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Not enumerated in retrieved abstract</t>
+          <t>Surveyed across studies; not fixed by the review</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Solar power generation data (source not stated in abstract)</t>
+          <t>26 selected studies screened from 155 Web of Science records</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Web of Science (literature corpus, not a PV dataset)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>155 retrieved, 26 included</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Not applicable (literature corpus)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Meteorological and derived features; feature identities discussed via XAI</t>
+          <t>Ambient temperature, pressure and humidity reported as the most common input features across surveyed studies</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Weather-related features (specific list not in abstract)</t>
+          <t>Ambient temperature, pressure, humidity (most common); Wavelet Transform most common decomposition; Pearson correlation most common feature selection</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Classical ML + explainability</t>
+          <t>Deep learning (systematic review)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Random Forest, Gradient Boosting, XGBoost, LightGBM, Decision Tree, each paired with three XAI methods</t>
+          <t>LSTM (32.69% of papers), CNN (28.85%); further architectures not enumerated in abstract</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>The other tree ensembles in the comparison</t>
+          <t>Not applicable (review); baselines of surveyed studies are not aggregated in the abstract</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>RMSE, MSE, MAE, R2</t>
+          <t>Surveyed metrics catalogued but not enumerated in the retrieved abstract</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>LightGBM best: RMSE 0.088, MSE 0.007749, MAE 0.052896, R2 0.842645</t>
+          <t>Not applicable (review)</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Identified as a persistent challenge; no regime-stratified synthesis reported in the abstract</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Yes - this is the paper's central contribution: SHAP, LIME and Permutation Feature Importance applied across five models</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Identified as a persistent challenge; not itself quantified</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -6317,22 +6374,22 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Applies three distinct XAI techniques to five tree ensembles and articulates their complementary roles: permutation importance identifies key features, SHAP reveals feature interactions, LIME provides local explanations.</t>
+          <t>Systematic literature review (155 -&gt; 26 papers) quantifying which DL architectures, preprocessing techniques, input features, metrics and challenges dominate solar/PV forecasting.</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>Only tree ensembles are explained, so the findings do not transfer to the recurrent or attention architectures that dominate the rest of the corpus; no explanation-faithfulness validation is reported.</t>
+          <t>Corpus restricted to Web of Science; reported architecture frequencies describe the literature's choices, not their measured superiority.</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>Explainability is confined to interpretable model families and validated only qualitatively, so the black-box architectures that most need explanation remain unexamined.</t>
+          <t>Quantifies the field's concentration on LSTM/CNN and identifies preprocessing, metrics and persistent challenges as under-examined dimensions.</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>Moderate - models and XAI methods explicit; dataset not shared per abstract</t>
+          <t>Good - explicit inclusion/exclusion counts, database and frequencies reported</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -6345,14 +6402,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s00202-024-02933-4</t>
+      <c r="AB30" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.esr.2025.101735</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Probabilistic / explainable / robust</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Systematic review / state of the field</t>
         </is>
       </c>
     </row>
@@ -6362,120 +6419,120 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Zhang et al. (2026)</t>
+          <t>Kumari &amp; Toshniwal (2021)</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PV power</t>
+          <t>Solar irradiance</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Five horizons from 4 hours to 7 days (multi-horizon)</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Open-source datasets from four utility-scale plants in northern China and one aggregated plant in central Australia</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Northern China (4 plants) and central Australia (1 aggregated plant)</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Five PV plants/stations</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Not stated in retrieved abstract</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Historical generation data fused with forward-looking inputs: numerical weather prediction, satellite-derived irradiance, and AI-based weather model forecasts</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>NWP, satellite-derived irradiance, AI weather model forecasts (three distinct forecast sources)</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Transformer (encoder-decoder)</t>
+          <t>Deep learning (comprehensive review)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Cross-Unet - Transformer-based architecture with multi-scale temporal encoding, correlation-aware channel attention, and hierarchical cross-attention decoding</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Ten deep learning baselines plus traditional operational benchmarks</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Forecast accuracy metrics (not enumerated in abstract); horizon-resolved comparison</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Outperforms ten deep learning baselines and traditional operational benchmarks across the majority of evaluated configurations spanning five plants, five horizons and three forecast sources (absolute values not in abstract)</t>
+          <t>Not applicable (review)</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>Not stated as named regimes; conditions varied implicitly through the three forecast sources and five horizons</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Partial - channel attention provides architectural interpretability, but attention weights are not validated as explanations</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Yes - five plants across two countries</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>Yes - genuine cross-country, cross-climate evaluation</t>
+          <t>Not stated - abstract not publicly retrievable</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>The most rigorous benchmark in this corpus: five horizons (4 h to 7 days) x five plants x three forecast sources, against ten deep baselines and operational benchmarks, re-evaluating architectural choices and emphasising full encoder-decoder designs and channel-dependence modelling.</t>
+          <t>Comprehensive review of deep learning models for solar irradiance forecasting (title and venue verified; 394 citations per Semantic Scholar).</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>Does not report weather-regime-stratified accuracy, uncertainty quantification, or computational cost, so robustness under specific conditions and the accuracy-cost trade-off remain unquantified.</t>
+          <t>PROVENANCE LIMITATION: the abstract is not available from Crossref, OpenAlex, Semantic Scholar, the publisher landing page or any RePEc mirror (paywalled), so no claim beyond verified bibliographic metadata is asserted here. Full-text consultation is required before citing this work for any specific methodological or numerical detail.</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>Even the most rigorous multi-horizon, multi-site benchmark in the literature omits regime-stratified evaluation, uncertainty quantification and cost reporting - showing these are systematically absent rather than merely rare.</t>
+          <t>Not assessable without full text; flagged as unverified rather than characterised.</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>Good - datasets described as open-source, full experimental grid stated; code availability not stated in abstract</t>
+          <t>Not assessable without full text</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6485,21 +6542,54 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>10.1038/s41467-026-73817-3</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB31" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.jclepro.2021.128566</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>Crossref + OpenAlex + Semantic Scholar; category Probabilistic / explainable / robust</t>
+          <t>Crossref + OpenAlex + Semantic Scholar; category Systematic review / state of the field; FLAG: abstract_unavailable_paywalled</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC31"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AB31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6510,56 +6600,74 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="66" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="66" customWidth="1" min="7" max="7"/>
-    <col width="66" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="66" customWidth="1" min="10" max="10"/>
+    <col width="66" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Gap ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Triage Role</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Triage Reason</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Research Gap</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Evidence Papers</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Why It Matters</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Current Approaches</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Limitation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Opportunity for Our Project</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Testable Research Question</t>
         </is>
@@ -6573,35 +6681,50 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>The central gap this project addresses: no shared protocol places the classical, recurrent and attention families side by side on one leakage-audited split.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>No common-dataset benchmark places classical ML, recurrent deep learning and modern attention/transformer architectures under one identical chronological split with a strong persistence reference.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>G1, G4, D1, B1, D5, D4, A4</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>G1, A5, D1, B1, D5, D4, A4</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Without a shared split and a persistence anchor, headline improvements cannot be compared across studies, and an architecture can appear superior simply because it was benchmarked against a weak reference rather than a well-tuned classical model.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Each study selects its own site, resolution, split rule and baseline set; the largest classical comparison (G4, 24 models, 16 plants) excludes deep learning, while transformer studies (D1, D2) compare against plain LSTM.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Each study selects its own site, resolution, split rule and baseline set; the largest classical comparison (A5, 24 models, 16 plants) excludes deep learning, while transformer studies (D1, D2) compare against plain LSTM.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Cross-family comparison is performed within studies, never across the field on shared data, so the field cannot currently answer which model family is preferable.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Run classical ML, recurrent DL and one transformer-family model on one publicly documented dataset with one chronological split, one scaling policy and one persistence anchor, and report all metrics on identical test windows.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>RQ1/RQ4: Under an identical chronological split and a shared persistence anchor, do recurrent or attention-based architectures deliver a statistically significant improvement over well-tuned classical ML for short-term PV power forecasting?</t>
         </is>
@@ -6615,35 +6738,50 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Aggregate-only evaluation dominates, and a ranking change between conditions is almost never reported.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Weather-regime-stratified evaluation is rare, and where it exists each study uses an incompatible taxonomy, so regime-wise robustness cannot be compared.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>B3, B4, C4, C6, A2, D2, G2</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Aggregate error metrics average over easy clear-sky periods and hard broken-cloud periods, so a model can look strong overall while failing exactly when operators need it. Without a shared regime definition, the literature cannot establish which models are robust.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Studies classify conditions ad hoc, often using a clearness index derived from the same irradiance signal being forecast, which partly confounds regime-wise error attribution.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>No transparent, documented regime definition based solely on information available at forecast time is applied consistently, and regime labels are rarely published alongside per-regime metrics.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Define one transparent regime taxonomy computed from forecast-time-available variables only, publish the regime assignment rule and the regime-wise metrics for every model, and test whether model ranking changes across regimes.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>RQ3: Does the ranking of forecasting models change across clear, partly cloudy, cloudy and high-variability regimes, and do aggregate metrics conceal regime-specific failure?</t>
         </is>
@@ -6657,35 +6795,50 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>not retained</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>answered_by_practice</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A real reporting weakness, but this project answers it rather than documenting a gap: every comparison here is formally tested with a block bootstrap and a Diebold-Mariano procedure.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Differences between models are asserted from point estimates without formal statistical testing, so the literature cannot distinguish real improvement from sampling variation.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>C6, A4, G4, D1, D4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>C6, A4, A5, D1, D4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Error differences on a single test period can be produced by favourable weather sampling. Without paired tests and confidence intervals, an improvement claim is not verifiable and cannot be replicated.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Point-estimate comparison of MAE/RMSE/R2, occasionally with dispersion across folds, but no paired error comparison over a common test set.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>No standard error-difference test with an appropriate small-sample correction is applied, and no bootstrap confidence intervals accompany headline gains.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Apply a Diebold-Mariano test with the Harvey-Leybourne-Newbold small-sample correction plus moving-block bootstrap confidence intervals to every model comparison, and report which differences survive.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>RQ1/RQ4: Which of the observed model differences remain statistically significant after accounting for serial correlation in forecast errors?</t>
         </is>
@@ -6699,35 +6852,50 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>not retained</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>answered_by_practice</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>A genuine defect in the literature and one this project is careful about, with chronological splits and explicit leakage tests. It is a requirement of the work, not a gap the work leaves open.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Temporal leakage through non-chronological validation is common, making reported accuracy incomparable with properly time-ordered studies.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A4, G4, D4, E3, A1, F3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>A4, A5, D4, E3, A1, F3</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Random or k-fold splitting of an autocorrelated series lets a model interpolate between near-duplicate neighbouring observations, inflating accuracy and making a weak model appear competitive with a strong one.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Both k-fold cross-validation and chronological hold-out appear in the same corpus, with no reporting requirement for the split rule.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Split policy is rarely stated explicitly and is never audited, so leakage cannot be detected by a reader.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Adopt a single strictly chronological split (train / validation / test with embargoed boundaries), fit scalers on training data only, state the exact information available at forecast time, and include a leakage unit test in the test suite.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>RQ1: How much of the reported advantage of gradient-boosting and recurrent models survives when all models are evaluated under one strictly chronological, leakage-audited split?</t>
         </is>
@@ -6741,35 +6909,50 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Horizon sensitivity is asserted rather than measured, which this project measures directly and finds refutes the usual claim.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Multi-horizon evaluation is not systematic; horizon ranges differ per study and are rarely combined with a common baseline, so error growth with horizon is uncharacterised.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>F4, B3, D4, E2, B2, C1, A2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Operational value depends on horizon, and a model that wins at 15 minutes may lose at 6 hours. Without a shared horizon grid, statements about architecture suitability are not transferable.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Each study fixes its own horizon set, typically one or two values, and reports aggregate accuracy across them.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>No study reports the full accuracy-versus-horizon curve for a common model set on common data.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Evaluate every model at a fixed ladder of horizons derived from the dataset resolution, report the accuracy-horizon curve, and test whether the model ranking is horizon-stable.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>RQ2: Is model performance consistent across forecasting horizons, and does the relative advantage of advanced architectures shrink as the horizon grows?</t>
         </is>
@@ -6783,35 +6966,50 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>not retained</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>narrower_than_stated</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>The initial claim was that calibration is rarely reported. The probabilistic PV literature is methodologically careful and does report it; the real gap is narrower, that the deterministic majority reports no interval at all, and it is not this paper's contribution.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Uncertainty quantification is confined to a small minority of studies, is not paired with deterministic benchmarks on a shared split, and does not report the computational cost of its added machinery.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>F1, F2, A4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>An operator needs calibrated intervals to reserve capacity and schedule storage. Deterministic accuracy alone does not quantify risk, and an interval method that costs ten times the inference time may be unusable in real time.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Parametric quantile regression and non-parametric density estimation are both represented, but each in isolation, on a private dataset, with no shared evaluation protocol.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>No standard coverage or interval-width metric is reported in the retrieved abstracts, and no study pairs an uncertainty method with a deterministic baseline on the same test set while measuring inference cost.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Add conformal-prediction intervals around the best deterministic model, report coverage and mean interval width, verify finite-sample marginal coverage, and measure the inference-time overhead relative to the deterministic model.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>RQ7: Can an accurate deterministic model be augmented with well-calibrated prediction intervals at acceptable computational cost, and does interval width track error growth across horizons and weather regimes?</t>
         </is>
@@ -6825,35 +7023,50 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Feature importance is reported from one method, or from attention weights treated as explanations, and a single ranking cannot be checked against anything.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Explainability is applied only to inherently interpretable model families, while attention-based architectures are used without validating attention weights as explanations.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>F3, A3, D1, D2, C6, F4, D3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Attention weights are not explanations, and permutation importance does not establish causality. A benchmark that reports which meteorological variables drive error is more actionable for plant operators than an unexplained accuracy ranking.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Post-hoc feature importance for tree models; attention weights assumed to be self-interpreting in deep models; no faithfulness or stability testing of explanations.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>No study validates explanations against a ground truth or a perturbation-based check, and no study compares explanation method behaviour across model families.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Apply SHAP to tree models and permutation importance computed on the chronological test set to sequence models, report the two side by side, and state explicitly that these are predictive attributions rather than causal effects.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>RQ5/RQ7: Which meteorological and temporal variables dominate forecasting error, and do feature attributions obtained from tree and sequence models agree?</t>
         </is>
@@ -6867,35 +7080,50 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>The classical arm is reported untuned and cost is almost never reported alongside the accuracy it is meant to justify, so a fair accuracy-versus-cost frontier cannot be drawn.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>Computational cost is almost never reported alongside accuracy, so the accuracy-versus-cost trade-off that governs deployment is unknown.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>B2, B4, D3, F2, C2, D3</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>B2, B4, D3, F2, C2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>A model that cannot run at the required cadence is not deployable, and inference cost per site scales across a fleet. Reporting accuracy alone encourages architectures that are impractical at grid scale.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Cost is mentioned only incidentally, typically as a preprocessing runtime or a qualitative statement of efficiency.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>No study reports training time, inference latency, parameter count or memory alongside accuracy, so the two cannot be traded off.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Measure and report training duration, single-batch inference latency, parameter count and peak memory for every model under identical hardware and batch conditions, and present accuracy against cost rather than ranking on accuracy alone.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>RQ1 (cost dimension): What is the accuracy-per-unit-cost profile of each model family, and which models are Pareto-optimal for operational deployment?</t>
         </is>
@@ -6909,35 +7137,50 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>not retained</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>answered_by_practice</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>The observation is correct and unusual, but it is a virtue of this repository rather than a gap in the literature that the paper sets out to close.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>Reproducibility artefacts are rare: publicly released forecasting code is the exception rather than the rule, and dataset provenance is frequently unstated.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>B4, C5, D2, E3, F4, A2, A3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Without code and a named public dataset, a reported result cannot be reproduced or even approximately checked, so errors in preprocessing and leakage cannot be detected by the community.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Method descriptions are detailed enough to reimplement approximately, but exact data splits, seeds and preprocessing parameters are not released.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>There is no expectation of artefact release, and no study in the corpus documents its random seeds or software environment.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Release the full pipeline, configuration files, exact split boundaries, seeds and software versions, record every experiment to machine-readable JSON, and document the dataset source and licence explicitly.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Not a research question but a design requirement: can an independent reader regenerate the reported numbers from the released artefacts alone?</t>
         </is>
@@ -6951,41 +7194,171 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>not retained</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>answered_by_practice</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Metric inconsistency is real and this project documents every metric, but it is a matter of hygiene rather than a research gap.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>Forecast-error metric practice is inconsistent, and percentage errors are reported on a target that is exactly zero outside daylight hours without justification.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>C1, D2, D4, E3, A2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MAPE is undefined at zero and is dominated by near-zero daylight-morning and evening values, so it can rank models by behaviour in periods that carry negligible energy. Mixed conventions prevent meta-analysis.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Studies freely mix MAE, RMSE, MAPE, sMAPE and R2 without a stated primary metric or a night-time masking policy.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>No shared primary metric, no explicit handling of zero-target periods, and no agreement on normalising error by installed capacity rather than by the observed mean.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Fix a primary metric family (MAE, RMSE, nRMSE, R2, sMAPE) with explicit formulas, avoid MAPE on the zero-containing target, report daylight and night-time periods separately, and justify every normalisation choice.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>RQ3: Do aggregate rankings change when errors are restricted to daylight hours, i.e. how much of reported PV forecasting error is a night-time metric artefact?</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RG-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Retained: the reference's competence is a function of the horizon, so the choice of persistence reference is a substantive design decision rather than a formality.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Skill is almost always reported against naive persistence, while the clear-sky-corrected variant appears in only a few studies and skill against it is rarer still</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>B1, B3, C1, C4, D1, G1</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Skill against naive persistence flatters every model, because naive persistence is a weak reference at long horizons and a strong one at short ones. On this data the two references separate by 16% in RMSE at one hour, and four of eleven models fail to beat the stronger of them</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Studies compare against naive persistence, or against a climatological or seasonal average, without stating which reference the skill score is measured from</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>The clear-sky-corrected reference requires a clear-sky model and a capacity estimate, and studies that do not report them cannot be compared on skill at all</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Report both references for every model, define skill explicitly, and evaluate on identical timestamps so the reference choice is visible</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>RQ1: How much of a reported skill score is attributable to the choice of persistence reference, and how many models change rank between the two?</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RG-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>retained</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Retained: this is the clearest methodological gap in the reproduction literature, and it is where the project obtains its most consequential result, which is a negative one.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Cross-site transfer is claimed far more often than it is validated: the corpus contains many multi-site and spatiotemporal studies and very few evaluations that fit at one installation and test at another</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>D2, D3, G1, G2, B3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>A model fitted at one installation carries site-specific calibration. Reporting such a model as a general solar forecaster is unsupported, and the corpus rarely tests the assumption it relies on</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Either a single site is studied and generalisation is assumed, or many sites are pooled into one model, which tests a different claim: that a single network serves every site, not that a site-specific model transfers</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>A transfer protocol is expensive: leave-one-site-out over a panel multiplies the fit count by the panel size, which is why it is absent even from studies with the data to run it</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Fix a station panel and run three protocols: within-site, cross-site and leave-one-site-out pooling, with capacity normalisation and scalers fitted on training sites only</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>RQ6: Does a model fitted at one PV installation retain its skill at a different installation, and does pooling training sites repair the transfer?</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7012,7 +7385,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Paper ID</t>
         </is>
@@ -7066,17 +7439,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10.1109/access.2023.3270041</t>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.asoc.2020.106389</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Based Solar Photovoltaic Power Forecasting: A Review and Comparison</t>
+          <t>Short-term photovoltaic power generation forecasting based on random forest feature selection and CEEMD: A case study</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7085,7 +7458,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1224</v>
+        <v>1285</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -7096,36 +7469,36 @@
         <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.esr.2025.101735</t>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>10.1002/pip.1152</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Evaluating the impact of deep learning approaches on solar and photovoltaic power forecasting: A systematic review</t>
+          <t>Use of support vector regression and numerically predicted cloudiness to forecast power output of a photovoltaic power plant in Kitakyushu, Japan</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>openalex_inverted_index</t>
+          <t>crossref</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2087</v>
+        <v>1318</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -7136,36 +7509,36 @@
         <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>49</v>
+        <v>153</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>51</v>
+        <v>132</v>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.jclepro.2021.128566</t>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/en14133992</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Deep learning models for solar irradiance forecasting: A comprehensive review</t>
+          <t>Enhanced Random Forest Model for Robust Short-Term Photovoltaic Power Forecasting Using Weather Measurements</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>unavailable_paywalled</t>
+          <t>crossref</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -7176,40 +7549,36 @@
         <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>394</v>
+        <v>52</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>399</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>abstract_unavailable_paywalled</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.rser.2022.112364</t>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-026-47042-3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Comparison of machine learning methods for photovoltaic power forecasting based on numerical weather prediction</t>
+          <t>A stacked Gradient Boosting–XGBoost ensemble with ridge meta-learner for accurate short-term solar PV power forecasting in smart grids</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>openalex_inverted_index</t>
+          <t>semanticscholar</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1671</v>
+        <v>2050</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -7220,36 +7589,36 @@
         <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>429</v>
+        <v>8</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>469</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.asoc.2020.106389</t>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.rser.2022.112364</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Short-term photovoltaic power generation forecasting based on random forest feature selection and CEEMD: A case study</t>
+          <t>Comparison of machine learning methods for photovoltaic power forecasting based on numerical weather prediction</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>semanticscholar</t>
+          <t>openalex_inverted_index</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1285</v>
+        <v>1671</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -7260,36 +7629,36 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>226</v>
+        <v>429</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>242</v>
+        <v>469</v>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>10.1002/pip.1152</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2019.116225</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Use of support vector regression and numerically predicted cloudiness to forecast power output of a photovoltaic power plant in Kitakyushu, Japan</t>
+          <t>Photovoltaic power forecasting based LSTM-Convolutional Network</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>crossref</t>
+          <t>semanticscholar</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1318</v>
+        <v>1511</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -7300,36 +7669,36 @@
         <v>1</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>153</v>
+        <v>463</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>132</v>
+        <v>483</v>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/en14133992</t>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.segan.2023.101133</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Enhanced Random Forest Model for Robust Short-Term Photovoltaic Power Forecasting Using Weather Measurements</t>
+          <t>Forecasting hourly day-ahead solar photovoltaic power generation by assembling a new adaptive multivariate data analysis with a long short-term memory network</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>crossref</t>
+          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1145</v>
+        <v>1316</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -7340,27 +7709,27 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>10.1038/s41598-026-47042-3</t>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/access.2019.2946057</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>A stacked Gradient Boosting–XGBoost ensemble with ridge meta-learner for accurate short-term solar PV power forecasting in smart grids</t>
+          <t>An LSTM Short-Term Solar Irradiance Forecasting Under Complicated Weather Conditions</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -7369,7 +7738,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2050</v>
+        <v>1792</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -7380,27 +7749,27 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>8</v>
+        <v>258</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2019.116225</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.solener.2019.06.041</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Photovoltaic power forecasting based LSTM-Convolutional Network</t>
+          <t>Short-term solar power forecast with deep learning: Exploring optimal input and output configuration</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7409,7 +7778,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1511</v>
+        <v>1251</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -7420,36 +7789,36 @@
         <v>1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>463</v>
+        <v>177</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>483</v>
+        <v>195</v>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.segan.2023.101133</t>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.measurement.2020.108250</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Forecasting hourly day-ahead solar photovoltaic power generation by assembling a new adaptive multivariate data analysis with a long short-term memory network</t>
+          <t>Deep learning and wavelet transform integrated approach for short-term solar PV power prediction</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
+          <t>semanticscholar</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1316</v>
+        <v>1025</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -7460,27 +7829,27 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27</v>
+        <v>199</v>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>10.1109/access.2019.2946057</t>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/tste.2021.3123337</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>An LSTM Short-Term Solar Irradiance Forecasting Under Complicated Weather Conditions</t>
+          <t>Intra-Hour Photovoltaic Generation Forecasting Based on Multi-Source Data and Deep Learning Methods</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -7489,7 +7858,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1792</v>
+        <v>1086</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -7500,36 +7869,36 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>258</v>
+        <v>86</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>300</v>
+        <v>99</v>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.solener.2019.06.041</t>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.renene.2024.120437</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Short-term solar power forecast with deep learning: Exploring optimal input and output configuration</t>
+          <t>Short-term photovoltaic power forecasting with feature extraction and attention mechanisms</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>semanticscholar</t>
+          <t>publisher_abstract_via_repec_indexed_excerpt</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1251</v>
+        <v>1404</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -7540,36 +7909,36 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.measurement.2020.108250</t>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/app14125189</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Deep learning and wavelet transform integrated approach for short-term solar PV power prediction</t>
+          <t>A Hybrid Convolutional–Long Short-Term Memory–Attention Framework for Short-Term Photovoltaic Power Forecasting, Incorporating Data from Neighboring Stations</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>semanticscholar</t>
+          <t>crossref</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1025</v>
+        <v>1198</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -7580,76 +7949,74 @@
         <v>1</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>176</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>199</v>
+        <v>16</v>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>10.1109/tste.2021.3123337</t>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2022.124661</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Intra-Hour Photovoltaic Generation Forecasting Based on Multi-Source Data and Deep Learning Methods</t>
+          <t>LOWESS smoothing and Random Forest based GRU model: A short-term photovoltaic power generation forecasting method</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>semanticscholar</t>
+          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1086</v>
+        <v>1408</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>crossref, openalex, s2</t>
+          <t>crossref, openalex</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>86</v>
-      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.renene.2024.120437</t>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/en19071747</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Short-term photovoltaic power forecasting with feature extraction and attention mechanisms</t>
+          <t>Short-Term Photovoltaic Power Forecasting Based on CNN–LSTM–Attention Mechanism</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>publisher_abstract_via_repec_indexed_excerpt</t>
+          <t>crossref</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1404</v>
+        <v>1397</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -7660,36 +8027,36 @@
         <v>1</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/app14125189</t>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.rser.2024.114479</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>A Hybrid Convolutional–Long Short-Term Memory–Attention Framework for Short-Term Photovoltaic Power Forecasting, Incorporating Data from Neighboring Stations</t>
+          <t>Multi-step photovoltaic power forecasting using transformer and recurrent neural networks</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>crossref</t>
+          <t>publisher_abstract_via_openalex_indexed_highlights</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1198</v>
+        <v>1149</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -7700,74 +8067,76 @@
         <v>1</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2022.124661</t>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.egyai.2024.100444</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>LOWESS smoothing and Random Forest based GRU model: A short-term photovoltaic power generation forecasting method</t>
+          <t>Photovoltaic power forecasting: A Transformer based framework</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
+          <t>openalex_inverted_index</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1408</v>
+        <v>1305</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>crossref, openalex</t>
+          <t>crossref, openalex, s2</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H18" s="2" t="n"/>
+      <c r="H18" s="2" t="n">
+        <v>93</v>
+      </c>
       <c r="I18" s="2" t="n">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/en19071747</t>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.enconman.2025.119773</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Short-Term Photovoltaic Power Forecasting Based on CNN–LSTM–Attention Mechanism</t>
+          <t>Multi-scale fused Graph Convolutional Network for multi-site photovoltaic power forecasting</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>crossref</t>
+          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1397</v>
+        <v>1896</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -7778,36 +8147,36 @@
         <v>1</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.rser.2024.114479</t>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>10.3390/en16104097</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Multi-step photovoltaic power forecasting using transformer and recurrent neural networks</t>
+          <t>Deep and Machine Learning Models to Forecast Photovoltaic Power Generation</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>publisher_abstract_via_openalex_indexed_highlights</t>
+          <t>crossref</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1149</v>
+        <v>1288</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -7818,27 +8187,27 @@
         <v>1</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.egyai.2024.100444</t>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.ecmx.2025.101431</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Photovoltaic power forecasting: A Transformer based framework</t>
+          <t>Enhancing short-term solar power forecasting using a hybrid deep learning approach and a comparative analysis of machine learning models</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -7847,7 +8216,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1305</v>
+        <v>2270</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -7858,36 +8227,36 @@
         <v>1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.enconman.2025.119773</t>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2021.120240</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Multi-scale fused Graph Convolutional Network for multi-site photovoltaic power forecasting</t>
+          <t>Deep learning based forecasting of photovoltaic power generation by incorporating domain knowledge</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
+          <t>semanticscholar</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1896</v>
+        <v>1516</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -7898,36 +8267,36 @@
         <v>1</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>13</v>
+        <v>302</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/en16104097</t>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.energy.2024.131709</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Deep and Machine Learning Models to Forecast Photovoltaic Power Generation</t>
+          <t>Solar power forecasting using domain knowledge</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>crossref</t>
+          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1288</v>
+        <v>1209</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -7938,27 +8307,27 @@
         <v>1</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.ecmx.2025.101431</t>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.nxener.2026.100531</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Enhancing short-term solar power forecasting using a hybrid deep learning approach and a comparative analysis of machine learning models</t>
+          <t>Deep learning prediction models for short-term solar photovoltaic power generation forecasting</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -7967,7 +8336,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2270</v>
+        <v>1616</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -7978,36 +8347,36 @@
         <v>1</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2021.120240</t>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>10.2174/0123520965458194260410052152</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Deep learning based forecasting of photovoltaic power generation by incorporating domain knowledge</t>
+          <t>Day-Ahead Probabilistic Photovoltaic Power Forecasting based on Deep Feature Enhancement and Bidirectional Temporal Modeling</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>semanticscholar</t>
+          <t>crossref</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1516</v>
+        <v>1847</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -8018,27 +8387,27 @@
         <v>1</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2024.131709</t>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.solener.2025.113769</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Solar power forecasting using domain knowledge</t>
+          <t>Distribution-Free photovoltaic power probability density forecasting based on hybrid deep learning</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -8047,7 +8416,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1209</v>
+        <v>1741</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -8058,36 +8427,36 @@
         <v>1</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.nxener.2026.100531</t>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>10.1007/s00202-024-02933-4</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Deep learning prediction models for short-term solar photovoltaic power generation forecasting</t>
+          <t>Machine learning insights into forecasting solar power generation with explainable AI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>openalex_inverted_index</t>
+          <t>publisher_landing_page_meta</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1616</v>
+        <v>1738</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -8098,27 +8467,27 @@
         <v>1</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10.2174/0123520965458194260410052152</t>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-73817-3</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Day-Ahead Probabilistic Photovoltaic Power Forecasting based on Deep Feature Enhancement and Bidirectional Temporal Modeling</t>
+          <t>Rethinking the use of deep learning methods for photovoltaic power forecasting</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -8127,7 +8496,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1847</v>
+        <v>1523</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -8141,33 +8510,33 @@
         <v>0</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.solener.2025.113769</t>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>10.1109/access.2023.3270041</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Distribution-Free photovoltaic power probability density forecasting based on hybrid deep learning</t>
+          <t>Machine Learning Based Solar Photovoltaic Power Forecasting: A Review and Comparison</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>publisher_abstract_via_sciencedirect_indexed_excerpt</t>
+          <t>semanticscholar</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1741</v>
+        <v>1224</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -8178,36 +8547,36 @@
         <v>1</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8</v>
+        <v>241</v>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10.1007/s00202-024-02933-4</t>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.esr.2025.101735</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Machine learning insights into forecasting solar power generation with explainable AI</t>
+          <t>Evaluating the impact of deep learning approaches on solar and photovoltaic power forecasting: A systematic review</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>publisher_landing_page_meta</t>
+          <t>openalex_inverted_index</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1738</v>
+        <v>2087</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -8218,36 +8587,36 @@
         <v>1</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10.1038/s41467-026-73817-3</t>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.jclepro.2021.128566</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Rethinking the use of deep learning methods for photovoltaic power forecasting</t>
+          <t>Deep learning models for solar irradiance forecasting: A comprehensive review</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>crossref</t>
+          <t>unavailable_paywalled</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1523</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -8258,14 +8627,51 @@
         <v>1</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
+        <v>399</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>abstract_unavailable_paywalled</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J31"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8276,248 +8682,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Corpus size</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Selection protocol</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Discovery seeds were treated as hypotheses only. Each candidate title was resolved against Crossref and OpenAlex by normalised title similarity, then the surviving records were verified by DOI against Crossref, OpenAlex and Semantic Scholar. Records that resolved only to a preprint, or to a venue below the corpus quality bar, were replaced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Peer-review status</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>All 30 records are Crossref type 'journal-article'. No preprints, posters or withdrawn records are included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Excluded candidates</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Exclusion log</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>See the 'Exclusion Log' sheet and tools/literature/exclusions.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Verification artefacts</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>literature/verification/verified_papers.json and literature/verification/raw/*.json (unmodified API payloads)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Known limitation</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>G3 (Kumari &amp; Toshniwal, 2021) has a paywalled abstract that no open metadata source exposes. Its bibliographic metadata is verified; no methodological or numerical claim is asserted for it anywhere in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Workbook generated</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Generator</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>tools/literature/build_workbook.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Field</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Excluded candidate</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="n"/>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Reason for exclusion</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Corpus size</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C2" s="2" t="n"/>
+          <t>10.1080/23311804.2022.2042642</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Solar Photovoltaic Energy Forecasting Using Machine Learning and Deep Learning Technique</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Peer-reviewed but published in a regional IEEE section conference (UPCON 2022) with a narrow experimental scope; excluded to keep the classical-ML category at five higher-quality sources. Verified metadata is retained in literature/verification/ for audit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Selection protocol</t>
+          <t>10.3390/app13126990</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Discovery seeds were treated as hypotheses only. Each candidate title was resolved against Crossref and OpenAlex by normalised title similarity, then the surviving records were verified by DOI against Crossref, OpenAlex and Semantic Scholar. Records that resolved only to a preprint, or to a venue below the corpus quality bar, were replaced.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n"/>
+          <t>Evaluating the Impact of Deep Learning Approaches on Solar and Photovoltaic Power Forecasting: A Systematic Review</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Original seed DOI guess was wrong; the title was resolved to Energy Strategy Reviews (2025) and retained as G2 under its verified DOI.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Peer-review status</t>
+          <t>arXiv (OpenAlex only match)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>All 30 records are Crossref type 'journal-article'. No preprints, posters or withdrawn records are included.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
+          <t>Transformers Applied to Short-term Solar PV Power Output Forecasting</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Resolves only to an arXiv preprint with no peer-reviewed version located. Excluded because the review corpus is restricted to peer-reviewed publications; transformer-family PV forecasting is instead represented by two journal articles (D1 RSER 2024, D2 Energy and AI 2024).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Excluded candidates</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="n"/>
+          <t>10.1016/j.energy.2023.126306</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>A Hybrid VMD-GRU Model for Enhanced Photovoltaic Power Forecasting</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Resolved to a 2025 SENZE conference paper with zero citations and no abstract available from any source. Replaced by a peer-reviewed Energy (2022) hybrid decomposition-plus-recurrent study (C5, 10.1016/j.energy.2022.124661).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Exclusion log</t>
+          <t>10.1016/j.rser.2022.112364</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>See the 'Selection and Exclusions' rows below and tools/literature/exclusions.json</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Verification artefacts</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>literature/verification/verified_papers.json and literature/verification/raw/*.json (unmodified API payloads)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Known limitation</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>G3 (Kumari &amp; Toshniwal, 2021) has a paywalled abstract that no open metadata source exposes. Its bibliographic metadata is verified; no methodological or numerical claim is asserted for it anywhere in this workbook.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Workbook generated</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Generator</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>tools/literature/build_workbook.py</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Excluded candidate</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Reason for exclusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>10.1080/23311804.2022.2042642</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Solar Photovoltaic Energy Forecasting Using Machine Learning and Deep Learning Technique</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Peer-reviewed but published in a regional IEEE section conference (UPCON 2022) with a narrow experimental scope; excluded to keep the classical-ML category at five higher-quality sources. Verified metadata is retained in literature/verification/ for audit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10.3390/app13126990</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Evaluating the Impact of Deep Learning Approaches on Solar and Photovoltaic Power Forecasting: A Systematic Review</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Original seed DOI guess was wrong; the title was resolved to Energy Strategy Reviews (2025) and retained as G2 under its verified DOI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>arXiv (OpenAlex only match)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Transformers Applied to Short-term Solar PV Power Output Forecasting</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Resolves only to an arXiv preprint with no peer-reviewed version located. Excluded because the review corpus is restricted to peer-reviewed publications; transformer-family PV forecasting is instead represented by two journal articles (D1 RSER 2024, D2 Energy and AI 2024).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.energy.2023.126306</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>A Hybrid VMD-GRU Model for Enhanced Photovoltaic Power Forecasting</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Resolved to a 2025 SENZE conference paper with zero citations and no abstract available from any source. Replaced by a peer-reviewed Energy (2022) hybrid decomposition-plus-recurrent study (C5, 10.1016/j.energy.2022.124661).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10.1016/j.rser.2022.112364</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
           <t>Comparison of machine learning methods for photovoltaic power forecasting based on numerical weather prediction data</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Not excluded. Initially seeded twice (G4 and A1); deduplicated to a single record and classified under category A because its contribution is a controlled classical-ML comparison.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>